--- a/source-data/Strategic_End_User_Facilities_Bottler_Expansion_v2.xlsx
+++ b/source-data/Strategic_End_User_Facilities_Bottler_Expansion_v2.xlsx
@@ -2,9 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Master Facilities v2" sheetId="1" r:id="R85d9318630b645cc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Research Coverage" sheetId="2" r:id="R707da258fe6a4c71"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scope &amp; Notes" sheetId="3" r:id="R464701b413b54a34"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Master Facilities v2" sheetId="1" r:id="Raee20bc6c58943b1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Research Coverage" sheetId="2" r:id="R7b9d10ee66cc4c27"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scope &amp; Notes" sheetId="3" r:id="Rd3d241d6bfa7422f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coordinate Audit" sheetId="4" r:id="R37efbe295822440d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -15,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="2">
+  <x:numFmts count="1">
+    <x:numFmt numFmtId="200" formatCode="0.000000"/>
+  </x:numFmts>
+  <x:fonts count="4">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -26,8 +30,19 @@
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF172532"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Arial"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="3">
+  <x:fills count="4">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -39,15 +54,110 @@
         <x:fgColor rgb="FF0B3A6E"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF0A3F73"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="2">
+  <x:borders count="11">
     <x:border/>
     <x:border/>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFD9E4EC"/>
+      </x:right>
+      <x:bottom style="thin">
+        <x:color rgb="FFD9E4EC"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD9E4EC"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD9E4EC"/>
+      </x:right>
+      <x:bottom style="thin">
+        <x:color rgb="FFD9E4EC"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD9E4EC"/>
+      </x:left>
+      <x:bottom style="thin">
+        <x:color rgb="FFD9E4EC"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFD9E4EC"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD9E4EC"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD9E4EC"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD9E4EC"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD9E4EC"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD9E4EC"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD9E4EC"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD9E4EC"/>
+      </x:left>
+      <x:top style="thin">
+        <x:color rgb="FFD9E4EC"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD9E4EC"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFD9E4EC"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD9E4EC"/>
+      </x:top>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD9E4EC"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD9E4EC"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD9E4EC"/>
+      </x:top>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD9E4EC"/>
+      </x:left>
+      <x:top style="thin">
+        <x:color rgb="FFD9E4EC"/>
+      </x:top>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="16">
+  <x:cellXfs count="40">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -84,6 +194,76 @@
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -91,14 +271,14 @@
   <x:dxfs count="2">
     <x:dxf>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF2CC"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
     <x:dxf>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFD9EAF7"/>
         </x:patternFill>
       </x:fill>
@@ -140,6 +320,20 @@
     <x:tableColumn id="4" name="Production Rows Added"/>
     <x:tableColumn id="5" name="Exact-Street Rows"/>
     <x:tableColumn id="6" name="Research Status"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="CoordinateAuditTable" displayName="CoordinateAuditTable" ref="A1:F258" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="6">
+    <x:tableColumn id="1" name="Excel Row"/>
+    <x:tableColumn id="2" name="Facility Name"/>
+    <x:tableColumn id="3" name="Coordinate Status"/>
+    <x:tableColumn id="4" name="Method / Source"/>
+    <x:tableColumn id="5" name="Match Quality"/>
+    <x:tableColumn id="6" name="Matched Address / Note"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -439,8 +633,12 @@
       <x:c r="J2" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K2" s="11"/>
-      <x:c r="L2" s="11"/>
+      <x:c r="K2" s="16" t="n">
+        <x:v>34.3580189</x:v>
+      </x:c>
+      <x:c r="L2" s="16" t="n">
+        <x:v>-118.5108299</x:v>
+      </x:c>
       <x:c r="M2" s="11"/>
       <x:c r="N2" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -481,8 +679,8 @@
       <x:c r="J3" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K3" s="11"/>
-      <x:c r="L3" s="11"/>
+      <x:c r="K3" s="16"/>
+      <x:c r="L3" s="16"/>
       <x:c r="M3" s="11"/>
       <x:c r="N3" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -523,8 +721,12 @@
       <x:c r="J4" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K4" s="11"/>
-      <x:c r="L4" s="11"/>
+      <x:c r="K4" s="16" t="n">
+        <x:v>34.357177502647</x:v>
+      </x:c>
+      <x:c r="L4" s="16" t="n">
+        <x:v>-118.517580801525</x:v>
+      </x:c>
       <x:c r="M4" s="11"/>
       <x:c r="N4" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -561,8 +763,8 @@
       <x:c r="J5" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K5" s="11"/>
-      <x:c r="L5" s="11"/>
+      <x:c r="K5" s="16"/>
+      <x:c r="L5" s="16"/>
       <x:c r="M5" s="11"/>
       <x:c r="N5" s="11" t="str">
         <x:v>Verified city - street address pending</x:v>
@@ -601,8 +803,8 @@
       <x:c r="J6" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K6" s="11"/>
-      <x:c r="L6" s="11"/>
+      <x:c r="K6" s="16"/>
+      <x:c r="L6" s="16"/>
       <x:c r="M6" s="11"/>
       <x:c r="N6" s="11" t="str">
         <x:v>Planned - official source</x:v>
@@ -645,8 +847,8 @@
       <x:c r="J7" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K7" s="11"/>
-      <x:c r="L7" s="11"/>
+      <x:c r="K7" s="16"/>
+      <x:c r="L7" s="16"/>
       <x:c r="M7" s="11"/>
       <x:c r="N7" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -683,8 +885,8 @@
       <x:c r="J8" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K8" s="11"/>
-      <x:c r="L8" s="11"/>
+      <x:c r="K8" s="16"/>
+      <x:c r="L8" s="16"/>
       <x:c r="M8" s="11"/>
       <x:c r="N8" s="11" t="str">
         <x:v>Verified city - official source</x:v>
@@ -721,8 +923,8 @@
       <x:c r="J9" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K9" s="11"/>
-      <x:c r="L9" s="11"/>
+      <x:c r="K9" s="16"/>
+      <x:c r="L9" s="16"/>
       <x:c r="M9" s="11"/>
       <x:c r="N9" s="11" t="str">
         <x:v>Verified city - official source</x:v>
@@ -759,8 +961,8 @@
       <x:c r="J10" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K10" s="11"/>
-      <x:c r="L10" s="11"/>
+      <x:c r="K10" s="16"/>
+      <x:c r="L10" s="16"/>
       <x:c r="M10" s="11"/>
       <x:c r="N10" s="11" t="str">
         <x:v>Verified city - official source</x:v>
@@ -797,8 +999,8 @@
       <x:c r="J11" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K11" s="11"/>
-      <x:c r="L11" s="11"/>
+      <x:c r="K11" s="16"/>
+      <x:c r="L11" s="16"/>
       <x:c r="M11" s="11"/>
       <x:c r="N11" s="11" t="str">
         <x:v>Verified city - official source</x:v>
@@ -835,8 +1037,8 @@
       <x:c r="J12" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K12" s="11"/>
-      <x:c r="L12" s="11"/>
+      <x:c r="K12" s="16"/>
+      <x:c r="L12" s="16"/>
       <x:c r="M12" s="11"/>
       <x:c r="N12" s="11" t="str">
         <x:v>Verified city - official source</x:v>
@@ -873,8 +1075,8 @@
       <x:c r="J13" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K13" s="11"/>
-      <x:c r="L13" s="11"/>
+      <x:c r="K13" s="16"/>
+      <x:c r="L13" s="16"/>
       <x:c r="M13" s="11"/>
       <x:c r="N13" s="11" t="str">
         <x:v>Verified city - official source</x:v>
@@ -911,8 +1113,8 @@
       <x:c r="J14" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K14" s="11"/>
-      <x:c r="L14" s="11"/>
+      <x:c r="K14" s="16"/>
+      <x:c r="L14" s="16"/>
       <x:c r="M14" s="11"/>
       <x:c r="N14" s="11" t="str">
         <x:v>Verified city - official source</x:v>
@@ -949,8 +1151,8 @@
       <x:c r="J15" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K15" s="11"/>
-      <x:c r="L15" s="11"/>
+      <x:c r="K15" s="16"/>
+      <x:c r="L15" s="16"/>
       <x:c r="M15" s="11"/>
       <x:c r="N15" s="11" t="str">
         <x:v>Verified city - official source</x:v>
@@ -987,8 +1189,8 @@
       <x:c r="J16" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K16" s="11"/>
-      <x:c r="L16" s="11"/>
+      <x:c r="K16" s="16"/>
+      <x:c r="L16" s="16"/>
       <x:c r="M16" s="11"/>
       <x:c r="N16" s="11" t="str">
         <x:v>Verified city - official source</x:v>
@@ -1025,8 +1227,8 @@
       <x:c r="J17" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K17" s="11"/>
-      <x:c r="L17" s="11"/>
+      <x:c r="K17" s="16"/>
+      <x:c r="L17" s="16"/>
       <x:c r="M17" s="11"/>
       <x:c r="N17" s="11" t="str">
         <x:v>Closure / sale announced - verify active status</x:v>
@@ -1065,8 +1267,8 @@
       <x:c r="J18" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K18" s="11"/>
-      <x:c r="L18" s="11"/>
+      <x:c r="K18" s="16"/>
+      <x:c r="L18" s="16"/>
       <x:c r="M18" s="11"/>
       <x:c r="N18" s="11" t="str">
         <x:v>Closure / sale announced - verify active status</x:v>
@@ -1105,8 +1307,8 @@
       <x:c r="J19" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K19" s="11"/>
-      <x:c r="L19" s="11"/>
+      <x:c r="K19" s="16"/>
+      <x:c r="L19" s="16"/>
       <x:c r="M19" s="11"/>
       <x:c r="N19" s="11" t="str">
         <x:v>Closure / sale announced - verify active status</x:v>
@@ -1145,8 +1347,8 @@
       <x:c r="J20" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K20" s="11"/>
-      <x:c r="L20" s="11"/>
+      <x:c r="K20" s="16"/>
+      <x:c r="L20" s="16"/>
       <x:c r="M20" s="11"/>
       <x:c r="N20" s="11" t="str">
         <x:v>Verified city - official source</x:v>
@@ -1183,8 +1385,8 @@
       <x:c r="J21" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K21" s="11"/>
-      <x:c r="L21" s="11"/>
+      <x:c r="K21" s="16"/>
+      <x:c r="L21" s="16"/>
       <x:c r="M21" s="11"/>
       <x:c r="N21" s="11" t="str">
         <x:v>Verified city - official source</x:v>
@@ -1221,8 +1423,8 @@
       <x:c r="J22" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K22" s="11"/>
-      <x:c r="L22" s="11"/>
+      <x:c r="K22" s="16"/>
+      <x:c r="L22" s="16"/>
       <x:c r="M22" s="11"/>
       <x:c r="N22" s="11" t="str">
         <x:v>Verified city - official source</x:v>
@@ -1259,8 +1461,8 @@
       <x:c r="J23" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K23" s="11"/>
-      <x:c r="L23" s="11"/>
+      <x:c r="K23" s="16"/>
+      <x:c r="L23" s="16"/>
       <x:c r="M23" s="11"/>
       <x:c r="N23" s="11" t="str">
         <x:v>Current status check required</x:v>
@@ -1299,8 +1501,8 @@
       <x:c r="J24" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K24" s="11"/>
-      <x:c r="L24" s="11"/>
+      <x:c r="K24" s="16"/>
+      <x:c r="L24" s="16"/>
       <x:c r="M24" s="11"/>
       <x:c r="N24" s="11" t="str">
         <x:v>Current status check required</x:v>
@@ -1339,8 +1541,8 @@
       <x:c r="J25" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K25" s="11"/>
-      <x:c r="L25" s="11"/>
+      <x:c r="K25" s="16"/>
+      <x:c r="L25" s="16"/>
       <x:c r="M25" s="11"/>
       <x:c r="N25" s="11" t="str">
         <x:v>Current status check required</x:v>
@@ -1379,8 +1581,8 @@
       <x:c r="J26" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K26" s="11"/>
-      <x:c r="L26" s="11"/>
+      <x:c r="K26" s="16"/>
+      <x:c r="L26" s="16"/>
       <x:c r="M26" s="11"/>
       <x:c r="N26" s="11" t="str">
         <x:v>Current status check required</x:v>
@@ -1419,8 +1621,8 @@
       <x:c r="J27" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K27" s="11"/>
-      <x:c r="L27" s="11"/>
+      <x:c r="K27" s="16"/>
+      <x:c r="L27" s="16"/>
       <x:c r="M27" s="11"/>
       <x:c r="N27" s="11" t="str">
         <x:v>Current status check required</x:v>
@@ -1459,8 +1661,8 @@
       <x:c r="J28" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K28" s="11"/>
-      <x:c r="L28" s="11"/>
+      <x:c r="K28" s="16"/>
+      <x:c r="L28" s="16"/>
       <x:c r="M28" s="11"/>
       <x:c r="N28" s="11" t="str">
         <x:v>Current status check required</x:v>
@@ -1499,8 +1701,8 @@
       <x:c r="J29" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K29" s="11"/>
-      <x:c r="L29" s="11"/>
+      <x:c r="K29" s="16"/>
+      <x:c r="L29" s="16"/>
       <x:c r="M29" s="11"/>
       <x:c r="N29" s="11" t="str">
         <x:v>Current status check required</x:v>
@@ -1539,8 +1741,8 @@
       <x:c r="J30" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K30" s="11"/>
-      <x:c r="L30" s="11"/>
+      <x:c r="K30" s="16"/>
+      <x:c r="L30" s="16"/>
       <x:c r="M30" s="11"/>
       <x:c r="N30" s="11" t="str">
         <x:v>Verified city - street address pending</x:v>
@@ -1577,8 +1779,8 @@
       <x:c r="J31" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K31" s="11"/>
-      <x:c r="L31" s="11"/>
+      <x:c r="K31" s="16"/>
+      <x:c r="L31" s="16"/>
       <x:c r="M31" s="11"/>
       <x:c r="N31" s="11" t="str">
         <x:v>Verified city - street address pending</x:v>
@@ -1615,8 +1817,8 @@
       <x:c r="J32" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K32" s="11"/>
-      <x:c r="L32" s="11"/>
+      <x:c r="K32" s="16"/>
+      <x:c r="L32" s="16"/>
       <x:c r="M32" s="11"/>
       <x:c r="N32" s="11" t="str">
         <x:v>Verified city - street address pending</x:v>
@@ -1653,8 +1855,8 @@
       <x:c r="J33" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K33" s="11"/>
-      <x:c r="L33" s="11"/>
+      <x:c r="K33" s="16"/>
+      <x:c r="L33" s="16"/>
       <x:c r="M33" s="11"/>
       <x:c r="N33" s="11" t="str">
         <x:v>Verified city - street address pending</x:v>
@@ -1691,8 +1893,8 @@
       <x:c r="J34" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K34" s="11"/>
-      <x:c r="L34" s="11"/>
+      <x:c r="K34" s="16"/>
+      <x:c r="L34" s="16"/>
       <x:c r="M34" s="11"/>
       <x:c r="N34" s="11" t="str">
         <x:v>Verified city - street address pending</x:v>
@@ -1729,8 +1931,8 @@
       <x:c r="J35" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K35" s="11"/>
-      <x:c r="L35" s="11"/>
+      <x:c r="K35" s="16"/>
+      <x:c r="L35" s="16"/>
       <x:c r="M35" s="11"/>
       <x:c r="N35" s="11" t="str">
         <x:v>Verified city - street address pending</x:v>
@@ -1767,8 +1969,8 @@
       <x:c r="J36" s="11" t="str">
         <x:v>Canada</x:v>
       </x:c>
-      <x:c r="K36" s="11"/>
-      <x:c r="L36" s="11"/>
+      <x:c r="K36" s="16"/>
+      <x:c r="L36" s="16"/>
       <x:c r="M36" s="11"/>
       <x:c r="N36" s="11" t="str">
         <x:v>Verified city - street address pending</x:v>
@@ -1805,8 +2007,8 @@
       <x:c r="J37" s="11" t="str">
         <x:v>Canada</x:v>
       </x:c>
-      <x:c r="K37" s="11"/>
-      <x:c r="L37" s="11"/>
+      <x:c r="K37" s="16"/>
+      <x:c r="L37" s="16"/>
       <x:c r="M37" s="11"/>
       <x:c r="N37" s="11" t="str">
         <x:v>Verified city - street address pending</x:v>
@@ -1843,8 +2045,8 @@
       <x:c r="J38" s="11" t="str">
         <x:v>Canada</x:v>
       </x:c>
-      <x:c r="K38" s="11"/>
-      <x:c r="L38" s="11"/>
+      <x:c r="K38" s="16"/>
+      <x:c r="L38" s="16"/>
       <x:c r="M38" s="11"/>
       <x:c r="N38" s="11" t="str">
         <x:v>Verified city - street address pending</x:v>
@@ -1885,8 +2087,8 @@
       <x:c r="J39" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K39" s="11"/>
-      <x:c r="L39" s="11"/>
+      <x:c r="K39" s="16"/>
+      <x:c r="L39" s="16"/>
       <x:c r="M39" s="11"/>
       <x:c r="N39" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -1927,8 +2129,12 @@
       <x:c r="J40" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K40" s="11"/>
-      <x:c r="L40" s="11"/>
+      <x:c r="K40" s="16" t="n">
+        <x:v>40.3198930363</x:v>
+      </x:c>
+      <x:c r="L40" s="16" t="n">
+        <x:v>-79.390939571806</x:v>
+      </x:c>
       <x:c r="M40" s="11"/>
       <x:c r="N40" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -1969,8 +2175,12 @@
       <x:c r="J41" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K41" s="11"/>
-      <x:c r="L41" s="11"/>
+      <x:c r="K41" s="16" t="n">
+        <x:v>35.035040031375</x:v>
+      </x:c>
+      <x:c r="L41" s="16" t="n">
+        <x:v>-89.891493728066</x:v>
+      </x:c>
       <x:c r="M41" s="11"/>
       <x:c r="N41" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -2011,8 +2221,8 @@
       <x:c r="J42" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K42" s="11"/>
-      <x:c r="L42" s="11"/>
+      <x:c r="K42" s="16"/>
+      <x:c r="L42" s="16"/>
       <x:c r="M42" s="11"/>
       <x:c r="N42" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -2049,8 +2259,8 @@
       <x:c r="J43" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K43" s="11"/>
-      <x:c r="L43" s="11"/>
+      <x:c r="K43" s="16"/>
+      <x:c r="L43" s="16"/>
       <x:c r="M43" s="11"/>
       <x:c r="N43" s="11" t="str">
         <x:v>Verified city - official source</x:v>
@@ -2087,8 +2297,8 @@
       <x:c r="J44" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K44" s="11"/>
-      <x:c r="L44" s="11"/>
+      <x:c r="K44" s="16"/>
+      <x:c r="L44" s="16"/>
       <x:c r="M44" s="11"/>
       <x:c r="N44" s="11" t="str">
         <x:v>Verified city - official source</x:v>
@@ -2125,8 +2335,8 @@
       <x:c r="J45" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K45" s="11"/>
-      <x:c r="L45" s="11"/>
+      <x:c r="K45" s="16"/>
+      <x:c r="L45" s="16"/>
       <x:c r="M45" s="11"/>
       <x:c r="N45" s="11" t="str">
         <x:v>Verified city - official source</x:v>
@@ -2163,8 +2373,8 @@
       <x:c r="J46" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K46" s="11"/>
-      <x:c r="L46" s="11"/>
+      <x:c r="K46" s="16"/>
+      <x:c r="L46" s="16"/>
       <x:c r="M46" s="11"/>
       <x:c r="N46" s="11" t="str">
         <x:v>Verified city - official source</x:v>
@@ -2201,8 +2411,8 @@
       <x:c r="J47" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K47" s="11"/>
-      <x:c r="L47" s="11"/>
+      <x:c r="K47" s="16"/>
+      <x:c r="L47" s="16"/>
       <x:c r="M47" s="11"/>
       <x:c r="N47" s="11" t="str">
         <x:v>Verified city - official source</x:v>
@@ -2239,8 +2449,8 @@
       <x:c r="J48" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K48" s="11"/>
-      <x:c r="L48" s="11"/>
+      <x:c r="K48" s="16"/>
+      <x:c r="L48" s="16"/>
       <x:c r="M48" s="11"/>
       <x:c r="N48" s="11" t="str">
         <x:v>Verified city - official source</x:v>
@@ -2277,8 +2487,8 @@
       <x:c r="J49" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K49" s="11"/>
-      <x:c r="L49" s="11"/>
+      <x:c r="K49" s="16"/>
+      <x:c r="L49" s="16"/>
       <x:c r="M49" s="11"/>
       <x:c r="N49" s="11" t="str">
         <x:v>Verified city - official source</x:v>
@@ -2315,8 +2525,8 @@
       <x:c r="J50" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K50" s="11"/>
-      <x:c r="L50" s="11"/>
+      <x:c r="K50" s="16"/>
+      <x:c r="L50" s="16"/>
       <x:c r="M50" s="11"/>
       <x:c r="N50" s="11" t="str">
         <x:v>Verified city - official source</x:v>
@@ -2353,8 +2563,8 @@
       <x:c r="J51" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K51" s="11"/>
-      <x:c r="L51" s="11"/>
+      <x:c r="K51" s="16"/>
+      <x:c r="L51" s="16"/>
       <x:c r="M51" s="11"/>
       <x:c r="N51" s="11" t="str">
         <x:v>Verified city - official source</x:v>
@@ -2393,8 +2603,8 @@
       <x:c r="J52" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K52" s="11"/>
-      <x:c r="L52" s="11"/>
+      <x:c r="K52" s="16"/>
+      <x:c r="L52" s="16"/>
       <x:c r="M52" s="11"/>
       <x:c r="N52" s="11" t="str">
         <x:v>Verified current manufacturing city - official careers source</x:v>
@@ -2433,8 +2643,8 @@
       <x:c r="J53" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K53" s="11"/>
-      <x:c r="L53" s="11"/>
+      <x:c r="K53" s="16"/>
+      <x:c r="L53" s="16"/>
       <x:c r="M53" s="11"/>
       <x:c r="N53" s="11" t="str">
         <x:v>Verified current manufacturing city - official careers source</x:v>
@@ -2473,8 +2683,8 @@
       <x:c r="J54" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K54" s="11"/>
-      <x:c r="L54" s="11"/>
+      <x:c r="K54" s="16"/>
+      <x:c r="L54" s="16"/>
       <x:c r="M54" s="11"/>
       <x:c r="N54" s="11" t="str">
         <x:v>Verified current manufacturing city - official careers source</x:v>
@@ -2513,8 +2723,8 @@
       <x:c r="J55" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K55" s="11"/>
-      <x:c r="L55" s="11"/>
+      <x:c r="K55" s="16"/>
+      <x:c r="L55" s="16"/>
       <x:c r="M55" s="11"/>
       <x:c r="N55" s="11" t="str">
         <x:v>Verified current manufacturing city - official careers source</x:v>
@@ -2553,8 +2763,8 @@
       <x:c r="J56" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K56" s="11"/>
-      <x:c r="L56" s="11"/>
+      <x:c r="K56" s="16"/>
+      <x:c r="L56" s="16"/>
       <x:c r="M56" s="11"/>
       <x:c r="N56" s="11" t="str">
         <x:v>Verified current manufacturing city - official careers source</x:v>
@@ -2593,8 +2803,8 @@
       <x:c r="J57" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K57" s="11"/>
-      <x:c r="L57" s="11"/>
+      <x:c r="K57" s="16"/>
+      <x:c r="L57" s="16"/>
       <x:c r="M57" s="11"/>
       <x:c r="N57" s="11" t="str">
         <x:v>Verified current manufacturing city - official careers source</x:v>
@@ -2633,8 +2843,8 @@
       <x:c r="J58" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K58" s="11"/>
-      <x:c r="L58" s="11"/>
+      <x:c r="K58" s="16"/>
+      <x:c r="L58" s="16"/>
       <x:c r="M58" s="11"/>
       <x:c r="N58" s="11" t="str">
         <x:v>Verified current manufacturing city - official careers source</x:v>
@@ -2673,8 +2883,8 @@
       <x:c r="J59" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K59" s="11"/>
-      <x:c r="L59" s="11"/>
+      <x:c r="K59" s="16"/>
+      <x:c r="L59" s="16"/>
       <x:c r="M59" s="11"/>
       <x:c r="N59" s="11" t="str">
         <x:v>Verified current manufacturing city - official careers source</x:v>
@@ -2713,8 +2923,8 @@
       <x:c r="J60" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K60" s="11"/>
-      <x:c r="L60" s="11"/>
+      <x:c r="K60" s="16"/>
+      <x:c r="L60" s="16"/>
       <x:c r="M60" s="11"/>
       <x:c r="N60" s="11" t="str">
         <x:v>Verified current manufacturing city - official careers source</x:v>
@@ -2753,8 +2963,8 @@
       <x:c r="J61" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K61" s="11"/>
-      <x:c r="L61" s="11"/>
+      <x:c r="K61" s="16"/>
+      <x:c r="L61" s="16"/>
       <x:c r="M61" s="11"/>
       <x:c r="N61" s="11" t="str">
         <x:v>Verified current manufacturing city - official careers source</x:v>
@@ -2793,8 +3003,8 @@
       <x:c r="J62" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K62" s="11"/>
-      <x:c r="L62" s="11"/>
+      <x:c r="K62" s="16"/>
+      <x:c r="L62" s="16"/>
       <x:c r="M62" s="11"/>
       <x:c r="N62" s="11" t="str">
         <x:v>Verified current manufacturing city - official careers source</x:v>
@@ -2833,8 +3043,8 @@
       <x:c r="J63" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K63" s="11"/>
-      <x:c r="L63" s="11"/>
+      <x:c r="K63" s="16"/>
+      <x:c r="L63" s="16"/>
       <x:c r="M63" s="11"/>
       <x:c r="N63" s="11" t="str">
         <x:v>Verified current manufacturing city - official careers source</x:v>
@@ -2871,10 +3081,10 @@
       <x:c r="J64" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K64" s="11" t="n">
+      <x:c r="K64" s="16" t="n">
         <x:v>34.5693083</x:v>
       </x:c>
-      <x:c r="L64" s="11" t="n">
+      <x:c r="L64" s="16" t="n">
         <x:v>-92.585378</x:v>
       </x:c>
       <x:c r="M64" s="11"/>
@@ -2913,10 +3123,10 @@
       <x:c r="J65" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K65" s="11" t="n">
+      <x:c r="K65" s="16" t="n">
         <x:v>42.506348</x:v>
       </x:c>
-      <x:c r="L65" s="11" t="n">
+      <x:c r="L65" s="16" t="n">
         <x:v>-90.6677347</x:v>
       </x:c>
       <x:c r="M65" s="11"/>
@@ -2955,10 +3165,10 @@
       <x:c r="J66" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K66" s="11" t="n">
+      <x:c r="K66" s="16" t="n">
         <x:v>41.6689223</x:v>
       </x:c>
-      <x:c r="L66" s="11" t="n">
+      <x:c r="L66" s="16" t="n">
         <x:v>-87.7386619</x:v>
       </x:c>
       <x:c r="M66" s="11"/>
@@ -2997,10 +3207,10 @@
       <x:c r="J67" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K67" s="11" t="n">
+      <x:c r="K67" s="16" t="n">
         <x:v>41.1200325</x:v>
       </x:c>
-      <x:c r="L67" s="11" t="n">
+      <x:c r="L67" s="16" t="n">
         <x:v>-87.8611531</x:v>
       </x:c>
       <x:c r="M67" s="11"/>
@@ -3039,10 +3249,10 @@
       <x:c r="J68" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K68" s="11" t="n">
+      <x:c r="K68" s="16" t="n">
         <x:v>36.9685219</x:v>
       </x:c>
-      <x:c r="L68" s="11" t="n">
+      <x:c r="L68" s="16" t="n">
         <x:v>-86.4808043</x:v>
       </x:c>
       <x:c r="M68" s="11"/>
@@ -3081,10 +3291,10 @@
       <x:c r="J69" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K69" s="11" t="n">
+      <x:c r="K69" s="16" t="n">
         <x:v>44.2949636</x:v>
       </x:c>
-      <x:c r="L69" s="11" t="n">
+      <x:c r="L69" s="16" t="n">
         <x:v>-93.268827</x:v>
       </x:c>
       <x:c r="M69" s="11"/>
@@ -3123,10 +3333,10 @@
       <x:c r="J70" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K70" s="11" t="n">
+      <x:c r="K70" s="16" t="n">
         <x:v>44.1635775</x:v>
       </x:c>
-      <x:c r="L70" s="11" t="n">
+      <x:c r="L70" s="16" t="n">
         <x:v>-93.9993996</x:v>
       </x:c>
       <x:c r="M70" s="11"/>
@@ -3165,10 +3375,10 @@
       <x:c r="J71" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K71" s="11" t="n">
+      <x:c r="K71" s="16" t="n">
         <x:v>44.0879297</x:v>
       </x:c>
-      <x:c r="L71" s="11" t="n">
+      <x:c r="L71" s="16" t="n">
         <x:v>-93.2260184</x:v>
       </x:c>
       <x:c r="M71" s="11"/>
@@ -3207,10 +3417,10 @@
       <x:c r="J72" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K72" s="11" t="n">
+      <x:c r="K72" s="16" t="n">
         <x:v>42.021741</x:v>
       </x:c>
-      <x:c r="L72" s="11" t="n">
+      <x:c r="L72" s="16" t="n">
         <x:v>-76.3668815</x:v>
       </x:c>
       <x:c r="M72" s="11"/>
@@ -3249,10 +3459,10 @@
       <x:c r="J73" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K73" s="11" t="n">
+      <x:c r="K73" s="16" t="n">
         <x:v>39.7589478</x:v>
       </x:c>
-      <x:c r="L73" s="11" t="n">
+      <x:c r="L73" s="16" t="n">
         <x:v>-84.1916069</x:v>
       </x:c>
       <x:c r="M73" s="11"/>
@@ -3291,10 +3501,10 @@
       <x:c r="J74" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K74" s="11" t="n">
+      <x:c r="K74" s="16" t="n">
         <x:v>39.7136754</x:v>
       </x:c>
-      <x:c r="L74" s="11" t="n">
+      <x:c r="L74" s="16" t="n">
         <x:v>-82.5993294</x:v>
       </x:c>
       <x:c r="M74" s="11"/>
@@ -3333,10 +3543,10 @@
       <x:c r="J75" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K75" s="11" t="n">
+      <x:c r="K75" s="16" t="n">
         <x:v>40.7967244</x:v>
       </x:c>
-      <x:c r="L75" s="11" t="n">
+      <x:c r="L75" s="16" t="n">
         <x:v>-81.5215093</x:v>
       </x:c>
       <x:c r="M75" s="11"/>
@@ -3375,10 +3585,10 @@
       <x:c r="J76" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K76" s="11" t="n">
+      <x:c r="K76" s="16" t="n">
         <x:v>39.7260575</x:v>
       </x:c>
-      <x:c r="L76" s="11" t="n">
+      <x:c r="L76" s="16" t="n">
         <x:v>-82.6700479</x:v>
       </x:c>
       <x:c r="M76" s="11"/>
@@ -3417,10 +3627,10 @@
       <x:c r="J77" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K77" s="11" t="n">
+      <x:c r="K77" s="16" t="n">
         <x:v>40.0178522</x:v>
       </x:c>
-      <x:c r="L77" s="11" t="n">
+      <x:c r="L77" s="16" t="n">
         <x:v>-79.5894828</x:v>
       </x:c>
       <x:c r="M77" s="11"/>
@@ -3459,10 +3669,10 @@
       <x:c r="J78" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K78" s="11" t="n">
+      <x:c r="K78" s="16" t="n">
         <x:v>39.8006553</x:v>
       </x:c>
-      <x:c r="L78" s="11" t="n">
+      <x:c r="L78" s="16" t="n">
         <x:v>-76.9830358</x:v>
       </x:c>
       <x:c r="M78" s="11"/>
@@ -3501,10 +3711,10 @@
       <x:c r="J79" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K79" s="11" t="n">
+      <x:c r="K79" s="16" t="n">
         <x:v>34.6976564</x:v>
       </x:c>
-      <x:c r="L79" s="11" t="n">
+      <x:c r="L79" s="16" t="n">
         <x:v>-79.8833971</x:v>
       </x:c>
       <x:c r="M79" s="11"/>
@@ -3543,8 +3753,8 @@
       <x:c r="J80" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K80" s="11"/>
-      <x:c r="L80" s="11"/>
+      <x:c r="K80" s="16"/>
+      <x:c r="L80" s="16"/>
       <x:c r="M80" s="11"/>
       <x:c r="N80" s="11" t="str">
         <x:v>Verified official location - street address pending</x:v>
@@ -3581,10 +3791,10 @@
       <x:c r="J81" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K81" s="11" t="n">
+      <x:c r="K81" s="16" t="n">
         <x:v>30.3118769</x:v>
       </x:c>
-      <x:c r="L81" s="11" t="n">
+      <x:c r="L81" s="16" t="n">
         <x:v>-95.4560512</x:v>
       </x:c>
       <x:c r="M81" s="11"/>
@@ -3623,10 +3833,10 @@
       <x:c r="J82" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K82" s="11" t="n">
+      <x:c r="K82" s="16" t="n">
         <x:v>29.5692614</x:v>
       </x:c>
-      <x:c r="L82" s="11" t="n">
+      <x:c r="L82" s="16" t="n">
         <x:v>-95.8142885</x:v>
       </x:c>
       <x:c r="M82" s="11"/>
@@ -3665,10 +3875,10 @@
       <x:c r="J83" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K83" s="11" t="n">
+      <x:c r="K83" s="16" t="n">
         <x:v>36.6915</x:v>
       </x:c>
-      <x:c r="L83" s="11" t="n">
+      <x:c r="L83" s="16" t="n">
         <x:v>-79.8725</x:v>
       </x:c>
       <x:c r="M83" s="11"/>
@@ -3707,10 +3917,10 @@
       <x:c r="J84" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K84" s="11" t="n">
+      <x:c r="K84" s="16" t="n">
         <x:v>39.1856597</x:v>
       </x:c>
-      <x:c r="L84" s="11" t="n">
+      <x:c r="L84" s="16" t="n">
         <x:v>-78.1633341</x:v>
       </x:c>
       <x:c r="M84" s="11"/>
@@ -3749,10 +3959,10 @@
       <x:c r="J85" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K85" s="11" t="n">
+      <x:c r="K85" s="16" t="n">
         <x:v>47.0378741</x:v>
       </x:c>
-      <x:c r="L85" s="11" t="n">
+      <x:c r="L85" s="16" t="n">
         <x:v>-122.9006951</x:v>
       </x:c>
       <x:c r="M85" s="11"/>
@@ -3791,10 +4001,10 @@
       <x:c r="J86" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K86" s="11" t="n">
+      <x:c r="K86" s="16" t="n">
         <x:v>43.8137751</x:v>
       </x:c>
-      <x:c r="L86" s="11" t="n">
+      <x:c r="L86" s="16" t="n">
         <x:v>-91.2519017</x:v>
       </x:c>
       <x:c r="M86" s="11"/>
@@ -3833,10 +4043,10 @@
       <x:c r="J87" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K87" s="11" t="n">
+      <x:c r="K87" s="16" t="n">
         <x:v>44.0169014</x:v>
       </x:c>
-      <x:c r="L87" s="11" t="n">
+      <x:c r="L87" s="16" t="n">
         <x:v>-107.9553721</x:v>
       </x:c>
       <x:c r="M87" s="11"/>
@@ -3875,8 +4085,8 @@
       <x:c r="J88" s="11" t="str">
         <x:v>Canada</x:v>
       </x:c>
-      <x:c r="K88" s="11"/>
-      <x:c r="L88" s="11"/>
+      <x:c r="K88" s="16"/>
+      <x:c r="L88" s="16"/>
       <x:c r="M88" s="11"/>
       <x:c r="N88" s="11" t="str">
         <x:v>Verified official location - street address pending</x:v>
@@ -3913,8 +4123,8 @@
       <x:c r="J89" s="11" t="str">
         <x:v>Canada</x:v>
       </x:c>
-      <x:c r="K89" s="11"/>
-      <x:c r="L89" s="11"/>
+      <x:c r="K89" s="16"/>
+      <x:c r="L89" s="16"/>
       <x:c r="M89" s="11"/>
       <x:c r="N89" s="11" t="str">
         <x:v>Verified official location - street address pending</x:v>
@@ -3951,8 +4161,8 @@
       <x:c r="J90" s="11" t="str">
         <x:v>Canada</x:v>
       </x:c>
-      <x:c r="K90" s="11"/>
-      <x:c r="L90" s="11"/>
+      <x:c r="K90" s="16"/>
+      <x:c r="L90" s="16"/>
       <x:c r="M90" s="11"/>
       <x:c r="N90" s="11" t="str">
         <x:v>Verified official location - street address pending</x:v>
@@ -3993,8 +4203,12 @@
       <x:c r="J91" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K91" s="11"/>
-      <x:c r="L91" s="11"/>
+      <x:c r="K91" s="16" t="n">
+        <x:v>42.963901686262</x:v>
+      </x:c>
+      <x:c r="L91" s="16" t="n">
+        <x:v>-76.558305036156</x:v>
+      </x:c>
       <x:c r="M91" s="11"/>
       <x:c r="N91" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -4035,8 +4249,8 @@
       <x:c r="J92" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K92" s="11"/>
-      <x:c r="L92" s="11"/>
+      <x:c r="K92" s="16"/>
+      <x:c r="L92" s="16"/>
       <x:c r="M92" s="11"/>
       <x:c r="N92" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -4077,8 +4291,8 @@
       <x:c r="J93" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K93" s="11"/>
-      <x:c r="L93" s="11"/>
+      <x:c r="K93" s="16"/>
+      <x:c r="L93" s="16"/>
       <x:c r="M93" s="11"/>
       <x:c r="N93" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -4121,8 +4335,8 @@
       <x:c r="J94" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K94" s="11"/>
-      <x:c r="L94" s="11"/>
+      <x:c r="K94" s="16"/>
+      <x:c r="L94" s="16"/>
       <x:c r="M94" s="11"/>
       <x:c r="N94" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -4165,8 +4379,8 @@
       <x:c r="J95" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K95" s="11"/>
-      <x:c r="L95" s="11"/>
+      <x:c r="K95" s="16"/>
+      <x:c r="L95" s="16"/>
       <x:c r="M95" s="11"/>
       <x:c r="N95" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -4209,8 +4423,8 @@
       <x:c r="J96" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K96" s="11"/>
-      <x:c r="L96" s="11"/>
+      <x:c r="K96" s="16"/>
+      <x:c r="L96" s="16"/>
       <x:c r="M96" s="11"/>
       <x:c r="N96" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -4251,8 +4465,8 @@
       <x:c r="J97" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K97" s="11"/>
-      <x:c r="L97" s="11"/>
+      <x:c r="K97" s="16"/>
+      <x:c r="L97" s="16"/>
       <x:c r="M97" s="11"/>
       <x:c r="N97" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -4293,8 +4507,8 @@
       <x:c r="J98" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K98" s="11"/>
-      <x:c r="L98" s="11"/>
+      <x:c r="K98" s="16"/>
+      <x:c r="L98" s="16"/>
       <x:c r="M98" s="11"/>
       <x:c r="N98" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -4335,8 +4549,12 @@
       <x:c r="J99" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K99" s="11"/>
-      <x:c r="L99" s="11"/>
+      <x:c r="K99" s="16" t="n">
+        <x:v>35.769607828434</x:v>
+      </x:c>
+      <x:c r="L99" s="16" t="n">
+        <x:v>-95.340293174686</x:v>
+      </x:c>
       <x:c r="M99" s="11"/>
       <x:c r="N99" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -4377,8 +4595,8 @@
       <x:c r="J100" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K100" s="11"/>
-      <x:c r="L100" s="11"/>
+      <x:c r="K100" s="16"/>
+      <x:c r="L100" s="16"/>
       <x:c r="M100" s="11"/>
       <x:c r="N100" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -4419,8 +4637,8 @@
       <x:c r="J101" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K101" s="11"/>
-      <x:c r="L101" s="11"/>
+      <x:c r="K101" s="16"/>
+      <x:c r="L101" s="16"/>
       <x:c r="M101" s="11"/>
       <x:c r="N101" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -4461,8 +4679,12 @@
       <x:c r="J102" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K102" s="11"/>
-      <x:c r="L102" s="11"/>
+      <x:c r="K102" s="16" t="n">
+        <x:v>40.465205113865</x:v>
+      </x:c>
+      <x:c r="L102" s="16" t="n">
+        <x:v>-104.853246045205</x:v>
+      </x:c>
       <x:c r="M102" s="11"/>
       <x:c r="N102" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -4503,8 +4725,12 @@
       <x:c r="J103" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K103" s="11"/>
-      <x:c r="L103" s="11"/>
+      <x:c r="K103" s="16" t="n">
+        <x:v>35.951031631299</x:v>
+      </x:c>
+      <x:c r="L103" s="16" t="n">
+        <x:v>-80.218941533468</x:v>
+      </x:c>
       <x:c r="M103" s="11"/>
       <x:c r="N103" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -4547,8 +4773,8 @@
       <x:c r="J104" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K104" s="11"/>
-      <x:c r="L104" s="11"/>
+      <x:c r="K104" s="16"/>
+      <x:c r="L104" s="16"/>
       <x:c r="M104" s="11"/>
       <x:c r="N104" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -4589,8 +4815,8 @@
       <x:c r="J105" s="11" t="str">
         <x:v>Canada</x:v>
       </x:c>
-      <x:c r="K105" s="11"/>
-      <x:c r="L105" s="11"/>
+      <x:c r="K105" s="16"/>
+      <x:c r="L105" s="16"/>
       <x:c r="M105" s="11"/>
       <x:c r="N105" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -4631,8 +4857,12 @@
       <x:c r="J106" s="11" t="str">
         <x:v>Canada</x:v>
       </x:c>
-      <x:c r="K106" s="11"/>
-      <x:c r="L106" s="11"/>
+      <x:c r="K106" s="16" t="n">
+        <x:v>45.4743316</x:v>
+      </x:c>
+      <x:c r="L106" s="16" t="n">
+        <x:v>-73.5598886</x:v>
+      </x:c>
       <x:c r="M106" s="11"/>
       <x:c r="N106" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -4669,8 +4899,8 @@
       <x:c r="J107" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K107" s="11"/>
-      <x:c r="L107" s="11"/>
+      <x:c r="K107" s="16"/>
+      <x:c r="L107" s="16"/>
       <x:c r="M107" s="11"/>
       <x:c r="N107" s="11" t="str">
         <x:v>Research starter - exact address pending</x:v>
@@ -4709,8 +4939,8 @@
       <x:c r="J108" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K108" s="11"/>
-      <x:c r="L108" s="11"/>
+      <x:c r="K108" s="16"/>
+      <x:c r="L108" s="16"/>
       <x:c r="M108" s="11"/>
       <x:c r="N108" s="11" t="str">
         <x:v>Research starter - exact address pending</x:v>
@@ -4749,8 +4979,8 @@
       <x:c r="J109" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K109" s="11"/>
-      <x:c r="L109" s="11"/>
+      <x:c r="K109" s="16"/>
+      <x:c r="L109" s="16"/>
       <x:c r="M109" s="11"/>
       <x:c r="N109" s="11" t="str">
         <x:v>Research starter - exact address pending</x:v>
@@ -4789,8 +5019,8 @@
       <x:c r="J110" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K110" s="11"/>
-      <x:c r="L110" s="11"/>
+      <x:c r="K110" s="16"/>
+      <x:c r="L110" s="16"/>
       <x:c r="M110" s="11"/>
       <x:c r="N110" s="11" t="str">
         <x:v>Research starter - exact address pending</x:v>
@@ -4829,8 +5059,8 @@
       <x:c r="J111" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K111" s="11"/>
-      <x:c r="L111" s="11"/>
+      <x:c r="K111" s="16"/>
+      <x:c r="L111" s="16"/>
       <x:c r="M111" s="11"/>
       <x:c r="N111" s="11" t="str">
         <x:v>Research starter - exact address pending</x:v>
@@ -4869,8 +5099,8 @@
       <x:c r="J112" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K112" s="11"/>
-      <x:c r="L112" s="11"/>
+      <x:c r="K112" s="16"/>
+      <x:c r="L112" s="16"/>
       <x:c r="M112" s="11"/>
       <x:c r="N112" s="11" t="str">
         <x:v>Research starter - exact address pending</x:v>
@@ -4909,8 +5139,8 @@
       <x:c r="J113" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K113" s="11"/>
-      <x:c r="L113" s="11"/>
+      <x:c r="K113" s="16"/>
+      <x:c r="L113" s="16"/>
       <x:c r="M113" s="11"/>
       <x:c r="N113" s="11" t="str">
         <x:v>Research starter - exact address pending</x:v>
@@ -4949,8 +5179,8 @@
       <x:c r="J114" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K114" s="11"/>
-      <x:c r="L114" s="11"/>
+      <x:c r="K114" s="16"/>
+      <x:c r="L114" s="16"/>
       <x:c r="M114" s="11"/>
       <x:c r="N114" s="11" t="str">
         <x:v>Research starter - exact address pending</x:v>
@@ -4989,8 +5219,8 @@
       <x:c r="J115" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K115" s="11"/>
-      <x:c r="L115" s="11"/>
+      <x:c r="K115" s="16"/>
+      <x:c r="L115" s="16"/>
       <x:c r="M115" s="11"/>
       <x:c r="N115" s="11" t="str">
         <x:v>Research starter - exact address pending</x:v>
@@ -5029,8 +5259,8 @@
       <x:c r="J116" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K116" s="11"/>
-      <x:c r="L116" s="11"/>
+      <x:c r="K116" s="16"/>
+      <x:c r="L116" s="16"/>
       <x:c r="M116" s="11"/>
       <x:c r="N116" s="11" t="str">
         <x:v>Research starter - exact address pending</x:v>
@@ -5069,8 +5299,8 @@
       <x:c r="J117" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K117" s="11"/>
-      <x:c r="L117" s="11"/>
+      <x:c r="K117" s="16"/>
+      <x:c r="L117" s="16"/>
       <x:c r="M117" s="11"/>
       <x:c r="N117" s="11" t="str">
         <x:v>Verified operating city - not exhaustive</x:v>
@@ -5109,8 +5339,8 @@
       <x:c r="J118" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K118" s="11"/>
-      <x:c r="L118" s="11"/>
+      <x:c r="K118" s="16"/>
+      <x:c r="L118" s="16"/>
       <x:c r="M118" s="11"/>
       <x:c r="N118" s="11" t="str">
         <x:v>Verified operating city - not exhaustive</x:v>
@@ -5149,8 +5379,8 @@
       <x:c r="J119" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K119" s="11"/>
-      <x:c r="L119" s="11"/>
+      <x:c r="K119" s="16"/>
+      <x:c r="L119" s="16"/>
       <x:c r="M119" s="11"/>
       <x:c r="N119" s="11" t="str">
         <x:v>Verified operating city - not exhaustive</x:v>
@@ -5189,8 +5419,8 @@
       <x:c r="J120" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K120" s="11"/>
-      <x:c r="L120" s="11"/>
+      <x:c r="K120" s="16"/>
+      <x:c r="L120" s="16"/>
       <x:c r="M120" s="11"/>
       <x:c r="N120" s="11" t="str">
         <x:v>Verified operating city - not exhaustive</x:v>
@@ -5229,8 +5459,8 @@
       <x:c r="J121" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K121" s="11"/>
-      <x:c r="L121" s="11"/>
+      <x:c r="K121" s="16"/>
+      <x:c r="L121" s="16"/>
       <x:c r="M121" s="11"/>
       <x:c r="N121" s="11" t="str">
         <x:v>Verified operating city - not exhaustive</x:v>
@@ -5269,8 +5499,8 @@
       <x:c r="J122" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K122" s="11"/>
-      <x:c r="L122" s="11"/>
+      <x:c r="K122" s="16"/>
+      <x:c r="L122" s="16"/>
       <x:c r="M122" s="11"/>
       <x:c r="N122" s="11" t="str">
         <x:v>Verified operating city - not exhaustive</x:v>
@@ -5309,8 +5539,8 @@
       <x:c r="J123" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K123" s="11"/>
-      <x:c r="L123" s="11"/>
+      <x:c r="K123" s="16"/>
+      <x:c r="L123" s="16"/>
       <x:c r="M123" s="11"/>
       <x:c r="N123" s="11" t="str">
         <x:v>Verified operating city - not exhaustive</x:v>
@@ -5349,8 +5579,8 @@
       <x:c r="J124" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K124" s="11"/>
-      <x:c r="L124" s="11"/>
+      <x:c r="K124" s="16"/>
+      <x:c r="L124" s="16"/>
       <x:c r="M124" s="11"/>
       <x:c r="N124" s="11" t="str">
         <x:v>Verified operating city - not exhaustive</x:v>
@@ -5389,8 +5619,8 @@
       <x:c r="J125" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K125" s="11"/>
-      <x:c r="L125" s="11"/>
+      <x:c r="K125" s="16"/>
+      <x:c r="L125" s="16"/>
       <x:c r="M125" s="11"/>
       <x:c r="N125" s="11" t="str">
         <x:v>Verified operating city - not exhaustive</x:v>
@@ -5429,8 +5659,8 @@
       <x:c r="J126" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K126" s="11"/>
-      <x:c r="L126" s="11"/>
+      <x:c r="K126" s="16"/>
+      <x:c r="L126" s="16"/>
       <x:c r="M126" s="11"/>
       <x:c r="N126" s="11" t="str">
         <x:v>Research starter - exact address/current status pending</x:v>
@@ -5469,8 +5699,8 @@
       <x:c r="J127" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K127" s="11"/>
-      <x:c r="L127" s="11"/>
+      <x:c r="K127" s="16"/>
+      <x:c r="L127" s="16"/>
       <x:c r="M127" s="11"/>
       <x:c r="N127" s="11" t="str">
         <x:v>Research starter - exact address/current status pending</x:v>
@@ -5509,8 +5739,8 @@
       <x:c r="J128" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K128" s="11"/>
-      <x:c r="L128" s="11"/>
+      <x:c r="K128" s="16"/>
+      <x:c r="L128" s="16"/>
       <x:c r="M128" s="11"/>
       <x:c r="N128" s="11" t="str">
         <x:v>Research starter - exact address/current status pending</x:v>
@@ -5549,8 +5779,8 @@
       <x:c r="J129" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K129" s="11"/>
-      <x:c r="L129" s="11"/>
+      <x:c r="K129" s="16"/>
+      <x:c r="L129" s="16"/>
       <x:c r="M129" s="11"/>
       <x:c r="N129" s="11" t="str">
         <x:v>Research starter - exact address/current status pending</x:v>
@@ -5589,8 +5819,8 @@
       <x:c r="J130" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K130" s="11"/>
-      <x:c r="L130" s="11"/>
+      <x:c r="K130" s="16"/>
+      <x:c r="L130" s="16"/>
       <x:c r="M130" s="11"/>
       <x:c r="N130" s="11" t="str">
         <x:v>Research starter - exact address/current status pending</x:v>
@@ -5633,8 +5863,12 @@
       <x:c r="J131" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K131" s="11"/>
-      <x:c r="L131" s="11"/>
+      <x:c r="K131" s="16" t="n">
+        <x:v>40.848900744615</x:v>
+      </x:c>
+      <x:c r="L131" s="16" t="n">
+        <x:v>-82.345641129846</x:v>
+      </x:c>
       <x:c r="M131" s="11"/>
       <x:c r="N131" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -5675,8 +5909,12 @@
       <x:c r="J132" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K132" s="11"/>
-      <x:c r="L132" s="11"/>
+      <x:c r="K132" s="16" t="n">
+        <x:v>30.472142008041</x:v>
+      </x:c>
+      <x:c r="L132" s="16" t="n">
+        <x:v>-97.675659137185</x:v>
+      </x:c>
       <x:c r="M132" s="11"/>
       <x:c r="N132" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -5717,8 +5955,12 @@
       <x:c r="J133" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K133" s="11"/>
-      <x:c r="L133" s="11"/>
+      <x:c r="K133" s="16" t="n">
+        <x:v>42.504639821829</x:v>
+      </x:c>
+      <x:c r="L133" s="16" t="n">
+        <x:v>-88.975543452539</x:v>
+      </x:c>
       <x:c r="M133" s="11"/>
       <x:c r="N133" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -5759,8 +6001,12 @@
       <x:c r="J134" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K134" s="11"/>
-      <x:c r="L134" s="11"/>
+      <x:c r="K134" s="16" t="n">
+        <x:v>41.867388326692</x:v>
+      </x:c>
+      <x:c r="L134" s="16" t="n">
+        <x:v>-72.719681198554</x:v>
+      </x:c>
       <x:c r="M134" s="11"/>
       <x:c r="N134" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -5801,8 +6047,12 @@
       <x:c r="J135" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K135" s="11"/>
-      <x:c r="L135" s="11"/>
+      <x:c r="K135" s="16" t="n">
+        <x:v>35.120940732713</x:v>
+      </x:c>
+      <x:c r="L135" s="16" t="n">
+        <x:v>-80.880457827941</x:v>
+      </x:c>
       <x:c r="M135" s="11"/>
       <x:c r="N135" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -5843,8 +6093,12 @@
       <x:c r="J136" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K136" s="11"/>
-      <x:c r="L136" s="11"/>
+      <x:c r="K136" s="16" t="n">
+        <x:v>40.226516942759</x:v>
+      </x:c>
+      <x:c r="L136" s="16" t="n">
+        <x:v>-76.091321129227</x:v>
+      </x:c>
       <x:c r="M136" s="11"/>
       <x:c r="N136" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -5885,8 +6139,8 @@
       <x:c r="J137" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K137" s="11"/>
-      <x:c r="L137" s="11"/>
+      <x:c r="K137" s="16"/>
+      <x:c r="L137" s="16"/>
       <x:c r="M137" s="11"/>
       <x:c r="N137" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -5927,8 +6181,12 @@
       <x:c r="J138" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K138" s="11"/>
-      <x:c r="L138" s="11"/>
+      <x:c r="K138" s="16" t="n">
+        <x:v>41.794360669007</x:v>
+      </x:c>
+      <x:c r="L138" s="16" t="n">
+        <x:v>-87.988353210431</x:v>
+      </x:c>
       <x:c r="M138" s="11"/>
       <x:c r="N138" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -5969,8 +6227,12 @@
       <x:c r="J139" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K139" s="11"/>
-      <x:c r="L139" s="11"/>
+      <x:c r="K139" s="16" t="n">
+        <x:v>40.002251777094</x:v>
+      </x:c>
+      <x:c r="L139" s="16" t="n">
+        <x:v>-75.690374635441</x:v>
+      </x:c>
       <x:c r="M139" s="11"/>
       <x:c r="N139" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -6011,8 +6273,12 @@
       <x:c r="J140" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K140" s="11"/>
-      <x:c r="L140" s="11"/>
+      <x:c r="K140" s="16" t="n">
+        <x:v>42.860417137066</x:v>
+      </x:c>
+      <x:c r="L140" s="16" t="n">
+        <x:v>-87.980066568531</x:v>
+      </x:c>
       <x:c r="M140" s="11"/>
       <x:c r="N140" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -6053,8 +6319,12 @@
       <x:c r="J141" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K141" s="11"/>
-      <x:c r="L141" s="11"/>
+      <x:c r="K141" s="16" t="n">
+        <x:v>33.453774403395</x:v>
+      </x:c>
+      <x:c r="L141" s="16" t="n">
+        <x:v>-112.375377418495</x:v>
+      </x:c>
       <x:c r="M141" s="11"/>
       <x:c r="N141" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -6095,8 +6365,12 @@
       <x:c r="J142" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K142" s="11"/>
-      <x:c r="L142" s="11"/>
+      <x:c r="K142" s="16" t="n">
+        <x:v>39.805195980164</x:v>
+      </x:c>
+      <x:c r="L142" s="16" t="n">
+        <x:v>-76.949864474168</x:v>
+      </x:c>
       <x:c r="M142" s="11"/>
       <x:c r="N142" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -6137,8 +6411,12 @@
       <x:c r="J143" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K143" s="11"/>
-      <x:c r="L143" s="11"/>
+      <x:c r="K143" s="16" t="n">
+        <x:v>41.680413452977</x:v>
+      </x:c>
+      <x:c r="L143" s="16" t="n">
+        <x:v>-70.295267597434</x:v>
+      </x:c>
       <x:c r="M143" s="11"/>
       <x:c r="N143" s="11" t="str">
         <x:v>Closure announced - verify active status</x:v>
@@ -6181,8 +6459,12 @@
       <x:c r="J144" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K144" s="11"/>
-      <x:c r="L144" s="11"/>
+      <x:c r="K144" s="16" t="n">
+        <x:v>38.290396498517</x:v>
+      </x:c>
+      <x:c r="L144" s="16" t="n">
+        <x:v>-85.748615157282</x:v>
+      </x:c>
       <x:c r="M144" s="11"/>
       <x:c r="N144" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -6223,8 +6505,12 @@
       <x:c r="J145" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K145" s="11"/>
-      <x:c r="L145" s="11"/>
+      <x:c r="K145" s="16" t="n">
+        <x:v>28.071712061744</x:v>
+      </x:c>
+      <x:c r="L145" s="16" t="n">
+        <x:v>-81.979100027709</x:v>
+      </x:c>
       <x:c r="M145" s="11"/>
       <x:c r="N145" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -6265,8 +6551,8 @@
       <x:c r="J146" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K146" s="11"/>
-      <x:c r="L146" s="11"/>
+      <x:c r="K146" s="16"/>
+      <x:c r="L146" s="16"/>
       <x:c r="M146" s="11"/>
       <x:c r="N146" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -6307,8 +6593,12 @@
       <x:c r="J147" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K147" s="11"/>
-      <x:c r="L147" s="11"/>
+      <x:c r="K147" s="16" t="n">
+        <x:v>42.952027277345</x:v>
+      </x:c>
+      <x:c r="L147" s="16" t="n">
+        <x:v>-87.917887377379</x:v>
+      </x:c>
       <x:c r="M147" s="11"/>
       <x:c r="N147" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -6349,8 +6639,8 @@
       <x:c r="J148" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K148" s="11"/>
-      <x:c r="L148" s="11"/>
+      <x:c r="K148" s="16"/>
+      <x:c r="L148" s="16"/>
       <x:c r="M148" s="11"/>
       <x:c r="N148" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -6391,8 +6681,8 @@
       <x:c r="J149" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K149" s="11"/>
-      <x:c r="L149" s="11"/>
+      <x:c r="K149" s="16"/>
+      <x:c r="L149" s="16"/>
       <x:c r="M149" s="11"/>
       <x:c r="N149" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -6435,8 +6725,8 @@
       <x:c r="J150" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K150" s="11"/>
-      <x:c r="L150" s="11"/>
+      <x:c r="K150" s="16"/>
+      <x:c r="L150" s="16"/>
       <x:c r="M150" s="11"/>
       <x:c r="N150" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -6477,8 +6767,12 @@
       <x:c r="J151" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K151" s="11"/>
-      <x:c r="L151" s="11"/>
+      <x:c r="K151" s="16" t="n">
+        <x:v>44.925419345579</x:v>
+      </x:c>
+      <x:c r="L151" s="16" t="n">
+        <x:v>-122.996499918632</x:v>
+      </x:c>
       <x:c r="M151" s="11"/>
       <x:c r="N151" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -6519,8 +6813,12 @@
       <x:c r="J152" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K152" s="11"/>
-      <x:c r="L152" s="11"/>
+      <x:c r="K152" s="16" t="n">
+        <x:v>37.909031224077</x:v>
+      </x:c>
+      <x:c r="L152" s="16" t="n">
+        <x:v>-121.265741196652</x:v>
+      </x:c>
       <x:c r="M152" s="11"/>
       <x:c r="N152" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -6561,8 +6859,12 @@
       <x:c r="J153" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K153" s="11"/>
-      <x:c r="L153" s="11"/>
+      <x:c r="K153" s="16" t="n">
+        <x:v>45.378949659524</x:v>
+      </x:c>
+      <x:c r="L153" s="16" t="n">
+        <x:v>-122.778445775909</x:v>
+      </x:c>
       <x:c r="M153" s="11"/>
       <x:c r="N153" s="11" t="str">
         <x:v>Closure announced - verify active status</x:v>
@@ -6605,8 +6907,8 @@
       <x:c r="J154" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K154" s="11"/>
-      <x:c r="L154" s="11"/>
+      <x:c r="K154" s="16"/>
+      <x:c r="L154" s="16"/>
       <x:c r="M154" s="11"/>
       <x:c r="N154" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -6647,8 +6949,12 @@
       <x:c r="J155" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K155" s="11"/>
-      <x:c r="L155" s="11"/>
+      <x:c r="K155" s="16" t="n">
+        <x:v>39.886450841515</x:v>
+      </x:c>
+      <x:c r="L155" s="16" t="n">
+        <x:v>-86.243193231866</x:v>
+      </x:c>
       <x:c r="M155" s="11"/>
       <x:c r="N155" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -6691,8 +6997,12 @@
       <x:c r="J156" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K156" s="11"/>
-      <x:c r="L156" s="11"/>
+      <x:c r="K156" s="16" t="n">
+        <x:v>39.867659407713</x:v>
+      </x:c>
+      <x:c r="L156" s="16" t="n">
+        <x:v>-86.233148883516</x:v>
+      </x:c>
       <x:c r="M156" s="11"/>
       <x:c r="N156" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -6735,8 +7045,12 @@
       <x:c r="J157" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K157" s="11"/>
-      <x:c r="L157" s="11"/>
+      <x:c r="K157" s="16" t="n">
+        <x:v>38.301513149477</x:v>
+      </x:c>
+      <x:c r="L157" s="16" t="n">
+        <x:v>-85.515622474404</x:v>
+      </x:c>
       <x:c r="M157" s="11"/>
       <x:c r="N157" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -6779,8 +7093,12 @@
       <x:c r="J158" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K158" s="11"/>
-      <x:c r="L158" s="11"/>
+      <x:c r="K158" s="16" t="n">
+        <x:v>40.021959901777</x:v>
+      </x:c>
+      <x:c r="L158" s="16" t="n">
+        <x:v>-84.191309434671</x:v>
+      </x:c>
       <x:c r="M158" s="11"/>
       <x:c r="N158" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -6819,8 +7137,8 @@
       <x:c r="J159" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K159" s="11"/>
-      <x:c r="L159" s="11"/>
+      <x:c r="K159" s="16"/>
+      <x:c r="L159" s="16"/>
       <x:c r="M159" s="11"/>
       <x:c r="N159" s="11" t="str">
         <x:v>Research starter - exact address pending</x:v>
@@ -6859,8 +7177,8 @@
       <x:c r="J160" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K160" s="11"/>
-      <x:c r="L160" s="11"/>
+      <x:c r="K160" s="16"/>
+      <x:c r="L160" s="16"/>
       <x:c r="M160" s="11"/>
       <x:c r="N160" s="11" t="str">
         <x:v>Research starter - exact address pending</x:v>
@@ -6899,8 +7217,8 @@
       <x:c r="J161" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K161" s="11"/>
-      <x:c r="L161" s="11"/>
+      <x:c r="K161" s="16"/>
+      <x:c r="L161" s="16"/>
       <x:c r="M161" s="11"/>
       <x:c r="N161" s="11" t="str">
         <x:v>Research starter - exact address pending</x:v>
@@ -6939,8 +7257,8 @@
       <x:c r="J162" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K162" s="11"/>
-      <x:c r="L162" s="11"/>
+      <x:c r="K162" s="16"/>
+      <x:c r="L162" s="16"/>
       <x:c r="M162" s="11"/>
       <x:c r="N162" s="11" t="str">
         <x:v>Research starter - exact address pending</x:v>
@@ -6979,8 +7297,8 @@
       <x:c r="J163" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K163" s="11"/>
-      <x:c r="L163" s="11"/>
+      <x:c r="K163" s="16"/>
+      <x:c r="L163" s="16"/>
       <x:c r="M163" s="11"/>
       <x:c r="N163" s="11" t="str">
         <x:v>Research starter - exact address pending</x:v>
@@ -7019,8 +7337,8 @@
       <x:c r="J164" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K164" s="11"/>
-      <x:c r="L164" s="11"/>
+      <x:c r="K164" s="16"/>
+      <x:c r="L164" s="16"/>
       <x:c r="M164" s="11"/>
       <x:c r="N164" s="11" t="str">
         <x:v>Research starter - exact address pending</x:v>
@@ -7059,8 +7377,8 @@
       <x:c r="J165" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K165" s="11"/>
-      <x:c r="L165" s="11"/>
+      <x:c r="K165" s="16"/>
+      <x:c r="L165" s="16"/>
       <x:c r="M165" s="11"/>
       <x:c r="N165" s="11" t="str">
         <x:v>Research starter - exact address pending</x:v>
@@ -7099,8 +7417,8 @@
       <x:c r="J166" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K166" s="11"/>
-      <x:c r="L166" s="11"/>
+      <x:c r="K166" s="16"/>
+      <x:c r="L166" s="16"/>
       <x:c r="M166" s="11"/>
       <x:c r="N166" s="11" t="str">
         <x:v>Research starter - exact address pending</x:v>
@@ -7143,8 +7461,12 @@
       <x:c r="J167" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K167" s="11"/>
-      <x:c r="L167" s="11"/>
+      <x:c r="K167" s="16" t="n">
+        <x:v>38.012271849789</x:v>
+      </x:c>
+      <x:c r="L167" s="16" t="n">
+        <x:v>-121.773009979934</x:v>
+      </x:c>
       <x:c r="M167" s="11"/>
       <x:c r="N167" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -7185,8 +7507,12 @@
       <x:c r="J168" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K168" s="11"/>
-      <x:c r="L168" s="11"/>
+      <x:c r="K168" s="16" t="n">
+        <x:v>37.638159145048</x:v>
+      </x:c>
+      <x:c r="L168" s="16" t="n">
+        <x:v>-120.91751363924</x:v>
+      </x:c>
       <x:c r="M168" s="11"/>
       <x:c r="N168" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -7227,8 +7553,12 @@
       <x:c r="J169" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K169" s="11"/>
-      <x:c r="L169" s="11"/>
+      <x:c r="K169" s="16" t="n">
+        <x:v>37.633199575779</x:v>
+      </x:c>
+      <x:c r="L169" s="16" t="n">
+        <x:v>-120.951063172415</x:v>
+      </x:c>
       <x:c r="M169" s="11"/>
       <x:c r="N169" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -7269,8 +7599,12 @@
       <x:c r="J170" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K170" s="11"/>
-      <x:c r="L170" s="11"/>
+      <x:c r="K170" s="16" t="n">
+        <x:v>37.631335326094</x:v>
+      </x:c>
+      <x:c r="L170" s="16" t="n">
+        <x:v>-120.948058283457</x:v>
+      </x:c>
       <x:c r="M170" s="11"/>
       <x:c r="N170" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -7311,8 +7645,12 @@
       <x:c r="J171" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K171" s="11"/>
-      <x:c r="L171" s="11"/>
+      <x:c r="K171" s="16" t="n">
+        <x:v>37.732649074883</x:v>
+      </x:c>
+      <x:c r="L171" s="16" t="n">
+        <x:v>-120.936436790125</x:v>
+      </x:c>
       <x:c r="M171" s="11"/>
       <x:c r="N171" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -7353,8 +7691,12 @@
       <x:c r="J172" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K172" s="11"/>
-      <x:c r="L172" s="11"/>
+      <x:c r="K172" s="16" t="n">
+        <x:v>38.515220963097</x:v>
+      </x:c>
+      <x:c r="L172" s="16" t="n">
+        <x:v>-121.468936190813</x:v>
+      </x:c>
       <x:c r="M172" s="11"/>
       <x:c r="N172" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -7395,8 +7737,12 @@
       <x:c r="J173" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K173" s="11"/>
-      <x:c r="L173" s="11"/>
+      <x:c r="K173" s="16" t="n">
+        <x:v>40.467333675489</x:v>
+      </x:c>
+      <x:c r="L173" s="16" t="n">
+        <x:v>-87.674032097045</x:v>
+      </x:c>
       <x:c r="M173" s="11"/>
       <x:c r="N173" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -7437,8 +7783,12 @@
       <x:c r="J174" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K174" s="11"/>
-      <x:c r="L174" s="11"/>
+      <x:c r="K174" s="16" t="n">
+        <x:v>41.922957492626</x:v>
+      </x:c>
+      <x:c r="L174" s="16" t="n">
+        <x:v>-89.078526179768</x:v>
+      </x:c>
       <x:c r="M174" s="11"/>
       <x:c r="N174" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -7479,8 +7829,12 @@
       <x:c r="J175" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K175" s="11"/>
-      <x:c r="L175" s="11"/>
+      <x:c r="K175" s="16" t="n">
+        <x:v>41.595715591562</x:v>
+      </x:c>
+      <x:c r="L175" s="16" t="n">
+        <x:v>-87.469640695344</x:v>
+      </x:c>
       <x:c r="M175" s="11"/>
       <x:c r="N175" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -7521,8 +7875,12 @@
       <x:c r="J176" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K176" s="11"/>
-      <x:c r="L176" s="11"/>
+      <x:c r="K176" s="16" t="n">
+        <x:v>40.806241826191</x:v>
+      </x:c>
+      <x:c r="L176" s="16" t="n">
+        <x:v>-91.150521906022</x:v>
+      </x:c>
       <x:c r="M176" s="11"/>
       <x:c r="N176" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -7563,8 +7921,12 @@
       <x:c r="J177" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K177" s="11"/>
-      <x:c r="L177" s="11"/>
+      <x:c r="K177" s="16" t="n">
+        <x:v>42.49933014244</x:v>
+      </x:c>
+      <x:c r="L177" s="16" t="n">
+        <x:v>-94.134456662006</x:v>
+      </x:c>
       <x:c r="M177" s="11"/>
       <x:c r="N177" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -7605,8 +7967,12 @@
       <x:c r="J178" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K178" s="11"/>
-      <x:c r="L178" s="11"/>
+      <x:c r="K178" s="16" t="n">
+        <x:v>40.620293449949</x:v>
+      </x:c>
+      <x:c r="L178" s="16" t="n">
+        <x:v>-91.40652494444</x:v>
+      </x:c>
       <x:c r="M178" s="11"/>
       <x:c r="N178" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -7647,8 +8013,8 @@
       <x:c r="J179" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K179" s="11"/>
-      <x:c r="L179" s="11"/>
+      <x:c r="K179" s="16"/>
+      <x:c r="L179" s="16"/>
       <x:c r="M179" s="11"/>
       <x:c r="N179" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -7689,8 +8055,12 @@
       <x:c r="J180" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K180" s="11"/>
-      <x:c r="L180" s="11"/>
+      <x:c r="K180" s="16" t="n">
+        <x:v>39.719488232498</x:v>
+      </x:c>
+      <x:c r="L180" s="16" t="n">
+        <x:v>-94.891673371689</x:v>
+      </x:c>
       <x:c r="M180" s="11"/>
       <x:c r="N180" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -7731,8 +8101,12 @@
       <x:c r="J181" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K181" s="11"/>
-      <x:c r="L181" s="11"/>
+      <x:c r="K181" s="16" t="n">
+        <x:v>40.538764208225</x:v>
+      </x:c>
+      <x:c r="L181" s="16" t="n">
+        <x:v>-74.386500483653</x:v>
+      </x:c>
       <x:c r="M181" s="11"/>
       <x:c r="N181" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -7773,8 +8147,8 @@
       <x:c r="J182" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K182" s="11"/>
-      <x:c r="L182" s="11"/>
+      <x:c r="K182" s="16"/>
+      <x:c r="L182" s="16"/>
       <x:c r="M182" s="11"/>
       <x:c r="N182" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -7815,8 +8189,8 @@
       <x:c r="J183" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K183" s="11"/>
-      <x:c r="L183" s="11"/>
+      <x:c r="K183" s="16"/>
+      <x:c r="L183" s="16"/>
       <x:c r="M183" s="11"/>
       <x:c r="N183" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -7857,8 +8231,12 @@
       <x:c r="J184" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K184" s="11"/>
-      <x:c r="L184" s="11"/>
+      <x:c r="K184" s="16" t="n">
+        <x:v>40.561909617146</x:v>
+      </x:c>
+      <x:c r="L184" s="16" t="n">
+        <x:v>-75.622014590773</x:v>
+      </x:c>
       <x:c r="M184" s="11"/>
       <x:c r="N184" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -7899,8 +8277,12 @@
       <x:c r="J185" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K185" s="11"/>
-      <x:c r="L185" s="11"/>
+      <x:c r="K185" s="16" t="n">
+        <x:v>34.730415226934</x:v>
+      </x:c>
+      <x:c r="L185" s="16" t="n">
+        <x:v>-80.739115519923</x:v>
+      </x:c>
       <x:c r="M185" s="11"/>
       <x:c r="N185" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -7941,8 +8323,12 @@
       <x:c r="J186" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K186" s="11"/>
-      <x:c r="L186" s="11"/>
+      <x:c r="K186" s="16" t="n">
+        <x:v>35.958112955221</x:v>
+      </x:c>
+      <x:c r="L186" s="16" t="n">
+        <x:v>-88.949697558312</x:v>
+      </x:c>
       <x:c r="M186" s="11"/>
       <x:c r="N186" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -7983,8 +8369,8 @@
       <x:c r="J187" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K187" s="11"/>
-      <x:c r="L187" s="11"/>
+      <x:c r="K187" s="16"/>
+      <x:c r="L187" s="16"/>
       <x:c r="M187" s="11"/>
       <x:c r="N187" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -8025,8 +8411,12 @@
       <x:c r="J188" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K188" s="11"/>
-      <x:c r="L188" s="11"/>
+      <x:c r="K188" s="16" t="n">
+        <x:v>46.372598423788</x:v>
+      </x:c>
+      <x:c r="L188" s="16" t="n">
+        <x:v>-120.305009300056</x:v>
+      </x:c>
       <x:c r="M188" s="11"/>
       <x:c r="N188" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -8067,8 +8457,8 @@
       <x:c r="J189" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K189" s="11"/>
-      <x:c r="L189" s="11"/>
+      <x:c r="K189" s="16"/>
+      <x:c r="L189" s="16"/>
       <x:c r="M189" s="11"/>
       <x:c r="N189" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -8109,8 +8499,12 @@
       <x:c r="J190" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K190" s="11"/>
-      <x:c r="L190" s="11"/>
+      <x:c r="K190" s="16" t="n">
+        <x:v>43.182464659512</x:v>
+      </x:c>
+      <x:c r="L190" s="16" t="n">
+        <x:v>-88.086324071593</x:v>
+      </x:c>
       <x:c r="M190" s="11"/>
       <x:c r="N190" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -8151,8 +8545,8 @@
       <x:c r="J191" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K191" s="11"/>
-      <x:c r="L191" s="11"/>
+      <x:c r="K191" s="16"/>
+      <x:c r="L191" s="16"/>
       <x:c r="M191" s="11"/>
       <x:c r="N191" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -8193,8 +8587,12 @@
       <x:c r="J192" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K192" s="11"/>
-      <x:c r="L192" s="11"/>
+      <x:c r="K192" s="16" t="n">
+        <x:v>43.10992865381</x:v>
+      </x:c>
+      <x:c r="L192" s="16" t="n">
+        <x:v>-88.508444973968</x:v>
+      </x:c>
       <x:c r="M192" s="11"/>
       <x:c r="N192" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -8235,8 +8633,12 @@
       <x:c r="J193" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K193" s="11"/>
-      <x:c r="L193" s="11"/>
+      <x:c r="K193" s="16" t="n">
+        <x:v>44.454028132157</x:v>
+      </x:c>
+      <x:c r="L193" s="16" t="n">
+        <x:v>-89.509434176761</x:v>
+      </x:c>
       <x:c r="M193" s="11"/>
       <x:c r="N193" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -8277,8 +8679,8 @@
       <x:c r="J194" s="11" t="str">
         <x:v>Puerto Rico</x:v>
       </x:c>
-      <x:c r="K194" s="11"/>
-      <x:c r="L194" s="11"/>
+      <x:c r="K194" s="16"/>
+      <x:c r="L194" s="16"/>
       <x:c r="M194" s="11"/>
       <x:c r="N194" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -8315,8 +8717,8 @@
       <x:c r="J195" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K195" s="11"/>
-      <x:c r="L195" s="11"/>
+      <x:c r="K195" s="16"/>
+      <x:c r="L195" s="16"/>
       <x:c r="M195" s="11"/>
       <x:c r="N195" s="11" t="str">
         <x:v>Research starter - exact address pending</x:v>
@@ -8355,8 +8757,8 @@
       <x:c r="J196" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K196" s="11"/>
-      <x:c r="L196" s="11"/>
+      <x:c r="K196" s="16"/>
+      <x:c r="L196" s="16"/>
       <x:c r="M196" s="11"/>
       <x:c r="N196" s="11" t="str">
         <x:v>Research starter - exact address pending</x:v>
@@ -8395,8 +8797,8 @@
       <x:c r="J197" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K197" s="11"/>
-      <x:c r="L197" s="11"/>
+      <x:c r="K197" s="16"/>
+      <x:c r="L197" s="16"/>
       <x:c r="M197" s="11"/>
       <x:c r="N197" s="11" t="str">
         <x:v>Research starter - exact address pending</x:v>
@@ -8435,8 +8837,8 @@
       <x:c r="J198" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K198" s="11"/>
-      <x:c r="L198" s="11"/>
+      <x:c r="K198" s="16"/>
+      <x:c r="L198" s="16"/>
       <x:c r="M198" s="11"/>
       <x:c r="N198" s="11" t="str">
         <x:v>Research starter - exact address pending</x:v>
@@ -8475,8 +8877,8 @@
       <x:c r="J199" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K199" s="11"/>
-      <x:c r="L199" s="11"/>
+      <x:c r="K199" s="16"/>
+      <x:c r="L199" s="16"/>
       <x:c r="M199" s="11"/>
       <x:c r="N199" s="11" t="str">
         <x:v>Research starter - exact address pending</x:v>
@@ -8515,8 +8917,8 @@
       <x:c r="J200" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K200" s="11"/>
-      <x:c r="L200" s="11"/>
+      <x:c r="K200" s="16"/>
+      <x:c r="L200" s="16"/>
       <x:c r="M200" s="11"/>
       <x:c r="N200" s="11" t="str">
         <x:v>Research starter - exact address pending</x:v>
@@ -8555,8 +8957,8 @@
       <x:c r="J201" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K201" s="11"/>
-      <x:c r="L201" s="11"/>
+      <x:c r="K201" s="16"/>
+      <x:c r="L201" s="16"/>
       <x:c r="M201" s="11"/>
       <x:c r="N201" s="11" t="str">
         <x:v>Research starter - exact address pending</x:v>
@@ -8595,8 +8997,8 @@
       <x:c r="J202" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K202" s="11"/>
-      <x:c r="L202" s="11"/>
+      <x:c r="K202" s="16"/>
+      <x:c r="L202" s="16"/>
       <x:c r="M202" s="11"/>
       <x:c r="N202" s="11" t="str">
         <x:v>Research starter - exact address pending</x:v>
@@ -8639,8 +9041,12 @@
       <x:c r="J203" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K203" s="11"/>
-      <x:c r="L203" s="11"/>
+      <x:c r="K203" s="16" t="n">
+        <x:v>33.624722449366</x:v>
+      </x:c>
+      <x:c r="L203" s="16" t="n">
+        <x:v>-84.462973711541</x:v>
+      </x:c>
       <x:c r="M203" s="11" t="str"/>
       <x:c r="N203" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -8683,8 +9089,12 @@
       <x:c r="J204" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K204" s="11"/>
-      <x:c r="L204" s="11"/>
+      <x:c r="K204" s="16" t="n">
+        <x:v>33.975894624451</x:v>
+      </x:c>
+      <x:c r="L204" s="16" t="n">
+        <x:v>-84.543731230241</x:v>
+      </x:c>
       <x:c r="M204" s="11" t="str"/>
       <x:c r="N204" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -8727,8 +9137,12 @@
       <x:c r="J205" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K205" s="11"/>
-      <x:c r="L205" s="11"/>
+      <x:c r="K205" s="16" t="n">
+        <x:v>35.135719790595</x:v>
+      </x:c>
+      <x:c r="L205" s="16" t="n">
+        <x:v>-84.901570586369</x:v>
+      </x:c>
       <x:c r="M205" s="11" t="str"/>
       <x:c r="N205" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -8771,8 +9185,12 @@
       <x:c r="J206" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K206" s="11"/>
-      <x:c r="L206" s="11"/>
+      <x:c r="K206" s="16" t="n">
+        <x:v>32.294051654652</x:v>
+      </x:c>
+      <x:c r="L206" s="16" t="n">
+        <x:v>-86.349604031051</x:v>
+      </x:c>
       <x:c r="M206" s="11" t="str"/>
       <x:c r="N206" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -8815,8 +9233,12 @@
       <x:c r="J207" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K207" s="11"/>
-      <x:c r="L207" s="11"/>
+      <x:c r="K207" s="16" t="n">
+        <x:v>35.094099308181</x:v>
+      </x:c>
+      <x:c r="L207" s="16" t="n">
+        <x:v>-85.252327175746</x:v>
+      </x:c>
       <x:c r="M207" s="11" t="str"/>
       <x:c r="N207" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -8859,8 +9281,12 @@
       <x:c r="J208" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K208" s="11"/>
-      <x:c r="L208" s="11"/>
+      <x:c r="K208" s="16" t="n">
+        <x:v>29.965223369901</x:v>
+      </x:c>
+      <x:c r="L208" s="16" t="n">
+        <x:v>-90.195049054852</x:v>
+      </x:c>
       <x:c r="M208" s="11" t="str"/>
       <x:c r="N208" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -8903,8 +9329,12 @@
       <x:c r="J209" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K209" s="11"/>
-      <x:c r="L209" s="11"/>
+      <x:c r="K209" s="16" t="n">
+        <x:v>30.585934358966</x:v>
+      </x:c>
+      <x:c r="L209" s="16" t="n">
+        <x:v>-88.169731883499</x:v>
+      </x:c>
       <x:c r="M209" s="11" t="str"/>
       <x:c r="N209" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -8947,8 +9377,12 @@
       <x:c r="J210" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K210" s="11"/>
-      <x:c r="L210" s="11"/>
+      <x:c r="K210" s="16" t="n">
+        <x:v>30.542053062517</x:v>
+      </x:c>
+      <x:c r="L210" s="16" t="n">
+        <x:v>-91.136149247209</x:v>
+      </x:c>
       <x:c r="M210" s="11" t="str"/>
       <x:c r="N210" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -8991,8 +9425,12 @@
       <x:c r="J211" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K211" s="11"/>
-      <x:c r="L211" s="11"/>
+      <x:c r="K211" s="16" t="n">
+        <x:v>40.721972217093</x:v>
+      </x:c>
+      <x:c r="L211" s="16" t="n">
+        <x:v>-111.969155771441</x:v>
+      </x:c>
       <x:c r="M211" s="11" t="str"/>
       <x:c r="N211" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -9035,8 +9473,8 @@
       <x:c r="J212" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K212" s="11"/>
-      <x:c r="L212" s="11"/>
+      <x:c r="K212" s="16"/>
+      <x:c r="L212" s="16"/>
       <x:c r="M212" s="11" t="str"/>
       <x:c r="N212" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -9079,8 +9517,12 @@
       <x:c r="J213" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K213" s="11"/>
-      <x:c r="L213" s="11"/>
+      <x:c r="K213" s="16" t="n">
+        <x:v>39.77294987022</x:v>
+      </x:c>
+      <x:c r="L213" s="16" t="n">
+        <x:v>-104.963003612365</x:v>
+      </x:c>
       <x:c r="M213" s="11" t="str"/>
       <x:c r="N213" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -9123,8 +9565,12 @@
       <x:c r="J214" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K214" s="11"/>
-      <x:c r="L214" s="11"/>
+      <x:c r="K214" s="16" t="n">
+        <x:v>45.303907902297</x:v>
+      </x:c>
+      <x:c r="L214" s="16" t="n">
+        <x:v>-122.777902081981</x:v>
+      </x:c>
       <x:c r="M214" s="11" t="str"/>
       <x:c r="N214" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -9167,8 +9613,12 @@
       <x:c r="J215" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K215" s="11"/>
-      <x:c r="L215" s="11"/>
+      <x:c r="K215" s="16" t="n">
+        <x:v>47.620082387934</x:v>
+      </x:c>
+      <x:c r="L215" s="16" t="n">
+        <x:v>-122.17491515411</x:v>
+      </x:c>
       <x:c r="M215" s="11" t="str"/>
       <x:c r="N215" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -9211,8 +9661,8 @@
       <x:c r="J216" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K216" s="11"/>
-      <x:c r="L216" s="11"/>
+      <x:c r="K216" s="16"/>
+      <x:c r="L216" s="16"/>
       <x:c r="M216" s="11" t="str"/>
       <x:c r="N216" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -9251,8 +9701,8 @@
       <x:c r="J217" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K217" s="11"/>
-      <x:c r="L217" s="11"/>
+      <x:c r="K217" s="16"/>
+      <x:c r="L217" s="16"/>
       <x:c r="M217" s="11" t="str"/>
       <x:c r="N217" s="11" t="str">
         <x:v>Planned / under construction - official source</x:v>
@@ -9295,8 +9745,12 @@
       <x:c r="J218" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K218" s="11"/>
-      <x:c r="L218" s="11"/>
+      <x:c r="K218" s="16" t="n">
+        <x:v>34.028981546889</x:v>
+      </x:c>
+      <x:c r="L218" s="16" t="n">
+        <x:v>-118.246255856478</x:v>
+      </x:c>
       <x:c r="M218" s="11" t="str"/>
       <x:c r="N218" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -9339,8 +9793,12 @@
       <x:c r="J219" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K219" s="11"/>
-      <x:c r="L219" s="11"/>
+      <x:c r="K219" s="16" t="n">
+        <x:v>37.69519032426</x:v>
+      </x:c>
+      <x:c r="L219" s="16" t="n">
+        <x:v>-122.163728659626</x:v>
+      </x:c>
       <x:c r="M219" s="11" t="str"/>
       <x:c r="N219" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -9383,8 +9841,12 @@
       <x:c r="J220" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K220" s="11"/>
-      <x:c r="L220" s="11"/>
+      <x:c r="K220" s="16" t="n">
+        <x:v>33.931522319231</x:v>
+      </x:c>
+      <x:c r="L220" s="16" t="n">
+        <x:v>-118.128843685899</x:v>
+      </x:c>
       <x:c r="M220" s="11" t="str"/>
       <x:c r="N220" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -9427,8 +9889,12 @@
       <x:c r="J221" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K221" s="11"/>
-      <x:c r="L221" s="11"/>
+      <x:c r="K221" s="16" t="n">
+        <x:v>42.957951216293</x:v>
+      </x:c>
+      <x:c r="L221" s="16" t="n">
+        <x:v>-85.703349446667</x:v>
+      </x:c>
       <x:c r="M221" s="11" t="str"/>
       <x:c r="N221" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -9471,8 +9937,12 @@
       <x:c r="J222" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K222" s="11"/>
-      <x:c r="L222" s="11"/>
+      <x:c r="K222" s="16" t="n">
+        <x:v>42.014512572892</x:v>
+      </x:c>
+      <x:c r="L222" s="16" t="n">
+        <x:v>-87.793858596202</x:v>
+      </x:c>
       <x:c r="M222" s="11" t="str"/>
       <x:c r="N222" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -9515,8 +9985,12 @@
       <x:c r="J223" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K223" s="11"/>
-      <x:c r="L223" s="11"/>
+      <x:c r="K223" s="16" t="n">
+        <x:v>41.67049986079</x:v>
+      </x:c>
+      <x:c r="L223" s="16" t="n">
+        <x:v>-87.748830618253</x:v>
+      </x:c>
       <x:c r="M223" s="11" t="str"/>
       <x:c r="N223" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -9559,8 +10033,12 @@
       <x:c r="J224" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K224" s="11"/>
-      <x:c r="L224" s="11"/>
+      <x:c r="K224" s="16" t="n">
+        <x:v>43.17793147412</x:v>
+      </x:c>
+      <x:c r="L224" s="16" t="n">
+        <x:v>-88.049443515569</x:v>
+      </x:c>
       <x:c r="M224" s="11" t="str"/>
       <x:c r="N224" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -9603,8 +10081,12 @@
       <x:c r="J225" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K225" s="11"/>
-      <x:c r="L225" s="11"/>
+      <x:c r="K225" s="16" t="n">
+        <x:v>44.857349337947</x:v>
+      </x:c>
+      <x:c r="L225" s="16" t="n">
+        <x:v>-93.153878954634</x:v>
+      </x:c>
       <x:c r="M225" s="11" t="str"/>
       <x:c r="N225" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -9647,8 +10129,12 @@
       <x:c r="J226" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K226" s="11"/>
-      <x:c r="L226" s="11"/>
+      <x:c r="K226" s="16" t="n">
+        <x:v>41.068560047086</x:v>
+      </x:c>
+      <x:c r="L226" s="16" t="n">
+        <x:v>-73.821561470957</x:v>
+      </x:c>
       <x:c r="M226" s="11" t="str"/>
       <x:c r="N226" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -9687,8 +10173,8 @@
       <x:c r="J227" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K227" s="11"/>
-      <x:c r="L227" s="11"/>
+      <x:c r="K227" s="16"/>
+      <x:c r="L227" s="16"/>
       <x:c r="M227" s="11" t="str"/>
       <x:c r="N227" s="11" t="str">
         <x:v>Verified production city - street address pending</x:v>
@@ -9727,8 +10213,8 @@
       <x:c r="J228" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K228" s="11"/>
-      <x:c r="L228" s="11"/>
+      <x:c r="K228" s="16"/>
+      <x:c r="L228" s="16"/>
       <x:c r="M228" s="11" t="str"/>
       <x:c r="N228" s="11" t="str">
         <x:v>Verified production city - street address pending</x:v>
@@ -9771,8 +10257,12 @@
       <x:c r="J229" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K229" s="11"/>
-      <x:c r="L229" s="11"/>
+      <x:c r="K229" s="16" t="n">
+        <x:v>41.410635303223</x:v>
+      </x:c>
+      <x:c r="L229" s="16" t="n">
+        <x:v>-95.015777603544</x:v>
+      </x:c>
       <x:c r="M229" s="11" t="str"/>
       <x:c r="N229" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -9815,8 +10305,12 @@
       <x:c r="J230" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K230" s="11"/>
-      <x:c r="L230" s="11"/>
+      <x:c r="K230" s="16" t="n">
+        <x:v>38.818212121207</x:v>
+      </x:c>
+      <x:c r="L230" s="16" t="n">
+        <x:v>-94.853362441035</x:v>
+      </x:c>
       <x:c r="M230" s="11" t="str"/>
       <x:c r="N230" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -9855,8 +10349,8 @@
       <x:c r="J231" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K231" s="11"/>
-      <x:c r="L231" s="11"/>
+      <x:c r="K231" s="16"/>
+      <x:c r="L231" s="16"/>
       <x:c r="M231" s="11" t="str"/>
       <x:c r="N231" s="11" t="str">
         <x:v>Verified current manufacturing site - official source</x:v>
@@ -9895,8 +10389,8 @@
       <x:c r="J232" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K232" s="11"/>
-      <x:c r="L232" s="11"/>
+      <x:c r="K232" s="16"/>
+      <x:c r="L232" s="16"/>
       <x:c r="M232" s="11" t="str"/>
       <x:c r="N232" s="11" t="str">
         <x:v>Verified current manufacturing site - official source</x:v>
@@ -9935,8 +10429,8 @@
       <x:c r="J233" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K233" s="11"/>
-      <x:c r="L233" s="11"/>
+      <x:c r="K233" s="16"/>
+      <x:c r="L233" s="16"/>
       <x:c r="M233" s="11" t="str"/>
       <x:c r="N233" s="11" t="str">
         <x:v>Verified current manufacturing site - official source</x:v>
@@ -9975,8 +10469,8 @@
       <x:c r="J234" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K234" s="11"/>
-      <x:c r="L234" s="11"/>
+      <x:c r="K234" s="16"/>
+      <x:c r="L234" s="16"/>
       <x:c r="M234" s="11" t="str"/>
       <x:c r="N234" s="11" t="str">
         <x:v>Verified current manufacturing site - official source</x:v>
@@ -10017,8 +10511,12 @@
       <x:c r="J235" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K235" s="11"/>
-      <x:c r="L235" s="11"/>
+      <x:c r="K235" s="16" t="n">
+        <x:v>39.802045200458</x:v>
+      </x:c>
+      <x:c r="L235" s="16" t="n">
+        <x:v>-86.244581618787</x:v>
+      </x:c>
       <x:c r="M235" s="11" t="str"/>
       <x:c r="N235" s="11" t="str">
         <x:v>Verified current manufacturing site - official source</x:v>
@@ -10057,8 +10555,8 @@
       <x:c r="J236" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K236" s="11"/>
-      <x:c r="L236" s="11"/>
+      <x:c r="K236" s="16"/>
+      <x:c r="L236" s="16"/>
       <x:c r="M236" s="11" t="str"/>
       <x:c r="N236" s="11" t="str">
         <x:v>Manufacturing site identified - current street/status final-check</x:v>
@@ -10097,8 +10595,8 @@
       <x:c r="J237" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K237" s="11"/>
-      <x:c r="L237" s="11"/>
+      <x:c r="K237" s="16"/>
+      <x:c r="L237" s="16"/>
       <x:c r="M237" s="11" t="str"/>
       <x:c r="N237" s="11" t="str">
         <x:v>Manufacturing site identified - current street/status final-check</x:v>
@@ -10139,8 +10637,12 @@
       <x:c r="J238" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K238" s="11"/>
-      <x:c r="L238" s="11"/>
+      <x:c r="K238" s="16" t="n">
+        <x:v>41.297701950294</x:v>
+      </x:c>
+      <x:c r="L238" s="16" t="n">
+        <x:v>-81.456302259189</x:v>
+      </x:c>
       <x:c r="M238" s="11" t="str"/>
       <x:c r="N238" s="11" t="str">
         <x:v>Verified current manufacturing site - official source</x:v>
@@ -10179,8 +10681,8 @@
       <x:c r="J239" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K239" s="11"/>
-      <x:c r="L239" s="11"/>
+      <x:c r="K239" s="16"/>
+      <x:c r="L239" s="16"/>
       <x:c r="M239" s="11" t="str"/>
       <x:c r="N239" s="11" t="str">
         <x:v>Verified current manufacturing site - official source</x:v>
@@ -10219,8 +10721,8 @@
       <x:c r="J240" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K240" s="11"/>
-      <x:c r="L240" s="11"/>
+      <x:c r="K240" s="16"/>
+      <x:c r="L240" s="16"/>
       <x:c r="M240" s="11" t="str"/>
       <x:c r="N240" s="11" t="str">
         <x:v>Manufacturing site identified - current street/status final-check</x:v>
@@ -10263,8 +10765,8 @@
       <x:c r="J241" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K241" s="11"/>
-      <x:c r="L241" s="11"/>
+      <x:c r="K241" s="16"/>
+      <x:c r="L241" s="16"/>
       <x:c r="M241" s="11" t="str"/>
       <x:c r="N241" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -10307,8 +10809,12 @@
       <x:c r="J242" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K242" s="11"/>
-      <x:c r="L242" s="11"/>
+      <x:c r="K242" s="16" t="n">
+        <x:v>36.108962361481</x:v>
+      </x:c>
+      <x:c r="L242" s="16" t="n">
+        <x:v>-80.171067507809</x:v>
+      </x:c>
       <x:c r="M242" s="11" t="str"/>
       <x:c r="N242" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -10351,8 +10857,12 @@
       <x:c r="J243" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K243" s="11"/>
-      <x:c r="L243" s="11"/>
+      <x:c r="K243" s="16" t="n">
+        <x:v>36.039012278611</x:v>
+      </x:c>
+      <x:c r="L243" s="16" t="n">
+        <x:v>-80.149962671024</x:v>
+      </x:c>
       <x:c r="M243" s="11" t="str"/>
       <x:c r="N243" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -10387,8 +10897,8 @@
       <x:c r="J244" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K244" s="11"/>
-      <x:c r="L244" s="11"/>
+      <x:c r="K244" s="16"/>
+      <x:c r="L244" s="16"/>
       <x:c r="M244" s="11" t="str"/>
       <x:c r="N244" s="11" t="str">
         <x:v>Known gap - PBV states 4 production facilities; fourth site not yet conclusively identified</x:v>
@@ -10431,8 +10941,12 @@
       <x:c r="J245" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K245" s="11"/>
-      <x:c r="L245" s="11"/>
+      <x:c r="K245" s="16" t="n">
+        <x:v>38.622102365851</x:v>
+      </x:c>
+      <x:c r="L245" s="16" t="n">
+        <x:v>-82.843880510264</x:v>
+      </x:c>
       <x:c r="M245" s="11" t="str"/>
       <x:c r="N245" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -10475,8 +10989,12 @@
       <x:c r="J246" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K246" s="11"/>
-      <x:c r="L246" s="11"/>
+      <x:c r="K246" s="16" t="n">
+        <x:v>39.366338747361</x:v>
+      </x:c>
+      <x:c r="L246" s="16" t="n">
+        <x:v>-84.538379214131</x:v>
+      </x:c>
       <x:c r="M246" s="11" t="str"/>
       <x:c r="N246" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -10519,8 +11037,12 @@
       <x:c r="J247" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K247" s="11"/>
-      <x:c r="L247" s="11"/>
+      <x:c r="K247" s="16" t="n">
+        <x:v>38.639520318812</x:v>
+      </x:c>
+      <x:c r="L247" s="16" t="n">
+        <x:v>-83.816131067011</x:v>
+      </x:c>
       <x:c r="M247" s="11" t="str"/>
       <x:c r="N247" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -10563,8 +11085,12 @@
       <x:c r="J248" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K248" s="11"/>
-      <x:c r="L248" s="11"/>
+      <x:c r="K248" s="16" t="n">
+        <x:v>39.944332757668</x:v>
+      </x:c>
+      <x:c r="L248" s="16" t="n">
+        <x:v>-82.004816053759</x:v>
+      </x:c>
       <x:c r="M248" s="11" t="str"/>
       <x:c r="N248" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -10607,8 +11133,12 @@
       <x:c r="J249" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K249" s="11"/>
-      <x:c r="L249" s="11"/>
+      <x:c r="K249" s="16" t="n">
+        <x:v>39.983245074747</x:v>
+      </x:c>
+      <x:c r="L249" s="16" t="n">
+        <x:v>-82.97051104758</x:v>
+      </x:c>
       <x:c r="M249" s="11" t="str"/>
       <x:c r="N249" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -10651,8 +11181,12 @@
       <x:c r="J250" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K250" s="11"/>
-      <x:c r="L250" s="11"/>
+      <x:c r="K250" s="16" t="n">
+        <x:v>43.189891069945</x:v>
+      </x:c>
+      <x:c r="L250" s="16" t="n">
+        <x:v>-88.746557356068</x:v>
+      </x:c>
       <x:c r="M250" s="11" t="str"/>
       <x:c r="N250" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -10695,8 +11229,8 @@
       <x:c r="J251" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K251" s="11"/>
-      <x:c r="L251" s="11"/>
+      <x:c r="K251" s="16"/>
+      <x:c r="L251" s="16"/>
       <x:c r="M251" s="11" t="str"/>
       <x:c r="N251" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -10739,8 +11273,12 @@
       <x:c r="J252" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K252" s="11"/>
-      <x:c r="L252" s="11"/>
+      <x:c r="K252" s="16" t="n">
+        <x:v>31.268703342259</x:v>
+      </x:c>
+      <x:c r="L252" s="16" t="n">
+        <x:v>-89.265621432098</x:v>
+      </x:c>
       <x:c r="M252" s="11" t="str"/>
       <x:c r="N252" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -10783,8 +11321,12 @@
       <x:c r="J253" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K253" s="11"/>
-      <x:c r="L253" s="11"/>
+      <x:c r="K253" s="16" t="n">
+        <x:v>43.882971572146</x:v>
+      </x:c>
+      <x:c r="L253" s="16" t="n">
+        <x:v>-91.267862848938</x:v>
+      </x:c>
       <x:c r="M253" s="11" t="str"/>
       <x:c r="N253" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -10827,8 +11369,12 @@
       <x:c r="J254" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K254" s="11"/>
-      <x:c r="L254" s="11"/>
+      <x:c r="K254" s="16" t="n">
+        <x:v>44.177107130246</x:v>
+      </x:c>
+      <x:c r="L254" s="16" t="n">
+        <x:v>-94.043931492625</x:v>
+      </x:c>
       <x:c r="M254" s="11" t="str"/>
       <x:c r="N254" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -10871,8 +11417,12 @@
       <x:c r="J255" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K255" s="11"/>
-      <x:c r="L255" s="11"/>
+      <x:c r="K255" s="16" t="n">
+        <x:v>42.00716314941</x:v>
+      </x:c>
+      <x:c r="L255" s="16" t="n">
+        <x:v>-97.428989376146</x:v>
+      </x:c>
       <x:c r="M255" s="11" t="str"/>
       <x:c r="N255" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -10915,8 +11465,12 @@
       <x:c r="J256" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K256" s="11"/>
-      <x:c r="L256" s="11"/>
+      <x:c r="K256" s="16" t="n">
+        <x:v>39.957387284416</x:v>
+      </x:c>
+      <x:c r="L256" s="16" t="n">
+        <x:v>-91.367465854589</x:v>
+      </x:c>
       <x:c r="M256" s="11" t="str"/>
       <x:c r="N256" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -10959,8 +11513,12 @@
       <x:c r="J257" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K257" s="11"/>
-      <x:c r="L257" s="11"/>
+      <x:c r="K257" s="16" t="n">
+        <x:v>33.439043552009</x:v>
+      </x:c>
+      <x:c r="L257" s="16" t="n">
+        <x:v>-86.845863999105</x:v>
+      </x:c>
       <x:c r="M257" s="11" t="str"/>
       <x:c r="N257" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -10999,8 +11557,8 @@
       <x:c r="J258" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K258" s="11"/>
-      <x:c r="L258" s="11"/>
+      <x:c r="K258" s="16"/>
+      <x:c r="L258" s="16"/>
       <x:c r="M258" s="11" t="str"/>
       <x:c r="N258" s="11" t="str">
         <x:v>Verified production city - street address pending</x:v>
@@ -11023,7 +11581,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R32befc6bad584615"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re09bc30023e84cda"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11103,7 +11661,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcebc9cd5d2ed4eb8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re56804ff7fce4fa0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11189,4 +11747,5184 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="11" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="30" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="34" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="24" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="70" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="21" t="str">
+        <x:v>Excel Row</x:v>
+      </x:c>
+      <x:c r="B1" s="21" t="str">
+        <x:v>Facility Name</x:v>
+      </x:c>
+      <x:c r="C1" s="21" t="str">
+        <x:v>Coordinate Status</x:v>
+      </x:c>
+      <x:c r="D1" s="21" t="str">
+        <x:v>Method / Source</x:v>
+      </x:c>
+      <x:c r="E1" s="21" t="str">
+        <x:v>Match Quality</x:v>
+      </x:c>
+      <x:c r="F1" s="21" t="str">
+        <x:v>Matched Address / Note</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="31" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B2" s="32" t="str">
+        <x:v>DP1-02</x:v>
+      </x:c>
+      <x:c r="C2" s="32" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="str">
+        <x:v>OpenStreetMap Nominatim (cached one-time lookup)</x:v>
+      </x:c>
+      <x:c r="E2" s="32" t="str">
+        <x:v>Exact building</x:v>
+      </x:c>
+      <x:c r="F2" s="33" t="str">
+        <x:v>Building 2, 21375, Needham Ranch Parkway, Waltz, Santa Clarita, Los Angeles County, California, 91322, United States</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="34" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B3" s="35" t="str">
+        <x:v>DP1-03</x:v>
+      </x:c>
+      <x:c r="C3" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D3" s="35" t="str">
+        <x:v>U.S. Census + OpenStreetMap fallback</x:v>
+      </x:c>
+      <x:c r="E3" s="35" t="str">
+        <x:v>No accepted match</x:v>
+      </x:c>
+      <x:c r="F3" s="36" t="str">
+        <x:v>Street address requires manual verification</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="34" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B4" s="35" t="str">
+        <x:v>DP1-04</x:v>
+      </x:c>
+      <x:c r="C4" s="35" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D4" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E4" s="35" t="str">
+        <x:v>Exact address match</x:v>
+      </x:c>
+      <x:c r="F4" s="36" t="str">
+        <x:v>23015 PINE ST, SANTA CLARITA, CA, 91321</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="34" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B5" s="35" t="str">
+        <x:v>DP2</x:v>
+      </x:c>
+      <x:c r="C5" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D5" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E5" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F5" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="34" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B6" s="35" t="str">
+        <x:v>DP3</x:v>
+      </x:c>
+      <x:c r="C6" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D6" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E6" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F6" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="34" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B7" s="35" t="str">
+        <x:v>RAUCH North America</x:v>
+      </x:c>
+      <x:c r="C7" s="35" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="D7" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E7" s="35" t="str">
+        <x:v>Non-exact match</x:v>
+      </x:c>
+      <x:c r="F7" s="36" t="str">
+        <x:v>10501 REEMS RD, WADDELL, AZ, 85355</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="34" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B8" s="35" t="str">
+        <x:v>Anheuser-Busch Brewery - St. Louis</x:v>
+      </x:c>
+      <x:c r="C8" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D8" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E8" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F8" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="34" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B9" s="35" t="str">
+        <x:v>Anheuser-Busch Brewery - Baldwinsville</x:v>
+      </x:c>
+      <x:c r="C9" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D9" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E9" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F9" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="34" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B10" s="35" t="str">
+        <x:v>Anheuser-Busch Brewery - Cartersville</x:v>
+      </x:c>
+      <x:c r="C10" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D10" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E10" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F10" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="34" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B11" s="35" t="str">
+        <x:v>Anheuser-Busch Brewery - Columbus</x:v>
+      </x:c>
+      <x:c r="C11" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D11" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E11" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F11" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="34" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B12" s="35" t="str">
+        <x:v>Anheuser-Busch Brewery - Fort Collins</x:v>
+      </x:c>
+      <x:c r="C12" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D12" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E12" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F12" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="34" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B13" s="35" t="str">
+        <x:v>Anheuser-Busch Brewery - Houston</x:v>
+      </x:c>
+      <x:c r="C13" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D13" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E13" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F13" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="34" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B14" s="35" t="str">
+        <x:v>Anheuser-Busch Brewery - Jacksonville</x:v>
+      </x:c>
+      <x:c r="C14" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D14" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E14" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F14" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="34" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B15" s="35" t="str">
+        <x:v>Anheuser-Busch Brewery - Los Angeles</x:v>
+      </x:c>
+      <x:c r="C15" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D15" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E15" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F15" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="34" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B16" s="35" t="str">
+        <x:v>Anheuser-Busch Brewery - Williamsburg</x:v>
+      </x:c>
+      <x:c r="C16" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D16" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E16" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F16" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="34" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B17" s="35" t="str">
+        <x:v>Anheuser-Busch Brewery - Fairfield</x:v>
+      </x:c>
+      <x:c r="C17" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D17" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E17" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F17" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="34" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B18" s="35" t="str">
+        <x:v>Anheuser-Busch Brewery - Merrimack</x:v>
+      </x:c>
+      <x:c r="C18" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D18" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E18" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F18" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="34" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B19" s="35" t="str">
+        <x:v>Anheuser-Busch Brewery - Newark</x:v>
+      </x:c>
+      <x:c r="C19" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D19" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E19" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F19" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="34" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B20" s="35" t="str">
+        <x:v>Mark Anthony Brewing - Glendale</x:v>
+      </x:c>
+      <x:c r="C20" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D20" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E20" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F20" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="34" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B21" s="35" t="str">
+        <x:v>Mark Anthony Brewing - Columbia</x:v>
+      </x:c>
+      <x:c r="C21" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D21" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E21" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F21" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="34" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B22" s="35" t="str">
+        <x:v>Mark Anthony Brewing - Hillside</x:v>
+      </x:c>
+      <x:c r="C22" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D22" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E22" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F22" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="34" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B23" s="35" t="str">
+        <x:v>MCC - Arnold</x:v>
+      </x:c>
+      <x:c r="C23" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D23" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E23" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F23" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="34" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B24" s="35" t="str">
+        <x:v>MCC - Jacksonville</x:v>
+      </x:c>
+      <x:c r="C24" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D24" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E24" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F24" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="34" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B25" s="35" t="str">
+        <x:v>MCC - Mira Loma</x:v>
+      </x:c>
+      <x:c r="C25" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D25" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E25" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F25" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="34" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B26" s="35" t="str">
+        <x:v>MCC - Newburgh</x:v>
+      </x:c>
+      <x:c r="C26" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D26" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E26" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F26" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="34" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B27" s="35" t="str">
+        <x:v>MCC - Windsor</x:v>
+      </x:c>
+      <x:c r="C27" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D27" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E27" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F27" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="34" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B28" s="35" t="str">
+        <x:v>MCC - Oklahoma City</x:v>
+      </x:c>
+      <x:c r="C28" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D28" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E28" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F28" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="34" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B29" s="35" t="str">
+        <x:v>MCC - Riverside</x:v>
+      </x:c>
+      <x:c r="C29" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D29" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E29" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F29" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="34" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B30" s="35" t="str">
+        <x:v>Molson Coors - Golden</x:v>
+      </x:c>
+      <x:c r="C30" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D30" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E30" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F30" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="34" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B31" s="35" t="str">
+        <x:v>Molson Coors - Milwaukee</x:v>
+      </x:c>
+      <x:c r="C31" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D31" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E31" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F31" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="34" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B32" s="35" t="str">
+        <x:v>Molson Coors - Albany</x:v>
+      </x:c>
+      <x:c r="C32" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D32" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E32" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F32" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="34" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B33" s="35" t="str">
+        <x:v>Molson Coors - Fort Worth</x:v>
+      </x:c>
+      <x:c r="C33" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D33" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E33" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F33" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="34" t="n">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B34" s="35" t="str">
+        <x:v>Molson Coors - Trenton</x:v>
+      </x:c>
+      <x:c r="C34" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D34" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E34" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F34" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="34" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B35" s="35" t="str">
+        <x:v>Molson Coors - Elkton</x:v>
+      </x:c>
+      <x:c r="C35" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D35" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E35" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F35" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="34" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B36" s="35" t="str">
+        <x:v>Molson Coors - Chilliwack</x:v>
+      </x:c>
+      <x:c r="C36" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D36" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E36" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F36" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="34" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B37" s="35" t="str">
+        <x:v>Molson Coors - Longueuil</x:v>
+      </x:c>
+      <x:c r="C37" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D37" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E37" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F37" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="34" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B38" s="35" t="str">
+        <x:v>Molson Coors - St. John's</x:v>
+      </x:c>
+      <x:c r="C38" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D38" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E38" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F38" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" s="34" t="n">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B39" s="35" t="str">
+        <x:v>City Brewing - La Crosse</x:v>
+      </x:c>
+      <x:c r="C39" s="35" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="D39" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E39" s="35" t="str">
+        <x:v>Non-exact match</x:v>
+      </x:c>
+      <x:c r="F39" s="36" t="str">
+        <x:v>925 3RD ST S, LA CROSSE, WI, 54601</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" s="34" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B40" s="35" t="str">
+        <x:v>City Brewing - Latrobe</x:v>
+      </x:c>
+      <x:c r="C40" s="35" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D40" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E40" s="35" t="str">
+        <x:v>Exact address match</x:v>
+      </x:c>
+      <x:c r="F40" s="36" t="str">
+        <x:v>100 33RD ST, LATROBE, PA, 15650</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" s="34" t="n">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="B41" s="35" t="str">
+        <x:v>City Brewing - Memphis</x:v>
+      </x:c>
+      <x:c r="C41" s="35" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D41" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E41" s="35" t="str">
+        <x:v>Exact address match</x:v>
+      </x:c>
+      <x:c r="F41" s="36" t="str">
+        <x:v>5151 E RAINES RD, MEMPHIS, TN, 38118</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" s="34" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B42" s="35" t="str">
+        <x:v>City Brewing - Irwindale</x:v>
+      </x:c>
+      <x:c r="C42" s="35" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="D42" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E42" s="35" t="str">
+        <x:v>Non-exact match</x:v>
+      </x:c>
+      <x:c r="F42" s="36" t="str">
+        <x:v>15801 E 1ST ST, IRWINDALE, CA, 91706</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" s="34" t="n">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B43" s="35" t="str">
+        <x:v>Ardagh - Elk Grove Village</x:v>
+      </x:c>
+      <x:c r="C43" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D43" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E43" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F43" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" s="34" t="n">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B44" s="35" t="str">
+        <x:v>Ardagh - Bishopville</x:v>
+      </x:c>
+      <x:c r="C44" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D44" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E44" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F44" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" s="34" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B45" s="35" t="str">
+        <x:v>Ardagh - Chicago</x:v>
+      </x:c>
+      <x:c r="C45" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D45" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E45" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F45" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" s="34" t="n">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B46" s="35" t="str">
+        <x:v>Ardagh - Fairfield</x:v>
+      </x:c>
+      <x:c r="C46" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D46" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E46" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F46" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" s="34" t="n">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B47" s="35" t="str">
+        <x:v>Ardagh - Fremont</x:v>
+      </x:c>
+      <x:c r="C47" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D47" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E47" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F47" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" s="34" t="n">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B48" s="35" t="str">
+        <x:v>Ardagh - Huron</x:v>
+      </x:c>
+      <x:c r="C48" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D48" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E48" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F48" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" s="34" t="n">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B49" s="35" t="str">
+        <x:v>Ardagh - Olive Branch</x:v>
+      </x:c>
+      <x:c r="C49" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D49" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E49" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F49" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50" s="34" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="B50" s="35" t="str">
+        <x:v>Ardagh - Valparaiso</x:v>
+      </x:c>
+      <x:c r="C50" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D50" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E50" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F50" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51">
+      <x:c r="A51" s="34" t="n">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="B51" s="35" t="str">
+        <x:v>Ardagh - Winston-Salem</x:v>
+      </x:c>
+      <x:c r="C51" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D51" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E51" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F51" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52">
+      <x:c r="A52" s="34" t="n">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="B52" s="35" t="str">
+        <x:v>Ball - Waddell</x:v>
+      </x:c>
+      <x:c r="C52" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D52" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E52" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F52" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53">
+      <x:c r="A53" s="34" t="n">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="B53" s="35" t="str">
+        <x:v>Ball - Goodyear</x:v>
+      </x:c>
+      <x:c r="C53" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D53" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E53" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F53" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54">
+      <x:c r="A54" s="34" t="n">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B54" s="35" t="str">
+        <x:v>Ball - Golden</x:v>
+      </x:c>
+      <x:c r="C54" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D54" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E54" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F54" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55">
+      <x:c r="A55" s="34" t="n">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="B55" s="35" t="str">
+        <x:v>Ball - Rome</x:v>
+      </x:c>
+      <x:c r="C55" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D55" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E55" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F55" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56">
+      <x:c r="A56" s="34" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B56" s="35" t="str">
+        <x:v>Ball - Findlay</x:v>
+      </x:c>
+      <x:c r="C56" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D56" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E56" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F56" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57">
+      <x:c r="A57" s="34" t="n">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="B57" s="35" t="str">
+        <x:v>Ball - Pittston</x:v>
+      </x:c>
+      <x:c r="C57" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D57" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E57" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F57" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58">
+      <x:c r="A58" s="34" t="n">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="B58" s="35" t="str">
+        <x:v>Ball - Fort Worth</x:v>
+      </x:c>
+      <x:c r="C58" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D58" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E58" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F58" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59">
+      <x:c r="A59" s="34" t="n">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="B59" s="35" t="str">
+        <x:v>Ball - Conroe</x:v>
+      </x:c>
+      <x:c r="C59" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D59" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E59" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F59" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60">
+      <x:c r="A60" s="34" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B60" s="35" t="str">
+        <x:v>Ball - Millersburg</x:v>
+      </x:c>
+      <x:c r="C60" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D60" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E60" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F60" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61">
+      <x:c r="A61" s="34" t="n">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="B61" s="35" t="str">
+        <x:v>Ball - Ft. Atkinson</x:v>
+      </x:c>
+      <x:c r="C61" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D61" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E61" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F61" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62">
+      <x:c r="A62" s="34" t="n">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="B62" s="35" t="str">
+        <x:v>Ball - Saratoga Springs</x:v>
+      </x:c>
+      <x:c r="C62" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D62" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E62" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F62" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63">
+      <x:c r="A63" s="34" t="n">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="B63" s="35" t="str">
+        <x:v>Ball - Winter Haven</x:v>
+      </x:c>
+      <x:c r="C63" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D63" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E63" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F63" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64">
+      <x:c r="A64" s="34" t="n">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="B64" s="35" t="str">
+        <x:v>Crown - Benton</x:v>
+      </x:c>
+      <x:c r="C64" s="35" t="str">
+        <x:v>Retained</x:v>
+      </x:c>
+      <x:c r="D64" s="35" t="str">
+        <x:v>Official Crown global-locations page</x:v>
+      </x:c>
+      <x:c r="E64" s="35" t="str">
+        <x:v>Official city-level point</x:v>
+      </x:c>
+      <x:c r="F64" s="36" t="str">
+        <x:v>Matches Crown's published city coordinate; not verified as an exact building point</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65">
+      <x:c r="A65" s="34" t="n">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="B65" s="35" t="str">
+        <x:v>Crown - Dubuque</x:v>
+      </x:c>
+      <x:c r="C65" s="35" t="str">
+        <x:v>Retained</x:v>
+      </x:c>
+      <x:c r="D65" s="35" t="str">
+        <x:v>Official Crown global-locations page</x:v>
+      </x:c>
+      <x:c r="E65" s="35" t="str">
+        <x:v>Official city-level point</x:v>
+      </x:c>
+      <x:c r="F65" s="36" t="str">
+        <x:v>Matches Crown's published city coordinate; not verified as an exact building point</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66">
+      <x:c r="A66" s="34" t="n">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="B66" s="35" t="str">
+        <x:v>Crown - Alsip</x:v>
+      </x:c>
+      <x:c r="C66" s="35" t="str">
+        <x:v>Retained</x:v>
+      </x:c>
+      <x:c r="D66" s="35" t="str">
+        <x:v>Official Crown global-locations page</x:v>
+      </x:c>
+      <x:c r="E66" s="35" t="str">
+        <x:v>Official city-level point</x:v>
+      </x:c>
+      <x:c r="F66" s="36" t="str">
+        <x:v>Matches Crown's published city coordinate; not verified as an exact building point</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67">
+      <x:c r="A67" s="34" t="n">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="B67" s="35" t="str">
+        <x:v>Crown - Kankakee</x:v>
+      </x:c>
+      <x:c r="C67" s="35" t="str">
+        <x:v>Retained</x:v>
+      </x:c>
+      <x:c r="D67" s="35" t="str">
+        <x:v>Official Crown global-locations page</x:v>
+      </x:c>
+      <x:c r="E67" s="35" t="str">
+        <x:v>Official city-level point</x:v>
+      </x:c>
+      <x:c r="F67" s="36" t="str">
+        <x:v>Matches Crown's published city coordinate; not verified as an exact building point</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68">
+      <x:c r="A68" s="34" t="n">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="B68" s="35" t="str">
+        <x:v>Crown - Bowling Green</x:v>
+      </x:c>
+      <x:c r="C68" s="35" t="str">
+        <x:v>Retained</x:v>
+      </x:c>
+      <x:c r="D68" s="35" t="str">
+        <x:v>Official Crown global-locations page</x:v>
+      </x:c>
+      <x:c r="E68" s="35" t="str">
+        <x:v>Official city-level point</x:v>
+      </x:c>
+      <x:c r="F68" s="36" t="str">
+        <x:v>Matches Crown's published city coordinate; not verified as an exact building point</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69">
+      <x:c r="A69" s="34" t="n">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="B69" s="35" t="str">
+        <x:v>Crown - Faribault</x:v>
+      </x:c>
+      <x:c r="C69" s="35" t="str">
+        <x:v>Retained</x:v>
+      </x:c>
+      <x:c r="D69" s="35" t="str">
+        <x:v>Official Crown global-locations page</x:v>
+      </x:c>
+      <x:c r="E69" s="35" t="str">
+        <x:v>Official city-level point</x:v>
+      </x:c>
+      <x:c r="F69" s="36" t="str">
+        <x:v>Matches Crown's published city coordinate; not verified as an exact building point</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70">
+      <x:c r="A70" s="34" t="n">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="B70" s="35" t="str">
+        <x:v>Crown - Mankato</x:v>
+      </x:c>
+      <x:c r="C70" s="35" t="str">
+        <x:v>Retained</x:v>
+      </x:c>
+      <x:c r="D70" s="35" t="str">
+        <x:v>Official Crown global-locations page</x:v>
+      </x:c>
+      <x:c r="E70" s="35" t="str">
+        <x:v>Official city-level point</x:v>
+      </x:c>
+      <x:c r="F70" s="36" t="str">
+        <x:v>Matches Crown's published city coordinate; not verified as an exact building point</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71">
+      <x:c r="A71" s="34" t="n">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="B71" s="35" t="str">
+        <x:v>Crown - Owatonna</x:v>
+      </x:c>
+      <x:c r="C71" s="35" t="str">
+        <x:v>Retained</x:v>
+      </x:c>
+      <x:c r="D71" s="35" t="str">
+        <x:v>Official Crown global-locations page</x:v>
+      </x:c>
+      <x:c r="E71" s="35" t="str">
+        <x:v>Official city-level point</x:v>
+      </x:c>
+      <x:c r="F71" s="36" t="str">
+        <x:v>Matches Crown's published city coordinate; not verified as an exact building point</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72">
+      <x:c r="A72" s="34" t="n">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="B72" s="35" t="str">
+        <x:v>Crown - Nichols</x:v>
+      </x:c>
+      <x:c r="C72" s="35" t="str">
+        <x:v>Retained</x:v>
+      </x:c>
+      <x:c r="D72" s="35" t="str">
+        <x:v>Official Crown global-locations page</x:v>
+      </x:c>
+      <x:c r="E72" s="35" t="str">
+        <x:v>Official city-level point</x:v>
+      </x:c>
+      <x:c r="F72" s="36" t="str">
+        <x:v>Matches Crown's published city coordinate; not verified as an exact building point</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73">
+      <x:c r="A73" s="34" t="n">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="B73" s="35" t="str">
+        <x:v>Crown - Dayton</x:v>
+      </x:c>
+      <x:c r="C73" s="35" t="str">
+        <x:v>Retained</x:v>
+      </x:c>
+      <x:c r="D73" s="35" t="str">
+        <x:v>Official Crown global-locations page</x:v>
+      </x:c>
+      <x:c r="E73" s="35" t="str">
+        <x:v>Official city-level point</x:v>
+      </x:c>
+      <x:c r="F73" s="36" t="str">
+        <x:v>Matches Crown's published city coordinate; not verified as an exact building point</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74">
+      <x:c r="A74" s="34" t="n">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="B74" s="35" t="str">
+        <x:v>Crown - Lancaster</x:v>
+      </x:c>
+      <x:c r="C74" s="35" t="str">
+        <x:v>Retained</x:v>
+      </x:c>
+      <x:c r="D74" s="35" t="str">
+        <x:v>Official Crown global-locations page</x:v>
+      </x:c>
+      <x:c r="E74" s="35" t="str">
+        <x:v>Official city-level point</x:v>
+      </x:c>
+      <x:c r="F74" s="36" t="str">
+        <x:v>Matches Crown's published city coordinate; not verified as an exact building point</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75">
+      <x:c r="A75" s="34" t="n">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="B75" s="35" t="str">
+        <x:v>Crown - Massillon</x:v>
+      </x:c>
+      <x:c r="C75" s="35" t="str">
+        <x:v>Retained</x:v>
+      </x:c>
+      <x:c r="D75" s="35" t="str">
+        <x:v>Official Crown global-locations page</x:v>
+      </x:c>
+      <x:c r="E75" s="35" t="str">
+        <x:v>Official city-level point</x:v>
+      </x:c>
+      <x:c r="F75" s="36" t="str">
+        <x:v>Matches Crown's published city coordinate; not verified as an exact building point</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76">
+      <x:c r="A76" s="34" t="n">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="B76" s="35" t="str">
+        <x:v>Crown - Mill Park</x:v>
+      </x:c>
+      <x:c r="C76" s="35" t="str">
+        <x:v>Retained</x:v>
+      </x:c>
+      <x:c r="D76" s="35" t="str">
+        <x:v>Official Crown global-locations page</x:v>
+      </x:c>
+      <x:c r="E76" s="35" t="str">
+        <x:v>Official city-level point</x:v>
+      </x:c>
+      <x:c r="F76" s="36" t="str">
+        <x:v>Matches Crown's published city coordinate; not verified as an exact building point</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77">
+      <x:c r="A77" s="34" t="n">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="B77" s="35" t="str">
+        <x:v>Crown - Connellsville</x:v>
+      </x:c>
+      <x:c r="C77" s="35" t="str">
+        <x:v>Retained</x:v>
+      </x:c>
+      <x:c r="D77" s="35" t="str">
+        <x:v>Official Crown global-locations page</x:v>
+      </x:c>
+      <x:c r="E77" s="35" t="str">
+        <x:v>Official city-level point</x:v>
+      </x:c>
+      <x:c r="F77" s="36" t="str">
+        <x:v>Matches Crown's published city coordinate; not verified as an exact building point</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78">
+      <x:c r="A78" s="34" t="n">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="B78" s="35" t="str">
+        <x:v>Crown - Hanover</x:v>
+      </x:c>
+      <x:c r="C78" s="35" t="str">
+        <x:v>Retained</x:v>
+      </x:c>
+      <x:c r="D78" s="35" t="str">
+        <x:v>Official Crown global-locations page</x:v>
+      </x:c>
+      <x:c r="E78" s="35" t="str">
+        <x:v>Official city-level point</x:v>
+      </x:c>
+      <x:c r="F78" s="36" t="str">
+        <x:v>Matches Crown's published city coordinate; not verified as an exact building point</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79">
+      <x:c r="A79" s="34" t="n">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="B79" s="35" t="str">
+        <x:v>Crown - Cheraw</x:v>
+      </x:c>
+      <x:c r="C79" s="35" t="str">
+        <x:v>Retained</x:v>
+      </x:c>
+      <x:c r="D79" s="35" t="str">
+        <x:v>Official Crown global-locations page</x:v>
+      </x:c>
+      <x:c r="E79" s="35" t="str">
+        <x:v>Official city-level point</x:v>
+      </x:c>
+      <x:c r="F79" s="36" t="str">
+        <x:v>Matches Crown's published city coordinate; not verified as an exact building point</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80">
+      <x:c r="A80" s="34" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="B80" s="35" t="str">
+        <x:v>Crown - Effingham</x:v>
+      </x:c>
+      <x:c r="C80" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D80" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E80" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F80" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81">
+      <x:c r="A81" s="34" t="n">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="B81" s="35" t="str">
+        <x:v>Crown - Conroe</x:v>
+      </x:c>
+      <x:c r="C81" s="35" t="str">
+        <x:v>Retained</x:v>
+      </x:c>
+      <x:c r="D81" s="35" t="str">
+        <x:v>Official Crown global-locations page</x:v>
+      </x:c>
+      <x:c r="E81" s="35" t="str">
+        <x:v>Official city-level point</x:v>
+      </x:c>
+      <x:c r="F81" s="36" t="str">
+        <x:v>Matches Crown's published city coordinate; not verified as an exact building point</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82">
+      <x:c r="A82" s="34" t="n">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="B82" s="35" t="str">
+        <x:v>Crown - Ft. Bend</x:v>
+      </x:c>
+      <x:c r="C82" s="35" t="str">
+        <x:v>Retained</x:v>
+      </x:c>
+      <x:c r="D82" s="35" t="str">
+        <x:v>Official Crown global-locations page</x:v>
+      </x:c>
+      <x:c r="E82" s="35" t="str">
+        <x:v>Official city-level point</x:v>
+      </x:c>
+      <x:c r="F82" s="36" t="str">
+        <x:v>Matches Crown's published city coordinate; not verified as an exact building point</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83">
+      <x:c r="A83" s="34" t="n">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="B83" s="35" t="str">
+        <x:v>Crown - Martinsville</x:v>
+      </x:c>
+      <x:c r="C83" s="35" t="str">
+        <x:v>Retained</x:v>
+      </x:c>
+      <x:c r="D83" s="35" t="str">
+        <x:v>Official Crown global-locations page</x:v>
+      </x:c>
+      <x:c r="E83" s="35" t="str">
+        <x:v>Official city-level point</x:v>
+      </x:c>
+      <x:c r="F83" s="36" t="str">
+        <x:v>Matches Crown's published city coordinate; not verified as an exact building point</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84">
+      <x:c r="A84" s="34" t="n">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="B84" s="35" t="str">
+        <x:v>Crown - Winchester</x:v>
+      </x:c>
+      <x:c r="C84" s="35" t="str">
+        <x:v>Retained</x:v>
+      </x:c>
+      <x:c r="D84" s="35" t="str">
+        <x:v>Official Crown global-locations page</x:v>
+      </x:c>
+      <x:c r="E84" s="35" t="str">
+        <x:v>Official city-level point</x:v>
+      </x:c>
+      <x:c r="F84" s="36" t="str">
+        <x:v>Matches Crown's published city coordinate; not verified as an exact building point</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85">
+      <x:c r="A85" s="34" t="n">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="B85" s="35" t="str">
+        <x:v>Crown - Olympia</x:v>
+      </x:c>
+      <x:c r="C85" s="35" t="str">
+        <x:v>Retained</x:v>
+      </x:c>
+      <x:c r="D85" s="35" t="str">
+        <x:v>Official Crown global-locations page</x:v>
+      </x:c>
+      <x:c r="E85" s="35" t="str">
+        <x:v>Official city-level point</x:v>
+      </x:c>
+      <x:c r="F85" s="36" t="str">
+        <x:v>Matches Crown's published city coordinate; not verified as an exact building point</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86">
+      <x:c r="A86" s="34" t="n">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="B86" s="35" t="str">
+        <x:v>Crown - La Crosse</x:v>
+      </x:c>
+      <x:c r="C86" s="35" t="str">
+        <x:v>Retained</x:v>
+      </x:c>
+      <x:c r="D86" s="35" t="str">
+        <x:v>Official Crown global-locations page</x:v>
+      </x:c>
+      <x:c r="E86" s="35" t="str">
+        <x:v>Official city-level point</x:v>
+      </x:c>
+      <x:c r="F86" s="36" t="str">
+        <x:v>Matches Crown's published city coordinate; not verified as an exact building point</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87">
+      <x:c r="A87" s="34" t="n">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B87" s="35" t="str">
+        <x:v>Crown - Worland</x:v>
+      </x:c>
+      <x:c r="C87" s="35" t="str">
+        <x:v>Retained</x:v>
+      </x:c>
+      <x:c r="D87" s="35" t="str">
+        <x:v>Official Crown global-locations page</x:v>
+      </x:c>
+      <x:c r="E87" s="35" t="str">
+        <x:v>Official city-level point</x:v>
+      </x:c>
+      <x:c r="F87" s="36" t="str">
+        <x:v>Matches Crown's published city coordinate; not verified as an exact building point</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88">
+      <x:c r="A88" s="34" t="n">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="B88" s="35" t="str">
+        <x:v>Crown - Calgary</x:v>
+      </x:c>
+      <x:c r="C88" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D88" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E88" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F88" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89">
+      <x:c r="A89" s="34" t="n">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="B89" s="35" t="str">
+        <x:v>Crown - Halton Hills</x:v>
+      </x:c>
+      <x:c r="C89" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D89" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E89" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F89" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90">
+      <x:c r="A90" s="34" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="B90" s="35" t="str">
+        <x:v>Crown - Toronto</x:v>
+      </x:c>
+      <x:c r="C90" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D90" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E90" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F90" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91">
+      <x:c r="A91" s="34" t="n">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="B91" s="35" t="str">
+        <x:v>O-I - Auburn</x:v>
+      </x:c>
+      <x:c r="C91" s="35" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D91" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E91" s="35" t="str">
+        <x:v>Exact address match</x:v>
+      </x:c>
+      <x:c r="F91" s="36" t="str">
+        <x:v>7134 COUNTY HOUSE RD, AUBURN, NY, 13021</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92">
+      <x:c r="A92" s="34" t="n">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="B92" s="35" t="str">
+        <x:v>O-I - Bowling Green</x:v>
+      </x:c>
+      <x:c r="C92" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D92" s="35" t="str">
+        <x:v>U.S. Census + OpenStreetMap fallback</x:v>
+      </x:c>
+      <x:c r="E92" s="35" t="str">
+        <x:v>No accepted match</x:v>
+      </x:c>
+      <x:c r="F92" s="36" t="str">
+        <x:v>Street address requires manual verification</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93">
+      <x:c r="A93" s="34" t="n">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="B93" s="35" t="str">
+        <x:v>O-I - Brockway</x:v>
+      </x:c>
+      <x:c r="C93" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D93" s="35" t="str">
+        <x:v>U.S. Census + OpenStreetMap fallback</x:v>
+      </x:c>
+      <x:c r="E93" s="35" t="str">
+        <x:v>No accepted match</x:v>
+      </x:c>
+      <x:c r="F93" s="36" t="str">
+        <x:v>Street address requires manual verification</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94">
+      <x:c r="A94" s="34" t="n">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="B94" s="35" t="str">
+        <x:v>O-I - Crenshaw</x:v>
+      </x:c>
+      <x:c r="C94" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D94" s="35" t="str">
+        <x:v>U.S. Census + OpenStreetMap fallback</x:v>
+      </x:c>
+      <x:c r="E94" s="35" t="str">
+        <x:v>No accepted match</x:v>
+      </x:c>
+      <x:c r="F94" s="36" t="str">
+        <x:v>Street address requires manual verification</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95">
+      <x:c r="A95" s="34" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="B95" s="35" t="str">
+        <x:v>O-I - Danville</x:v>
+      </x:c>
+      <x:c r="C95" s="35" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="D95" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E95" s="35" t="str">
+        <x:v>Non-exact match</x:v>
+      </x:c>
+      <x:c r="F95" s="36" t="str">
+        <x:v>29 GLASSBLOWER LN, RINGGOLD, VA, 24586</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96">
+      <x:c r="A96" s="34" t="n">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="B96" s="35" t="str">
+        <x:v>O-I - Kalama</x:v>
+      </x:c>
+      <x:c r="C96" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D96" s="35" t="str">
+        <x:v>U.S. Census + OpenStreetMap fallback</x:v>
+      </x:c>
+      <x:c r="E96" s="35" t="str">
+        <x:v>No accepted match</x:v>
+      </x:c>
+      <x:c r="F96" s="36" t="str">
+        <x:v>Street address requires manual verification</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97">
+      <x:c r="A97" s="34" t="n">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="B97" s="35" t="str">
+        <x:v>O-I - Lapel</x:v>
+      </x:c>
+      <x:c r="C97" s="35" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="D97" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E97" s="35" t="str">
+        <x:v>Non-exact match</x:v>
+      </x:c>
+      <x:c r="F97" s="36" t="str">
+        <x:v>2481 BROOKSIDE RD, LAPEL, IN, 46051</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98">
+      <x:c r="A98" s="34" t="n">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="B98" s="35" t="str">
+        <x:v>O-I - Los Angeles</x:v>
+      </x:c>
+      <x:c r="C98" s="35" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="D98" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E98" s="35" t="str">
+        <x:v>Non-exact match</x:v>
+      </x:c>
+      <x:c r="F98" s="36" t="str">
+        <x:v>2901 FRUITLAND AVE, LOS ANGELES, CA, 90058</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99">
+      <x:c r="A99" s="34" t="n">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="B99" s="35" t="str">
+        <x:v>O-I - Muskogee</x:v>
+      </x:c>
+      <x:c r="C99" s="35" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D99" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E99" s="35" t="str">
+        <x:v>Exact address match</x:v>
+      </x:c>
+      <x:c r="F99" s="36" t="str">
+        <x:v>2401 OLD SHAWNEE RD, MUSKOGEE, OK, 74403</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100">
+      <x:c r="A100" s="34" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="B100" s="35" t="str">
+        <x:v>O-I - Toano</x:v>
+      </x:c>
+      <x:c r="C100" s="35" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="D100" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E100" s="35" t="str">
+        <x:v>Non-exact match</x:v>
+      </x:c>
+      <x:c r="F100" s="36" t="str">
+        <x:v>150 INDUSTRIAL BLVD, TOANO, VA, 23168</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101">
+      <x:c r="A101" s="34" t="n">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="B101" s="35" t="str">
+        <x:v>O-I - Tracy</x:v>
+      </x:c>
+      <x:c r="C101" s="35" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="D101" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E101" s="35" t="str">
+        <x:v>Non-exact match</x:v>
+      </x:c>
+      <x:c r="F101" s="36" t="str">
+        <x:v>14700 W SCHULTE RD, TRACY, CA, 95377</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102">
+      <x:c r="A102" s="34" t="n">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="B102" s="35" t="str">
+        <x:v>O-I - Windsor</x:v>
+      </x:c>
+      <x:c r="C102" s="35" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D102" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E102" s="35" t="str">
+        <x:v>Exact address match</x:v>
+      </x:c>
+      <x:c r="F102" s="36" t="str">
+        <x:v>11133 EASTMAN PARK DR, WINDSOR, CO, 80550</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103">
+      <x:c r="A103" s="34" t="n">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="B103" s="35" t="str">
+        <x:v>O-I - Winston-Salem</x:v>
+      </x:c>
+      <x:c r="C103" s="35" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D103" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E103" s="35" t="str">
+        <x:v>Exact address match</x:v>
+      </x:c>
+      <x:c r="F103" s="36" t="str">
+        <x:v>9698 OLD US HWY 52, LEXINGTON, NC, 27295</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104">
+      <x:c r="A104" s="34" t="n">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="B104" s="35" t="str">
+        <x:v>O-I - Zanesville</x:v>
+      </x:c>
+      <x:c r="C104" s="35" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="D104" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E104" s="35" t="str">
+        <x:v>Non-exact match</x:v>
+      </x:c>
+      <x:c r="F104" s="36" t="str">
+        <x:v>1700 S STATE ST, ZANESVILLE, OH, 43701</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="105">
+      <x:c r="A105" s="34" t="n">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="B105" s="35" t="str">
+        <x:v>O-I - Brampton</x:v>
+      </x:c>
+      <x:c r="C105" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D105" s="35" t="str">
+        <x:v>Not automatically matched</x:v>
+      </x:c>
+      <x:c r="E105" s="35" t="str">
+        <x:v>Street address pending</x:v>
+      </x:c>
+      <x:c r="F105" s="36" t="str">
+        <x:v>Requires manual verification or non-U.S. geocoder</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106">
+      <x:c r="A106" s="34" t="n">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="B106" s="35" t="str">
+        <x:v>O-I - Montreal</x:v>
+      </x:c>
+      <x:c r="C106" s="35" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D106" s="35" t="str">
+        <x:v>OpenStreetMap Nominatim (cached one-time lookup)</x:v>
+      </x:c>
+      <x:c r="E106" s="35" t="str">
+        <x:v>Exact facility / works</x:v>
+      </x:c>
+      <x:c r="F106" s="36" t="str">
+        <x:v>Owens-Illinois, 2376, Rue Wellington, Pointe-Saint-Charles, Le Sud-Ouest, Montréal, Agglomération de Montréal, Montréal (région administrative), Québec, H3K 1X6, Canada</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="107">
+      <x:c r="A107" s="34" t="n">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="B107" s="35" t="str">
+        <x:v>Aspire Bakeries - Alsip</x:v>
+      </x:c>
+      <x:c r="C107" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D107" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E107" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F107" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="108">
+      <x:c r="A108" s="34" t="n">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="B108" s="35" t="str">
+        <x:v>Aspire Bakeries - Anaheim</x:v>
+      </x:c>
+      <x:c r="C108" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D108" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E108" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F108" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="109">
+      <x:c r="A109" s="34" t="n">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="B109" s="35" t="str">
+        <x:v>Aspire Bakeries - Bolingbrook</x:v>
+      </x:c>
+      <x:c r="C109" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D109" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E109" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F109" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="110">
+      <x:c r="A110" s="34" t="n">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="B110" s="35" t="str">
+        <x:v>Aspire Bakeries - Chicago Heights</x:v>
+      </x:c>
+      <x:c r="C110" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D110" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E110" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F110" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="111">
+      <x:c r="A111" s="34" t="n">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="B111" s="35" t="str">
+        <x:v>Aspire Bakeries - Chaska</x:v>
+      </x:c>
+      <x:c r="C111" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D111" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E111" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F111" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="112">
+      <x:c r="A112" s="34" t="n">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="B112" s="35" t="str">
+        <x:v>Aspire Bakeries - Cayce</x:v>
+      </x:c>
+      <x:c r="C112" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D112" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E112" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F112" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="113">
+      <x:c r="A113" s="34" t="n">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="B113" s="35" t="str">
+        <x:v>Aspire Bakeries - Commerce</x:v>
+      </x:c>
+      <x:c r="C113" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D113" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E113" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F113" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="114">
+      <x:c r="A114" s="34" t="n">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="B114" s="35" t="str">
+        <x:v>Aspire Bakeries - Hazleton</x:v>
+      </x:c>
+      <x:c r="C114" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D114" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E114" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F114" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="115">
+      <x:c r="A115" s="34" t="n">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="B115" s="35" t="str">
+        <x:v>Aspire Bakeries - Swedesboro</x:v>
+      </x:c>
+      <x:c r="C115" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D115" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E115" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F115" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="116">
+      <x:c r="A116" s="34" t="n">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="B116" s="35" t="str">
+        <x:v>Aspire Bakeries - Van Nuys</x:v>
+      </x:c>
+      <x:c r="C116" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D116" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E116" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F116" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="117">
+      <x:c r="A117" s="34" t="n">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="B117" s="35" t="str">
+        <x:v>Bimbo Bakeries USA - Mattoon</x:v>
+      </x:c>
+      <x:c r="C117" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D117" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E117" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F117" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="118">
+      <x:c r="A118" s="34" t="n">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="B118" s="35" t="str">
+        <x:v>Bimbo Bakeries USA - Oxnard</x:v>
+      </x:c>
+      <x:c r="C118" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D118" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E118" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F118" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="119">
+      <x:c r="A119" s="34" t="n">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="B119" s="35" t="str">
+        <x:v>Bimbo Bakeries USA - Fort Worth</x:v>
+      </x:c>
+      <x:c r="C119" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D119" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E119" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F119" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="120">
+      <x:c r="A120" s="34" t="n">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="B120" s="35" t="str">
+        <x:v>Bimbo Bakeries USA - San Antonio</x:v>
+      </x:c>
+      <x:c r="C120" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D120" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E120" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F120" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="121">
+      <x:c r="A121" s="34" t="n">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="B121" s="35" t="str">
+        <x:v>Bimbo Bakeries USA - Rockwall</x:v>
+      </x:c>
+      <x:c r="C121" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D121" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E121" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F121" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="122">
+      <x:c r="A122" s="34" t="n">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="B122" s="35" t="str">
+        <x:v>Bimbo Bakeries USA - Denver</x:v>
+      </x:c>
+      <x:c r="C122" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D122" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E122" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F122" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="123">
+      <x:c r="A123" s="34" t="n">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="B123" s="35" t="str">
+        <x:v>Bimbo Bakeries USA - Phoenix</x:v>
+      </x:c>
+      <x:c r="C123" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D123" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E123" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F123" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="124">
+      <x:c r="A124" s="34" t="n">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="B124" s="35" t="str">
+        <x:v>Bimbo Bakeries USA - South San Francisco</x:v>
+      </x:c>
+      <x:c r="C124" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D124" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E124" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F124" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="125">
+      <x:c r="A125" s="34" t="n">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="B125" s="35" t="str">
+        <x:v>Bimbo Bakeries USA - Escondido</x:v>
+      </x:c>
+      <x:c r="C125" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D125" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E125" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F125" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="126">
+      <x:c r="A126" s="34" t="n">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="B126" s="35" t="str">
+        <x:v>Mondelez - Chicago</x:v>
+      </x:c>
+      <x:c r="C126" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D126" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E126" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F126" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="127">
+      <x:c r="A127" s="34" t="n">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="B127" s="35" t="str">
+        <x:v>Mondelez - Richmond</x:v>
+      </x:c>
+      <x:c r="C127" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D127" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E127" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F127" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="128">
+      <x:c r="A128" s="34" t="n">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="B128" s="35" t="str">
+        <x:v>Mondelez - Fair Lawn</x:v>
+      </x:c>
+      <x:c r="C128" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D128" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E128" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F128" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="129">
+      <x:c r="A129" s="34" t="n">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="B129" s="35" t="str">
+        <x:v>Mondelez - Portland</x:v>
+      </x:c>
+      <x:c r="C129" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D129" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E129" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F129" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="130">
+      <x:c r="A130" s="34" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="B130" s="35" t="str">
+        <x:v>Mondelez - Naperville</x:v>
+      </x:c>
+      <x:c r="C130" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D130" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E130" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F130" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="131">
+      <x:c r="A131" s="34" t="n">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="B131" s="35" t="str">
+        <x:v>Campbell's - Ashland</x:v>
+      </x:c>
+      <x:c r="C131" s="35" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D131" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E131" s="35" t="str">
+        <x:v>Exact address match</x:v>
+      </x:c>
+      <x:c r="F131" s="36" t="str">
+        <x:v>2041 CLAREMONT AVE, ASHLAND, OH, 44805</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="132">
+      <x:c r="A132" s="34" t="n">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="B132" s="35" t="str">
+        <x:v>Campbell's - Austin</x:v>
+      </x:c>
+      <x:c r="C132" s="35" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D132" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E132" s="35" t="str">
+        <x:v>Exact address match</x:v>
+      </x:c>
+      <x:c r="F132" s="36" t="str">
+        <x:v>200 MICHAEL ANGELO WAY, AUSTIN, TX, 78728</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="133">
+      <x:c r="A133" s="34" t="n">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="B133" s="35" t="str">
+        <x:v>Campbell's - Beloit</x:v>
+      </x:c>
+      <x:c r="C133" s="35" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D133" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E133" s="35" t="str">
+        <x:v>Exact address match</x:v>
+      </x:c>
+      <x:c r="F133" s="36" t="str">
+        <x:v>3150 KETTLE WAY, BELOIT, WI, 53511</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="134">
+      <x:c r="A134" s="34" t="n">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="B134" s="35" t="str">
+        <x:v>Campbell's - Bloomfield</x:v>
+      </x:c>
+      <x:c r="C134" s="35" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D134" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E134" s="35" t="str">
+        <x:v>Exact address match</x:v>
+      </x:c>
+      <x:c r="F134" s="36" t="str">
+        <x:v>1414 BLUE HILLS AVE, BLOOMFIELD, CT, 06002</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="135">
+      <x:c r="A135" s="34" t="n">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="B135" s="35" t="str">
+        <x:v>Campbell's - Charlotte</x:v>
+      </x:c>
+      <x:c r="C135" s="35" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D135" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E135" s="35" t="str">
+        <x:v>Exact address match</x:v>
+      </x:c>
+      <x:c r="F135" s="36" t="str">
+        <x:v>8600 SOUTH BLVD, CHARLOTTE, NC, 28273</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="136">
+      <x:c r="A136" s="34" t="n">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="B136" s="35" t="str">
+        <x:v>Campbell's - Denver</x:v>
+      </x:c>
+      <x:c r="C136" s="35" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D136" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E136" s="35" t="str">
+        <x:v>Exact address match</x:v>
+      </x:c>
+      <x:c r="F136" s="36" t="str">
+        <x:v>2195 N READING RD, DENVER, PA, 17517</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="137">
+      <x:c r="A137" s="34" t="n">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="B137" s="35" t="str">
+        <x:v>Campbell's - Dixon</x:v>
+      </x:c>
+      <x:c r="C137" s="35" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="D137" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E137" s="35" t="str">
+        <x:v>Non-exact match</x:v>
+      </x:c>
+      <x:c r="F137" s="36" t="str">
+        <x:v>8380 PEDRICK RD, DIXON, CA, 95620</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="138">
+      <x:c r="A138" s="34" t="n">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="B138" s="35" t="str">
+        <x:v>Campbell's - Downers Grove</x:v>
+      </x:c>
+      <x:c r="C138" s="35" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D138" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E138" s="35" t="str">
+        <x:v>Exact address match</x:v>
+      </x:c>
+      <x:c r="F138" s="36" t="str">
+        <x:v>230 2ND ST, DOWNERS GROVE, IL, 60515</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="139">
+      <x:c r="A139" s="34" t="n">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="B139" s="35" t="str">
+        <x:v>Campbell's - Downingtown</x:v>
+      </x:c>
+      <x:c r="C139" s="35" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D139" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E139" s="35" t="str">
+        <x:v>Exact address match</x:v>
+      </x:c>
+      <x:c r="F139" s="36" t="str">
+        <x:v>421 BOOT RD, DOWNINGTOWN, PA, 19335</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="140">
+      <x:c r="A140" s="34" t="n">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="B140" s="35" t="str">
+        <x:v>Campbell's - Franklin</x:v>
+      </x:c>
+      <x:c r="C140" s="35" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D140" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E140" s="35" t="str">
+        <x:v>Exact address match</x:v>
+      </x:c>
+      <x:c r="F140" s="36" t="str">
+        <x:v>4625 W OAKWOOD PARK DR, FRANKLIN, WI, 53132</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="141">
+      <x:c r="A141" s="34" t="n">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="B141" s="35" t="str">
+        <x:v>Campbell's - Goodyear</x:v>
+      </x:c>
+      <x:c r="C141" s="35" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D141" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E141" s="35" t="str">
+        <x:v>Exact address match</x:v>
+      </x:c>
+      <x:c r="F141" s="36" t="str">
+        <x:v>1200 N BULLARD AVE, GOODYEAR, AZ, 85338</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="142">
+      <x:c r="A142" s="34" t="n">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="B142" s="35" t="str">
+        <x:v>Campbell's - Hanover</x:v>
+      </x:c>
+      <x:c r="C142" s="35" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D142" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E142" s="35" t="str">
+        <x:v>Exact address match</x:v>
+      </x:c>
+      <x:c r="F142" s="36" t="str">
+        <x:v>1350 YORK ST, HANOVER, PA, 17331</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="143">
+      <x:c r="A143" s="34" t="n">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="B143" s="35" t="str">
+        <x:v>Campbell's - Hyannis</x:v>
+      </x:c>
+      <x:c r="C143" s="35" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D143" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E143" s="35" t="str">
+        <x:v>Exact address match</x:v>
+      </x:c>
+      <x:c r="F143" s="36" t="str">
+        <x:v>100 BREEDS HILL RD, HYANNIS, MA, 02601</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="144">
+      <x:c r="A144" s="34" t="n">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="B144" s="35" t="str">
+        <x:v>Campbell's - Jeffersonville</x:v>
+      </x:c>
+      <x:c r="C144" s="35" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D144" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E144" s="35" t="str">
+        <x:v>Exact address match</x:v>
+      </x:c>
+      <x:c r="F144" s="36" t="str">
+        <x:v>125 PEACELY ST, JEFFERSONVILLE, IN, 47130</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="145">
+      <x:c r="A145" s="34" t="n">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="B145" s="35" t="str">
+        <x:v>Campbell's - Lakeland</x:v>
+      </x:c>
+      <x:c r="C145" s="35" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D145" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E145" s="35" t="str">
+        <x:v>Exact address match</x:v>
+      </x:c>
+      <x:c r="F145" s="36" t="str">
+        <x:v>2222 INTERSTATE DR, LAKELAND, FL, 33805</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="146">
+      <x:c r="A146" s="34" t="n">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="B146" s="35" t="str">
+        <x:v>Campbell's - Maxton</x:v>
+      </x:c>
+      <x:c r="C146" s="35" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="D146" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E146" s="35" t="str">
+        <x:v>Non-exact match</x:v>
+      </x:c>
+      <x:c r="F146" s="36" t="str">
+        <x:v>2120 STATE HWY 71 N, MAXTON, NC, 28364</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="147">
+      <x:c r="A147" s="34" t="n">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="B147" s="35" t="str">
+        <x:v>Campbell's - Milwaukee</x:v>
+      </x:c>
+      <x:c r="C147" s="35" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D147" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E147" s="35" t="str">
+        <x:v>Exact address match</x:v>
+      </x:c>
+      <x:c r="F147" s="36" t="str">
+        <x:v>500 W EDGERTON AVE, MILWAUKEE, WI, 53207</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="148">
+      <x:c r="A148" s="34" t="n">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="B148" s="35" t="str">
+        <x:v>Campbell's - Napoleon</x:v>
+      </x:c>
+      <x:c r="C148" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D148" s="35" t="str">
+        <x:v>U.S. Census + OpenStreetMap fallback</x:v>
+      </x:c>
+      <x:c r="E148" s="35" t="str">
+        <x:v>No accepted match</x:v>
+      </x:c>
+      <x:c r="F148" s="36" t="str">
+        <x:v>Street address requires manual verification</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="149">
+      <x:c r="A149" s="34" t="n">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="B149" s="35" t="str">
+        <x:v>Campbell's - Paris</x:v>
+      </x:c>
+      <x:c r="C149" s="35" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="D149" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E149" s="35" t="str">
+        <x:v>Non-exact match</x:v>
+      </x:c>
+      <x:c r="F149" s="36" t="str">
+        <x:v>500 NW LOOP 286, PARIS, TX, 75460</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="150">
+      <x:c r="A150" s="34" t="n">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="B150" s="35" t="str">
+        <x:v>Campbell's - Richmond</x:v>
+      </x:c>
+      <x:c r="C150" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D150" s="35" t="str">
+        <x:v>U.S. Census + OpenStreetMap fallback</x:v>
+      </x:c>
+      <x:c r="E150" s="35" t="str">
+        <x:v>No accepted match</x:v>
+      </x:c>
+      <x:c r="F150" s="36" t="str">
+        <x:v>Street address requires manual verification</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="151">
+      <x:c r="A151" s="34" t="n">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="B151" s="35" t="str">
+        <x:v>Campbell's - Salem</x:v>
+      </x:c>
+      <x:c r="C151" s="35" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D151" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E151" s="35" t="str">
+        <x:v>Exact address match</x:v>
+      </x:c>
+      <x:c r="F151" s="36" t="str">
+        <x:v>3125 KETTLE CT SE, SALEM, OR, 97301</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="152">
+      <x:c r="A152" s="34" t="n">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="B152" s="35" t="str">
+        <x:v>Campbell's - Stockton</x:v>
+      </x:c>
+      <x:c r="C152" s="35" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D152" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E152" s="35" t="str">
+        <x:v>Exact address match</x:v>
+      </x:c>
+      <x:c r="F152" s="36" t="str">
+        <x:v>750 INDUSTRIAL DR, STOCKTON, CA, 95206</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="153">
+      <x:c r="A153" s="34" t="n">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="B153" s="35" t="str">
+        <x:v>Campbell's - Tualatin</x:v>
+      </x:c>
+      <x:c r="C153" s="35" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D153" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E153" s="35" t="str">
+        <x:v>Exact address match</x:v>
+      </x:c>
+      <x:c r="F153" s="36" t="str">
+        <x:v>19480 SW 97TH AVE, TUALATIN, OR, 97062</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="154">
+      <x:c r="A154" s="34" t="n">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="B154" s="35" t="str">
+        <x:v>Campbell's - Willard</x:v>
+      </x:c>
+      <x:c r="C154" s="35" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="D154" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E154" s="35" t="str">
+        <x:v>Non-exact match</x:v>
+      </x:c>
+      <x:c r="F154" s="36" t="str">
+        <x:v>3320 STATE RTE 103, WILLARD, OH, 44890</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="155">
+      <x:c r="A155" s="34" t="n">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="B155" s="35" t="str">
+        <x:v>Conagra - Indianapolis - Bakery plant</x:v>
+      </x:c>
+      <x:c r="C155" s="35" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D155" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E155" s="35" t="str">
+        <x:v>Exact address match</x:v>
+      </x:c>
+      <x:c r="F155" s="36" t="str">
+        <x:v>7579 GEORGETOWN RD, INDIANAPOLIS, IN, 46268</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="156">
+      <x:c r="A156" s="34" t="n">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="B156" s="35" t="str">
+        <x:v>Conagra - Indianapolis - Reddi-Wip / table spreads plant</x:v>
+      </x:c>
+      <x:c r="C156" s="35" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D156" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E156" s="35" t="str">
+        <x:v>Exact address match</x:v>
+      </x:c>
+      <x:c r="F156" s="36" t="str">
+        <x:v>4300 W 62ND ST, INDIANAPOLIS, IN, 46268</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="157">
+      <x:c r="A157" s="34" t="n">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="B157" s="35" t="str">
+        <x:v>Conagra - Louisville - Foodservice plant</x:v>
+      </x:c>
+      <x:c r="C157" s="35" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D157" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E157" s="35" t="str">
+        <x:v>Exact address match</x:v>
+      </x:c>
+      <x:c r="F157" s="36" t="str">
+        <x:v>12650 WESTPORT RD, LOUISVILLE, KY, 40245</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="158">
+      <x:c r="A158" s="34" t="n">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="B158" s="35" t="str">
+        <x:v>Conagra - Troy - Food manufacturing plant</x:v>
+      </x:c>
+      <x:c r="C158" s="35" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D158" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E158" s="35" t="str">
+        <x:v>Exact address match</x:v>
+      </x:c>
+      <x:c r="F158" s="36" t="str">
+        <x:v>801 DYE MILL RD, TROY, OH, 45373</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="159">
+      <x:c r="A159" s="34" t="n">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="B159" s="35" t="str">
+        <x:v>Nestlé - Anderson</x:v>
+      </x:c>
+      <x:c r="C159" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D159" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E159" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F159" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="160">
+      <x:c r="A160" s="34" t="n">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="B160" s="35" t="str">
+        <x:v>Nestlé - Burlington</x:v>
+      </x:c>
+      <x:c r="C160" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D160" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E160" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F160" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="161">
+      <x:c r="A161" s="34" t="n">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="B161" s="35" t="str">
+        <x:v>Nestlé - Cleveland</x:v>
+      </x:c>
+      <x:c r="C161" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D161" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E161" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F161" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="162">
+      <x:c r="A162" s="34" t="n">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="B162" s="35" t="str">
+        <x:v>Nestlé - Davenport</x:v>
+      </x:c>
+      <x:c r="C162" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D162" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E162" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F162" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="163">
+      <x:c r="A163" s="34" t="n">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="B163" s="35" t="str">
+        <x:v>Nestlé - Eden</x:v>
+      </x:c>
+      <x:c r="C163" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D163" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E163" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F163" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="164">
+      <x:c r="A164" s="34" t="n">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="B164" s="35" t="str">
+        <x:v>Nestlé - Hartwell</x:v>
+      </x:c>
+      <x:c r="C164" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D164" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E164" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F164" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="165">
+      <x:c r="A165" s="34" t="n">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="B165" s="35" t="str">
+        <x:v>Nestlé - St. Louis</x:v>
+      </x:c>
+      <x:c r="C165" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D165" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E165" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F165" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="166">
+      <x:c r="A166" s="34" t="n">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="B166" s="35" t="str">
+        <x:v>Nestlé - Solon</x:v>
+      </x:c>
+      <x:c r="C166" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D166" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E166" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F166" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="167">
+      <x:c r="A167" s="34" t="n">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="B167" s="35" t="str">
+        <x:v>Silgan - Antioch</x:v>
+      </x:c>
+      <x:c r="C167" s="35" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D167" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E167" s="35" t="str">
+        <x:v>Exact address match</x:v>
+      </x:c>
+      <x:c r="F167" s="36" t="str">
+        <x:v>2200 WILBUR AVE, ANTIOCH, CA, 94509</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="168">
+      <x:c r="A168" s="34" t="n">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="B168" s="35" t="str">
+        <x:v>Silgan - Modesto</x:v>
+      </x:c>
+      <x:c r="C168" s="35" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D168" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E168" s="35" t="str">
+        <x:v>Exact address match</x:v>
+      </x:c>
+      <x:c r="F168" s="36" t="str">
+        <x:v>4210 YOSEMITE BLVD, MODESTO, CA, 95357</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="169">
+      <x:c r="A169" s="34" t="n">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="B169" s="35" t="str">
+        <x:v>Silgan - Modesto</x:v>
+      </x:c>
+      <x:c r="C169" s="35" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D169" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E169" s="35" t="str">
+        <x:v>Exact address match</x:v>
+      </x:c>
+      <x:c r="F169" s="36" t="str">
+        <x:v>430 DOHERTY AVE, MODESTO, CA, 95354</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="170">
+      <x:c r="A170" s="34" t="n">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="B170" s="35" t="str">
+        <x:v>Silgan - Modesto</x:v>
+      </x:c>
+      <x:c r="C170" s="35" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D170" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E170" s="35" t="str">
+        <x:v>Exact address match</x:v>
+      </x:c>
+      <x:c r="F170" s="36" t="str">
+        <x:v>567 S RIVERSIDE DR, MODESTO, CA, 95354</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="171">
+      <x:c r="A171" s="34" t="n">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="B171" s="35" t="str">
+        <x:v>Silgan - Riverbank</x:v>
+      </x:c>
+      <x:c r="C171" s="35" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D171" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E171" s="35" t="str">
+        <x:v>Exact address match</x:v>
+      </x:c>
+      <x:c r="F171" s="36" t="str">
+        <x:v>3250 PATTERSON RD, RIVERBANK, CA, 95367</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="172">
+      <x:c r="A172" s="34" t="n">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="B172" s="35" t="str">
+        <x:v>Silgan - Sacramento</x:v>
+      </x:c>
+      <x:c r="C172" s="35" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D172" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E172" s="35" t="str">
+        <x:v>Exact address match</x:v>
+      </x:c>
+      <x:c r="F172" s="36" t="str">
+        <x:v>6200 FRANKLIN BLVD, SACRAMENTO, CA, 95824</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="173">
+      <x:c r="A173" s="34" t="n">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="B173" s="35" t="str">
+        <x:v>Silgan - Hoopeston</x:v>
+      </x:c>
+      <x:c r="C173" s="35" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D173" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E173" s="35" t="str">
+        <x:v>Exact address match</x:v>
+      </x:c>
+      <x:c r="F173" s="36" t="str">
+        <x:v>324 W MAIN ST, HOOPESTON, IL, 60942</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="174">
+      <x:c r="A174" s="34" t="n">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="B174" s="35" t="str">
+        <x:v>Silgan - Rochelle</x:v>
+      </x:c>
+      <x:c r="C174" s="35" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D174" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E174" s="35" t="str">
+        <x:v>Exact address match</x:v>
+      </x:c>
+      <x:c r="F174" s="36" t="str">
+        <x:v>400 N 15TH ST, ROCHELLE, IL, 61068</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="175">
+      <x:c r="A175" s="34" t="n">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="B175" s="35" t="str">
+        <x:v>Silgan - Hammond</x:v>
+      </x:c>
+      <x:c r="C175" s="35" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D175" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E175" s="35" t="str">
+        <x:v>Exact address match</x:v>
+      </x:c>
+      <x:c r="F175" s="36" t="str">
+        <x:v>2501 165TH ST, HAMMOND, IN, 46320</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="176">
+      <x:c r="A176" s="34" t="n">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="B176" s="35" t="str">
+        <x:v>Silgan - Burlington</x:v>
+      </x:c>
+      <x:c r="C176" s="35" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D176" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E176" s="35" t="str">
+        <x:v>Exact address match</x:v>
+      </x:c>
+      <x:c r="F176" s="36" t="str">
+        <x:v>3725 DIVISION ST, BURLINGTON, IA, 52601</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="177">
+      <x:c r="A177" s="34" t="n">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="B177" s="35" t="str">
+        <x:v>Silgan - Fort Dodge</x:v>
+      </x:c>
+      <x:c r="C177" s="35" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D177" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E177" s="35" t="str">
+        <x:v>Exact address match</x:v>
+      </x:c>
+      <x:c r="F177" s="36" t="str">
+        <x:v>3591 MAPLE DR, FORT DODGE, IA, 50501</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="178">
+      <x:c r="A178" s="34" t="n">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="B178" s="35" t="str">
+        <x:v>Silgan - Fort Madison</x:v>
+      </x:c>
+      <x:c r="C178" s="35" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D178" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E178" s="35" t="str">
+        <x:v>Exact address match</x:v>
+      </x:c>
+      <x:c r="F178" s="36" t="str">
+        <x:v>2326 263RD AVE, FORT MADISON, IA, 52627</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="179">
+      <x:c r="A179" s="34" t="n">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="B179" s="35" t="str">
+        <x:v>Silgan - Savage</x:v>
+      </x:c>
+      <x:c r="C179" s="35" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="D179" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E179" s="35" t="str">
+        <x:v>Non-exact match</x:v>
+      </x:c>
+      <x:c r="F179" s="36" t="str">
+        <x:v>12130 LYNN AVE, SAVAGE, MN, 55378</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="180">
+      <x:c r="A180" s="34" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="B180" s="35" t="str">
+        <x:v>Silgan - St. Joseph</x:v>
+      </x:c>
+      <x:c r="C180" s="35" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D180" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E180" s="35" t="str">
+        <x:v>Exact address match</x:v>
+      </x:c>
+      <x:c r="F180" s="36" t="str">
+        <x:v>2115 SW LOWER LAKE RD, SAINT JOSEPH, MO, 64504</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="181">
+      <x:c r="A181" s="34" t="n">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="B181" s="35" t="str">
+        <x:v>Silgan - Edison</x:v>
+      </x:c>
+      <x:c r="C181" s="35" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D181" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E181" s="35" t="str">
+        <x:v>Exact address match</x:v>
+      </x:c>
+      <x:c r="F181" s="36" t="str">
+        <x:v>135 NATIONAL RD, EDISON, NJ, 08817</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="182">
+      <x:c r="A182" s="34" t="n">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="B182" s="35" t="str">
+        <x:v>Silgan - Maxton</x:v>
+      </x:c>
+      <x:c r="C182" s="35" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="D182" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E182" s="35" t="str">
+        <x:v>Non-exact match</x:v>
+      </x:c>
+      <x:c r="F182" s="36" t="str">
+        <x:v>2120 STATE HWY 71 N, MAXTON, NC, 28364</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="183">
+      <x:c r="A183" s="34" t="n">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="B183" s="35" t="str">
+        <x:v>Silgan - Napoleon</x:v>
+      </x:c>
+      <x:c r="C183" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D183" s="35" t="str">
+        <x:v>U.S. Census + OpenStreetMap fallback</x:v>
+      </x:c>
+      <x:c r="E183" s="35" t="str">
+        <x:v>No accepted match</x:v>
+      </x:c>
+      <x:c r="F183" s="36" t="str">
+        <x:v>Street address requires manual verification</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="184">
+      <x:c r="A184" s="34" t="n">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="B184" s="35" t="str">
+        <x:v>Silgan - Breinigsville</x:v>
+      </x:c>
+      <x:c r="C184" s="35" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D184" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E184" s="35" t="str">
+        <x:v>Exact address match</x:v>
+      </x:c>
+      <x:c r="F184" s="36" t="str">
+        <x:v>8201 INDUSTRIAL BLVD, BREINIGSVILLE, PA, 18031</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="185">
+      <x:c r="A185" s="34" t="n">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="B185" s="35" t="str">
+        <x:v>Silgan - Lancaster</x:v>
+      </x:c>
+      <x:c r="C185" s="35" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D185" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E185" s="35" t="str">
+        <x:v>Exact address match</x:v>
+      </x:c>
+      <x:c r="F185" s="36" t="str">
+        <x:v>1531 CAMP CREEK RD, LANCASTER, SC, 29720</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="186">
+      <x:c r="A186" s="34" t="n">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="B186" s="35" t="str">
+        <x:v>Silgan - Trenton</x:v>
+      </x:c>
+      <x:c r="C186" s="35" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D186" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E186" s="35" t="str">
+        <x:v>Exact address match</x:v>
+      </x:c>
+      <x:c r="F186" s="36" t="str">
+        <x:v>1226 MANUFACTURERS ROW, TRENTON, TN, 38382</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="187">
+      <x:c r="A187" s="34" t="n">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="B187" s="35" t="str">
+        <x:v>Silgan - Paris</x:v>
+      </x:c>
+      <x:c r="C187" s="35" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="D187" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E187" s="35" t="str">
+        <x:v>Non-exact match</x:v>
+      </x:c>
+      <x:c r="F187" s="36" t="str">
+        <x:v>500 NW LOOP 286, PARIS, TX, 75460</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="188">
+      <x:c r="A188" s="34" t="n">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="B188" s="35" t="str">
+        <x:v>Silgan - Toppenish</x:v>
+      </x:c>
+      <x:c r="C188" s="35" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D188" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E188" s="35" t="str">
+        <x:v>Exact address match</x:v>
+      </x:c>
+      <x:c r="F188" s="36" t="str">
+        <x:v>45 E 3RD AVE, TOPPENISH, WA, 98948</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="189">
+      <x:c r="A189" s="34" t="n">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="B189" s="35" t="str">
+        <x:v>Silgan - Kenosha</x:v>
+      </x:c>
+      <x:c r="C189" s="35" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="D189" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E189" s="35" t="str">
+        <x:v>Non-exact match</x:v>
+      </x:c>
+      <x:c r="F189" s="36" t="str">
+        <x:v>2602 128TH ST, KENOSHA, WI, 53158</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="190">
+      <x:c r="A190" s="34" t="n">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="B190" s="35" t="str">
+        <x:v>Silgan - Menomonee Falls</x:v>
+      </x:c>
+      <x:c r="C190" s="35" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D190" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E190" s="35" t="str">
+        <x:v>Exact address match</x:v>
+      </x:c>
+      <x:c r="F190" s="36" t="str">
+        <x:v>N90W14600 COMMERCE DR, MENOMONEE FALLS, WI, 53051</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="191">
+      <x:c r="A191" s="34" t="n">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="B191" s="35" t="str">
+        <x:v>Silgan - Menomonie</x:v>
+      </x:c>
+      <x:c r="C191" s="35" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="D191" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E191" s="35" t="str">
+        <x:v>Non-exact match</x:v>
+      </x:c>
+      <x:c r="F191" s="36" t="str">
+        <x:v>1416 INDIANHEAD DR E, MENOMONIE, WI, 54751</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="192">
+      <x:c r="A192" s="34" t="n">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="B192" s="35" t="str">
+        <x:v>Silgan - Oconomowoc</x:v>
+      </x:c>
+      <x:c r="C192" s="35" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D192" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E192" s="35" t="str">
+        <x:v>Exact address match</x:v>
+      </x:c>
+      <x:c r="F192" s="36" t="str">
+        <x:v>520 W 2ND ST, OCONOMOWOC, WI, 53066</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="193">
+      <x:c r="A193" s="34" t="n">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="B193" s="35" t="str">
+        <x:v>Silgan - Plover</x:v>
+      </x:c>
+      <x:c r="C193" s="35" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D193" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E193" s="35" t="str">
+        <x:v>Exact address match</x:v>
+      </x:c>
+      <x:c r="F193" s="36" t="str">
+        <x:v>1400 PLOVER RD, PLOVER, WI, 54467</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="194">
+      <x:c r="A194" s="34" t="n">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="B194" s="35" t="str">
+        <x:v>Silgan - Las Piedras</x:v>
+      </x:c>
+      <x:c r="C194" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D194" s="35" t="str">
+        <x:v>U.S. Census + OpenStreetMap fallback</x:v>
+      </x:c>
+      <x:c r="E194" s="35" t="str">
+        <x:v>No accepted match</x:v>
+      </x:c>
+      <x:c r="F194" s="36" t="str">
+        <x:v>Street address requires manual verification</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="195">
+      <x:c r="A195" s="34" t="n">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="B195" s="35" t="str">
+        <x:v>Kraft Heinz - Champaign</x:v>
+      </x:c>
+      <x:c r="C195" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D195" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E195" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F195" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="196">
+      <x:c r="A196" s="34" t="n">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="B196" s="35" t="str">
+        <x:v>Kraft Heinz - Fremont</x:v>
+      </x:c>
+      <x:c r="C196" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D196" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E196" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F196" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="197">
+      <x:c r="A197" s="34" t="n">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="B197" s="35" t="str">
+        <x:v>Kraft Heinz - Springfield</x:v>
+      </x:c>
+      <x:c r="C197" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D197" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E197" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F197" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="198">
+      <x:c r="A198" s="34" t="n">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="B198" s="35" t="str">
+        <x:v>Kraft Heinz - Garland</x:v>
+      </x:c>
+      <x:c r="C198" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D198" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E198" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F198" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="199">
+      <x:c r="A199" s="34" t="n">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="B199" s="35" t="str">
+        <x:v>Kraft Heinz - Dover</x:v>
+      </x:c>
+      <x:c r="C199" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D199" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E199" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F199" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="200">
+      <x:c r="A200" s="34" t="n">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="B200" s="35" t="str">
+        <x:v>Kraft Heinz - Newberry</x:v>
+      </x:c>
+      <x:c r="C200" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D200" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E200" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F200" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="201">
+      <x:c r="A201" s="34" t="n">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="B201" s="35" t="str">
+        <x:v>Kraft Heinz - Massillon</x:v>
+      </x:c>
+      <x:c r="C201" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D201" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E201" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F201" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="202">
+      <x:c r="A202" s="34" t="n">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="B202" s="35" t="str">
+        <x:v>Kraft Heinz - Jacksonville</x:v>
+      </x:c>
+      <x:c r="C202" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D202" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E202" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F202" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="203">
+      <x:c r="A203" s="34" t="n">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="B203" s="35" t="str">
+        <x:v>College Park Production Center</x:v>
+      </x:c>
+      <x:c r="C203" s="35" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D203" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E203" s="35" t="str">
+        <x:v>Exact address match</x:v>
+      </x:c>
+      <x:c r="F203" s="36" t="str">
+        <x:v>2355 SULLIVAN RD, COLLEGE PARK, GA, 30337</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="204">
+      <x:c r="A204" s="34" t="n">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="B204" s="35" t="str">
+        <x:v>Marietta Production Center</x:v>
+      </x:c>
+      <x:c r="C204" s="35" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D204" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E204" s="35" t="str">
+        <x:v>Exact address match</x:v>
+      </x:c>
+      <x:c r="F204" s="36" t="str">
+        <x:v>1091 INDUSTRIAL PARK DR, MARIETTA, GA, 30062</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="205">
+      <x:c r="A205" s="34" t="n">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="B205" s="35" t="str">
+        <x:v>Cleveland Production Center</x:v>
+      </x:c>
+      <x:c r="C205" s="35" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D205" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E205" s="35" t="str">
+        <x:v>Exact address match</x:v>
+      </x:c>
+      <x:c r="F205" s="36" t="str">
+        <x:v>174 REFRESHMENT LN SW, CLEVELAND, TN, 37311</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="206">
+      <x:c r="A206" s="34" t="n">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="B206" s="35" t="str">
+        <x:v>Montgomery Production Center</x:v>
+      </x:c>
+      <x:c r="C206" s="35" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D206" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E206" s="35" t="str">
+        <x:v>Exact address match</x:v>
+      </x:c>
+      <x:c r="F206" s="36" t="str">
+        <x:v>300 COCA-COLA RD, MONTGOMERY, AL, 36105</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="207">
+      <x:c r="A207" s="34" t="n">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="B207" s="35" t="str">
+        <x:v>Chattanooga Production Center</x:v>
+      </x:c>
+      <x:c r="C207" s="35" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D207" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E207" s="35" t="str">
+        <x:v>Exact address match</x:v>
+      </x:c>
+      <x:c r="F207" s="36" t="str">
+        <x:v>4000 AMNICOLA HWY, CHATTANOOGA, TN, 37406</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="208">
+      <x:c r="A208" s="34" t="n">
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="B208" s="35" t="str">
+        <x:v>New Orleans Production Center</x:v>
+      </x:c>
+      <x:c r="C208" s="35" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D208" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E208" s="35" t="str">
+        <x:v>Exact address match</x:v>
+      </x:c>
+      <x:c r="F208" s="36" t="str">
+        <x:v>5601 CITRUS BLVD, HARAHAN, LA, 70123</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="209">
+      <x:c r="A209" s="34" t="n">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="B209" s="35" t="str">
+        <x:v>Mobile Production Center</x:v>
+      </x:c>
+      <x:c r="C209" s="35" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D209" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E209" s="35" t="str">
+        <x:v>Exact address match</x:v>
+      </x:c>
+      <x:c r="F209" s="36" t="str">
+        <x:v>5300 COCA COLA RD, MOBILE, AL, 36619</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="210">
+      <x:c r="A210" s="34" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="B210" s="35" t="str">
+        <x:v>Baton Rouge Production Center</x:v>
+      </x:c>
+      <x:c r="C210" s="35" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D210" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E210" s="35" t="str">
+        <x:v>Exact address match</x:v>
+      </x:c>
+      <x:c r="F210" s="36" t="str">
+        <x:v>9696 PLANK RD, BATON ROUGE, LA, 70811</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="211">
+      <x:c r="A211" s="34" t="n">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="B211" s="35" t="str">
+        <x:v>Salt Lake City Plant</x:v>
+      </x:c>
+      <x:c r="C211" s="35" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D211" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E211" s="35" t="str">
+        <x:v>Exact address match</x:v>
+      </x:c>
+      <x:c r="F211" s="36" t="str">
+        <x:v>2269 S 3270 W, WEST VALLEY CITY, UT, 84119</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="212">
+      <x:c r="A212" s="34" t="n">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="B212" s="35" t="str">
+        <x:v>Tempe Plant</x:v>
+      </x:c>
+      <x:c r="C212" s="35" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="D212" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E212" s="35" t="str">
+        <x:v>Non-exact match</x:v>
+      </x:c>
+      <x:c r="F212" s="36" t="str">
+        <x:v>1850 W ELLIOT RD, TEMPE, AZ, 85284</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="213">
+      <x:c r="A213" s="34" t="n">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="B213" s="35" t="str">
+        <x:v>Denver Plant</x:v>
+      </x:c>
+      <x:c r="C213" s="35" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D213" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E213" s="35" t="str">
+        <x:v>Exact address match</x:v>
+      </x:c>
+      <x:c r="F213" s="36" t="str">
+        <x:v>2145 E 40TH AVE, DENVER, CO, 80205</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="214">
+      <x:c r="A214" s="34" t="n">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="B214" s="35" t="str">
+        <x:v>Wilsonville Plant</x:v>
+      </x:c>
+      <x:c r="C214" s="35" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D214" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E214" s="35" t="str">
+        <x:v>Exact address match</x:v>
+      </x:c>
+      <x:c r="F214" s="36" t="str">
+        <x:v>29900 SW KINSMAN RD, WILSONVILLE, OR, 97070</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="215">
+      <x:c r="A215" s="34" t="n">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="B215" s="35" t="str">
+        <x:v>Bellevue Plant</x:v>
+      </x:c>
+      <x:c r="C215" s="35" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D215" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E215" s="35" t="str">
+        <x:v>Exact address match</x:v>
+      </x:c>
+      <x:c r="F215" s="36" t="str">
+        <x:v>1150 124TH AVE NE, BELLEVUE, WA, 98005</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="216">
+      <x:c r="A216" s="34" t="n">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="B216" s="35" t="str">
+        <x:v>Fruitland Plant</x:v>
+      </x:c>
+      <x:c r="C216" s="35" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="D216" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E216" s="35" t="str">
+        <x:v>Non-exact match</x:v>
+      </x:c>
+      <x:c r="F216" s="36" t="str">
+        <x:v>500 SW 7TH ST, FRUITLAND, ID, 83619</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="217">
+      <x:c r="A217" s="34" t="n">
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="B217" s="35" t="str">
+        <x:v>Colorado Springs Manufacturing Facility</x:v>
+      </x:c>
+      <x:c r="C217" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D217" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E217" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F217" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="218">
+      <x:c r="A218" s="34" t="n">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="B218" s="35" t="str">
+        <x:v>Los Angeles Production Center</x:v>
+      </x:c>
+      <x:c r="C218" s="35" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D218" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E218" s="35" t="str">
+        <x:v>Exact address match</x:v>
+      </x:c>
+      <x:c r="F218" s="36" t="str">
+        <x:v>1334 S CENTRAL AVE, LOS ANGELES, CA, 90021</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="219">
+      <x:c r="A219" s="34" t="n">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="B219" s="35" t="str">
+        <x:v>San Leandro Production Center</x:v>
+      </x:c>
+      <x:c r="C219" s="35" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D219" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E219" s="35" t="str">
+        <x:v>Exact address match</x:v>
+      </x:c>
+      <x:c r="F219" s="36" t="str">
+        <x:v>14655 WICKS BLVD, SAN LEANDRO, CA, 94577</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="220">
+      <x:c r="A220" s="34" t="n">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="B220" s="35" t="str">
+        <x:v>Downey Production Center</x:v>
+      </x:c>
+      <x:c r="C220" s="35" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D220" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E220" s="35" t="str">
+        <x:v>Exact address match</x:v>
+      </x:c>
+      <x:c r="F220" s="36" t="str">
+        <x:v>8729 CLETA ST, DOWNEY, CA, 90241</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="221">
+      <x:c r="A221" s="34" t="n">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="B221" s="35" t="str">
+        <x:v>Grand Rapids Production Center</x:v>
+      </x:c>
+      <x:c r="C221" s="35" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D221" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E221" s="35" t="str">
+        <x:v>Exact address match</x:v>
+      </x:c>
+      <x:c r="F221" s="36" t="str">
+        <x:v>1440 BUTTERWORTH ST SW, GRAND RAPIDS, MI, 49504</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="222">
+      <x:c r="A222" s="34" t="n">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="B222" s="35" t="str">
+        <x:v>Niles Production Center</x:v>
+      </x:c>
+      <x:c r="C222" s="35" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D222" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E222" s="35" t="str">
+        <x:v>Exact address match</x:v>
+      </x:c>
+      <x:c r="F222" s="36" t="str">
+        <x:v>7400 N OAK PARK AVE, NILES, IL, 60714</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="223">
+      <x:c r="A223" s="34" t="n">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="B223" s="35" t="str">
+        <x:v>Alsip Production &amp; Distribution Center</x:v>
+      </x:c>
+      <x:c r="C223" s="35" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D223" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E223" s="35" t="str">
+        <x:v>Exact address match</x:v>
+      </x:c>
+      <x:c r="F223" s="36" t="str">
+        <x:v>12200 S LARAMIE AVE, ALSIP, IL, 60803</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="224">
+      <x:c r="A224" s="34" t="n">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="B224" s="35" t="str">
+        <x:v>Milwaukee Production &amp; Distribution Center</x:v>
+      </x:c>
+      <x:c r="C224" s="35" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D224" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E224" s="35" t="str">
+        <x:v>Exact address match</x:v>
+      </x:c>
+      <x:c r="F224" s="36" t="str">
+        <x:v>11800 W BROWN DEER RD, MILWAUKEE, WI, 53224</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="225">
+      <x:c r="A225" s="34" t="n">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="B225" s="35" t="str">
+        <x:v>Eagan Production &amp; Distribution Center</x:v>
+      </x:c>
+      <x:c r="C225" s="35" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D225" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E225" s="35" t="str">
+        <x:v>Exact address match</x:v>
+      </x:c>
+      <x:c r="F225" s="36" t="str">
+        <x:v>2750 EAGANDALE BLVD, EAGAN, MN, 55121</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="226">
+      <x:c r="A226" s="34" t="n">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="B226" s="35" t="str">
+        <x:v>Elmsford Production &amp; Distribution</x:v>
+      </x:c>
+      <x:c r="C226" s="35" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D226" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E226" s="35" t="str">
+        <x:v>Exact address match</x:v>
+      </x:c>
+      <x:c r="F226" s="36" t="str">
+        <x:v>115 FAIRVIEW PARK DR, ELMSFORD, NY, 10523</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="227">
+      <x:c r="A227" s="34" t="n">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="B227" s="35" t="str">
+        <x:v>Philadelphia Production, Sales &amp; Distribution</x:v>
+      </x:c>
+      <x:c r="C227" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D227" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E227" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F227" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="228">
+      <x:c r="A228" s="34" t="n">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="B228" s="35" t="str">
+        <x:v>Moorestown Production Plant</x:v>
+      </x:c>
+      <x:c r="C228" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D228" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E228" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F228" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="229">
+      <x:c r="A229" s="34" t="n">
+        <x:v>229</x:v>
+      </x:c>
+      <x:c r="B229" s="35" t="str">
+        <x:v>Atlantic Production Center</x:v>
+      </x:c>
+      <x:c r="C229" s="35" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D229" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E229" s="35" t="str">
+        <x:v>Exact address match</x:v>
+      </x:c>
+      <x:c r="F229" s="36" t="str">
+        <x:v>7 LOCUST ST, ATLANTIC, IA, 50022</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="230">
+      <x:c r="A230" s="34" t="n">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="B230" s="35" t="str">
+        <x:v>Olathe Production Campus</x:v>
+      </x:c>
+      <x:c r="C230" s="35" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D230" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E230" s="35" t="str">
+        <x:v>Exact address match</x:v>
+      </x:c>
+      <x:c r="F230" s="36" t="str">
+        <x:v>17100 S HEDGE LN, OLATHE, KS, 66062</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="231">
+      <x:c r="A231" s="34" t="n">
+        <x:v>231</x:v>
+      </x:c>
+      <x:c r="B231" s="35" t="str">
+        <x:v>Snyder Production Center</x:v>
+      </x:c>
+      <x:c r="C231" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D231" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E231" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F231" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="232">
+      <x:c r="A232" s="34" t="n">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="B232" s="35" t="str">
+        <x:v>Sandston Manufacturing Facility</x:v>
+      </x:c>
+      <x:c r="C232" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D232" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E232" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F232" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="233">
+      <x:c r="A233" s="34" t="n">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="B233" s="35" t="str">
+        <x:v>Silver Spring Production Facility</x:v>
+      </x:c>
+      <x:c r="C233" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D233" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E233" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F233" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="234">
+      <x:c r="A234" s="34" t="n">
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="B234" s="35" t="str">
+        <x:v>Baltimore Production Center</x:v>
+      </x:c>
+      <x:c r="C234" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D234" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E234" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F234" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="235">
+      <x:c r="A235" s="34" t="n">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="B235" s="35" t="str">
+        <x:v>Indianapolis Manufacturing Facility</x:v>
+      </x:c>
+      <x:c r="C235" s="35" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D235" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E235" s="35" t="str">
+        <x:v>Exact address match</x:v>
+      </x:c>
+      <x:c r="F235" s="36" t="str">
+        <x:v>5000 W 25TH ST, INDIANAPOLIS, IN, 46224</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="236">
+      <x:c r="A236" s="34" t="n">
+        <x:v>236</x:v>
+      </x:c>
+      <x:c r="B236" s="35" t="str">
+        <x:v>Portland Manufacturing Facility</x:v>
+      </x:c>
+      <x:c r="C236" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D236" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E236" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F236" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="237">
+      <x:c r="A237" s="34" t="n">
+        <x:v>237</x:v>
+      </x:c>
+      <x:c r="B237" s="35" t="str">
+        <x:v>Cincinnati Manufacturing Facility</x:v>
+      </x:c>
+      <x:c r="C237" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D237" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E237" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F237" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="238">
+      <x:c r="A238" s="34" t="n">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="B238" s="35" t="str">
+        <x:v>Twinsburg Manufacturing Facility</x:v>
+      </x:c>
+      <x:c r="C238" s="35" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D238" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E238" s="35" t="str">
+        <x:v>Exact address match</x:v>
+      </x:c>
+      <x:c r="F238" s="36" t="str">
+        <x:v>1882 HIGHLAND RD, TWINSBURG, OH, 44087</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="239">
+      <x:c r="A239" s="34" t="n">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="B239" s="35" t="str">
+        <x:v>West Memphis Manufacturing Facility</x:v>
+      </x:c>
+      <x:c r="C239" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D239" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E239" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F239" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="240">
+      <x:c r="A240" s="34" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="B240" s="35" t="str">
+        <x:v>Memphis Manufacturing Facility</x:v>
+      </x:c>
+      <x:c r="C240" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D240" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E240" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F240" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="241">
+      <x:c r="A241" s="34" t="n">
+        <x:v>241</x:v>
+      </x:c>
+      <x:c r="B241" s="35" t="str">
+        <x:v>Garner Production Facility</x:v>
+      </x:c>
+      <x:c r="C241" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D241" s="35" t="str">
+        <x:v>U.S. Census + OpenStreetMap fallback</x:v>
+      </x:c>
+      <x:c r="E241" s="35" t="str">
+        <x:v>No accepted match</x:v>
+      </x:c>
+      <x:c r="F241" s="36" t="str">
+        <x:v>Street address requires manual verification</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="242">
+      <x:c r="A242" s="34" t="n">
+        <x:v>242</x:v>
+      </x:c>
+      <x:c r="B242" s="35" t="str">
+        <x:v>Winston-Salem Production Facility</x:v>
+      </x:c>
+      <x:c r="C242" s="35" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D242" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E242" s="35" t="str">
+        <x:v>Exact address match</x:v>
+      </x:c>
+      <x:c r="F242" s="36" t="str">
+        <x:v>3425 MYER LEE DR, WINSTON SALEM, NC, 27101</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="243">
+      <x:c r="A243" s="34" t="n">
+        <x:v>243</x:v>
+      </x:c>
+      <x:c r="B243" s="35" t="str">
+        <x:v>Western Optimized Warehouse (WOW) Production Facility</x:v>
+      </x:c>
+      <x:c r="C243" s="35" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D243" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E243" s="35" t="str">
+        <x:v>Exact address match</x:v>
+      </x:c>
+      <x:c r="F243" s="36" t="str">
+        <x:v>390 BUS PARK DR, WINSTON SALEM, NC, 27107</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="244">
+      <x:c r="A244" s="34" t="n">
+        <x:v>244</x:v>
+      </x:c>
+      <x:c r="B244" s="35" t="str">
+        <x:v>PBV Fourth Production Facility - identity pending</x:v>
+      </x:c>
+      <x:c r="C244" s="35" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D244" s="35" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E244" s="35" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F244" s="36" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="245">
+      <x:c r="A245" s="34" t="n">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="B245" s="35" t="str">
+        <x:v>Franklin Furnace Production Facility</x:v>
+      </x:c>
+      <x:c r="C245" s="35" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D245" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E245" s="35" t="str">
+        <x:v>Exact address match</x:v>
+      </x:c>
+      <x:c r="F245" s="36" t="str">
+        <x:v>4587 GALLIA PIKE, FRANKLIN FURNACE, OH, 45629</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="246">
+      <x:c r="A246" s="34" t="n">
+        <x:v>246</x:v>
+      </x:c>
+      <x:c r="B246" s="35" t="str">
+        <x:v>Hamilton Production Facility</x:v>
+      </x:c>
+      <x:c r="C246" s="35" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D246" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E246" s="35" t="str">
+        <x:v>Exact address match</x:v>
+      </x:c>
+      <x:c r="F246" s="36" t="str">
+        <x:v>2580 BOBMEYER RD, HAMILTON, OH, 45015</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="247">
+      <x:c r="A247" s="34" t="n">
+        <x:v>247</x:v>
+      </x:c>
+      <x:c r="B247" s="35" t="str">
+        <x:v>Maysville Production Facility</x:v>
+      </x:c>
+      <x:c r="C247" s="35" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D247" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E247" s="35" t="str">
+        <x:v>Exact address match</x:v>
+      </x:c>
+      <x:c r="F247" s="36" t="str">
+        <x:v>1125 PROGRESS WAY, MAYSVILLE, KY, 41056</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="248">
+      <x:c r="A248" s="34" t="n">
+        <x:v>248</x:v>
+      </x:c>
+      <x:c r="B248" s="35" t="str">
+        <x:v>Zanesville Production Facility</x:v>
+      </x:c>
+      <x:c r="C248" s="35" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D248" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E248" s="35" t="str">
+        <x:v>Exact address match</x:v>
+      </x:c>
+      <x:c r="F248" s="36" t="str">
+        <x:v>336 N 6TH ST, ZANESVILLE, OH, 43701</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="249">
+      <x:c r="A249" s="34" t="n">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="B249" s="35" t="str">
+        <x:v>Columbus Operations / Production Campus</x:v>
+      </x:c>
+      <x:c r="C249" s="35" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D249" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E249" s="35" t="str">
+        <x:v>Exact address match</x:v>
+      </x:c>
+      <x:c r="F249" s="36" t="str">
+        <x:v>1241 GIBBARD AVE, COLUMBUS, OH, 43219</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="250">
+      <x:c r="A250" s="34" t="n">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="B250" s="35" t="str">
+        <x:v>Watertown Filling Plant</x:v>
+      </x:c>
+      <x:c r="C250" s="35" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D250" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E250" s="35" t="str">
+        <x:v>Exact address match</x:v>
+      </x:c>
+      <x:c r="F250" s="36" t="str">
+        <x:v>860 WEST ST, WATERTOWN, WI, 53094</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="251">
+      <x:c r="A251" s="34" t="n">
+        <x:v>251</x:v>
+      </x:c>
+      <x:c r="B251" s="35" t="str">
+        <x:v>Dyersburg Filling Plant</x:v>
+      </x:c>
+      <x:c r="C251" s="35" t="str">
+        <x:v>Pending review</x:v>
+      </x:c>
+      <x:c r="D251" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E251" s="35" t="str">
+        <x:v>Non-exact match</x:v>
+      </x:c>
+      <x:c r="F251" s="36" t="str">
+        <x:v>2918 US HWY 51, DYERSBURG, TN, 38024</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="252">
+      <x:c r="A252" s="34" t="n">
+        <x:v>252</x:v>
+      </x:c>
+      <x:c r="B252" s="35" t="str">
+        <x:v>Hattiesburg Filling Plant</x:v>
+      </x:c>
+      <x:c r="C252" s="35" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D252" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E252" s="35" t="str">
+        <x:v>Exact address match</x:v>
+      </x:c>
+      <x:c r="F252" s="36" t="str">
+        <x:v>2 W L RUNNELS IND DR, HATTIESBURG, MS, 39401</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="253">
+      <x:c r="A253" s="34" t="n">
+        <x:v>253</x:v>
+      </x:c>
+      <x:c r="B253" s="35" t="str">
+        <x:v>La Crosse Filling Plant</x:v>
+      </x:c>
+      <x:c r="C253" s="35" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D253" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E253" s="35" t="str">
+        <x:v>Exact address match</x:v>
+      </x:c>
+      <x:c r="F253" s="36" t="str">
+        <x:v>3239 AIRPORT DR, LA CROSSE, WI, 54603</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="254">
+      <x:c r="A254" s="34" t="n">
+        <x:v>254</x:v>
+      </x:c>
+      <x:c r="B254" s="35" t="str">
+        <x:v>Mankato Filling Plant</x:v>
+      </x:c>
+      <x:c r="C254" s="35" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D254" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E254" s="35" t="str">
+        <x:v>Exact address match</x:v>
+      </x:c>
+      <x:c r="F254" s="36" t="str">
+        <x:v>1707 TOWER BLVD, NORTH MANKATO, MN, 56003</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="255">
+      <x:c r="A255" s="34" t="n">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="B255" s="35" t="str">
+        <x:v>Norfolk Filling Plant</x:v>
+      </x:c>
+      <x:c r="C255" s="35" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D255" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E255" s="35" t="str">
+        <x:v>Exact address match</x:v>
+      </x:c>
+      <x:c r="F255" s="36" t="str">
+        <x:v>1400 TA HA ZOUKA RD, NORFOLK, NE, 68701</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="256">
+      <x:c r="A256" s="34" t="n">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="B256" s="35" t="str">
+        <x:v>Quincy Filling Plant</x:v>
+      </x:c>
+      <x:c r="C256" s="35" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D256" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E256" s="35" t="str">
+        <x:v>Exact address match</x:v>
+      </x:c>
+      <x:c r="F256" s="36" t="str">
+        <x:v>2400 N 30TH ST, QUINCY, IL, 62301</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="257">
+      <x:c r="A257" s="34" t="n">
+        <x:v>257</x:v>
+      </x:c>
+      <x:c r="B257" s="35" t="str">
+        <x:v>Birmingham Manufacturing / Bottling Facility</x:v>
+      </x:c>
+      <x:c r="C257" s="35" t="str">
+        <x:v>Added</x:v>
+      </x:c>
+      <x:c r="D257" s="35" t="str">
+        <x:v>U.S. Census Geocoder, benchmark 4</x:v>
+      </x:c>
+      <x:c r="E257" s="35" t="str">
+        <x:v>Exact address match</x:v>
+      </x:c>
+      <x:c r="F257" s="36" t="str">
+        <x:v>800 LAKESHORE PKWY, BIRMINGHAM, AL, 35211</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="258">
+      <x:c r="A258" s="37" t="n">
+        <x:v>258</x:v>
+      </x:c>
+      <x:c r="B258" s="38" t="str">
+        <x:v>Stone Mountain / Atlanta Beverage Plant</x:v>
+      </x:c>
+      <x:c r="C258" s="38" t="str">
+        <x:v>Unresolved</x:v>
+      </x:c>
+      <x:c r="D258" s="38" t="str">
+        <x:v>No street address supplied</x:v>
+      </x:c>
+      <x:c r="E258" s="38" t="str">
+        <x:v>City-level research required</x:v>
+      </x:c>
+      <x:c r="F258" s="39" t="str">
+        <x:v>Latitude/longitude intentionally left blank</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra6d17ae4bcfd4818"/>
+  </x:tableParts>
+</x:worksheet>
 </file>
--- a/source-data/Strategic_End_User_Facilities_Bottler_Expansion_v2.xlsx
+++ b/source-data/Strategic_End_User_Facilities_Bottler_Expansion_v2.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Master Facilities v2" sheetId="1" r:id="Raee20bc6c58943b1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Research Coverage" sheetId="2" r:id="R7b9d10ee66cc4c27"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scope &amp; Notes" sheetId="3" r:id="Rd3d241d6bfa7422f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coordinate Audit" sheetId="4" r:id="R37efbe295822440d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Master Facilities v2" sheetId="1" r:id="R3dd8f279e75f43e8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Research Coverage" sheetId="2" r:id="Rb31547e373e04a84"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scope &amp; Notes" sheetId="3" r:id="Rafec205009db4ef2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coordinate Audit" sheetId="4" r:id="R48aedae6647f4096"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -679,8 +679,12 @@
       <x:c r="J3" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K3" s="16"/>
-      <x:c r="L3" s="16"/>
+      <x:c r="K3" s="16" t="n">
+        <x:v>34.39166</x:v>
+      </x:c>
+      <x:c r="L3" s="16" t="n">
+        <x:v>-118.54259</x:v>
+      </x:c>
       <x:c r="M3" s="11"/>
       <x:c r="N3" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -763,8 +767,12 @@
       <x:c r="J5" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K5" s="16"/>
-      <x:c r="L5" s="16"/>
+      <x:c r="K5" s="16" t="n">
+        <x:v>32.72541</x:v>
+      </x:c>
+      <x:c r="L5" s="16" t="n">
+        <x:v>-97.32085</x:v>
+      </x:c>
       <x:c r="M5" s="11"/>
       <x:c r="N5" s="11" t="str">
         <x:v>Verified city - street address pending</x:v>
@@ -803,8 +811,12 @@
       <x:c r="J6" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K6" s="16"/>
-      <x:c r="L6" s="16"/>
+      <x:c r="K6" s="16" t="n">
+        <x:v>39.95238</x:v>
+      </x:c>
+      <x:c r="L6" s="16" t="n">
+        <x:v>-75.16362</x:v>
+      </x:c>
       <x:c r="M6" s="11"/>
       <x:c r="N6" s="11" t="str">
         <x:v>Planned - official source</x:v>
@@ -847,8 +859,12 @@
       <x:c r="J7" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K7" s="16"/>
-      <x:c r="L7" s="16"/>
+      <x:c r="K7" s="16" t="n">
+        <x:v>33.579808626126</x:v>
+      </x:c>
+      <x:c r="L7" s="16" t="n">
+        <x:v>-112.393603679178</x:v>
+      </x:c>
       <x:c r="M7" s="11"/>
       <x:c r="N7" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -885,8 +901,12 @@
       <x:c r="J8" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K8" s="16"/>
-      <x:c r="L8" s="16"/>
+      <x:c r="K8" s="16" t="n">
+        <x:v>38.62727</x:v>
+      </x:c>
+      <x:c r="L8" s="16" t="n">
+        <x:v>-90.19789</x:v>
+      </x:c>
       <x:c r="M8" s="11"/>
       <x:c r="N8" s="11" t="str">
         <x:v>Verified city - official source</x:v>
@@ -923,8 +943,12 @@
       <x:c r="J9" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K9" s="16"/>
-      <x:c r="L9" s="16"/>
+      <x:c r="K9" s="16" t="n">
+        <x:v>43.15868</x:v>
+      </x:c>
+      <x:c r="L9" s="16" t="n">
+        <x:v>-76.33271</x:v>
+      </x:c>
       <x:c r="M9" s="11"/>
       <x:c r="N9" s="11" t="str">
         <x:v>Verified city - official source</x:v>
@@ -961,8 +985,12 @@
       <x:c r="J10" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K10" s="16"/>
-      <x:c r="L10" s="16"/>
+      <x:c r="K10" s="16" t="n">
+        <x:v>34.16533</x:v>
+      </x:c>
+      <x:c r="L10" s="16" t="n">
+        <x:v>-84.80231</x:v>
+      </x:c>
       <x:c r="M10" s="11"/>
       <x:c r="N10" s="11" t="str">
         <x:v>Verified city - official source</x:v>
@@ -999,8 +1027,12 @@
       <x:c r="J11" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K11" s="16"/>
-      <x:c r="L11" s="16"/>
+      <x:c r="K11" s="16" t="n">
+        <x:v>39.96118</x:v>
+      </x:c>
+      <x:c r="L11" s="16" t="n">
+        <x:v>-82.99879</x:v>
+      </x:c>
       <x:c r="M11" s="11"/>
       <x:c r="N11" s="11" t="str">
         <x:v>Verified city - official source</x:v>
@@ -1037,8 +1069,12 @@
       <x:c r="J12" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K12" s="16"/>
-      <x:c r="L12" s="16"/>
+      <x:c r="K12" s="16" t="n">
+        <x:v>40.58526</x:v>
+      </x:c>
+      <x:c r="L12" s="16" t="n">
+        <x:v>-105.08442</x:v>
+      </x:c>
       <x:c r="M12" s="11"/>
       <x:c r="N12" s="11" t="str">
         <x:v>Verified city - official source</x:v>
@@ -1075,8 +1111,12 @@
       <x:c r="J13" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K13" s="16"/>
-      <x:c r="L13" s="16"/>
+      <x:c r="K13" s="16" t="n">
+        <x:v>29.76328</x:v>
+      </x:c>
+      <x:c r="L13" s="16" t="n">
+        <x:v>-95.36327</x:v>
+      </x:c>
       <x:c r="M13" s="11"/>
       <x:c r="N13" s="11" t="str">
         <x:v>Verified city - official source</x:v>
@@ -1113,8 +1153,12 @@
       <x:c r="J14" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K14" s="16"/>
-      <x:c r="L14" s="16"/>
+      <x:c r="K14" s="16" t="n">
+        <x:v>30.33218</x:v>
+      </x:c>
+      <x:c r="L14" s="16" t="n">
+        <x:v>-81.65565</x:v>
+      </x:c>
       <x:c r="M14" s="11"/>
       <x:c r="N14" s="11" t="str">
         <x:v>Verified city - official source</x:v>
@@ -1151,8 +1195,12 @@
       <x:c r="J15" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K15" s="16"/>
-      <x:c r="L15" s="16"/>
+      <x:c r="K15" s="16" t="n">
+        <x:v>34.05223</x:v>
+      </x:c>
+      <x:c r="L15" s="16" t="n">
+        <x:v>-118.24368</x:v>
+      </x:c>
       <x:c r="M15" s="11"/>
       <x:c r="N15" s="11" t="str">
         <x:v>Verified city - official source</x:v>
@@ -1189,8 +1237,12 @@
       <x:c r="J16" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K16" s="16"/>
-      <x:c r="L16" s="16"/>
+      <x:c r="K16" s="16" t="n">
+        <x:v>37.2707</x:v>
+      </x:c>
+      <x:c r="L16" s="16" t="n">
+        <x:v>-76.70746</x:v>
+      </x:c>
       <x:c r="M16" s="11"/>
       <x:c r="N16" s="11" t="str">
         <x:v>Verified city - official source</x:v>
@@ -1227,8 +1279,12 @@
       <x:c r="J17" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K17" s="16"/>
-      <x:c r="L17" s="16"/>
+      <x:c r="K17" s="16" t="n">
+        <x:v>38.24936</x:v>
+      </x:c>
+      <x:c r="L17" s="16" t="n">
+        <x:v>-122.03997</x:v>
+      </x:c>
       <x:c r="M17" s="11"/>
       <x:c r="N17" s="11" t="str">
         <x:v>Closure / sale announced - verify active status</x:v>
@@ -1267,8 +1323,12 @@
       <x:c r="J18" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K18" s="16"/>
-      <x:c r="L18" s="16"/>
+      <x:c r="K18" s="16" t="n">
+        <x:v>42.86509</x:v>
+      </x:c>
+      <x:c r="L18" s="16" t="n">
+        <x:v>-71.4934</x:v>
+      </x:c>
       <x:c r="M18" s="11"/>
       <x:c r="N18" s="11" t="str">
         <x:v>Closure / sale announced - verify active status</x:v>
@@ -1307,8 +1367,12 @@
       <x:c r="J19" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K19" s="16"/>
-      <x:c r="L19" s="16"/>
+      <x:c r="K19" s="16" t="n">
+        <x:v>40.73566</x:v>
+      </x:c>
+      <x:c r="L19" s="16" t="n">
+        <x:v>-74.17237</x:v>
+      </x:c>
       <x:c r="M19" s="11"/>
       <x:c r="N19" s="11" t="str">
         <x:v>Closure / sale announced - verify active status</x:v>
@@ -1347,8 +1411,12 @@
       <x:c r="J20" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K20" s="16"/>
-      <x:c r="L20" s="16"/>
+      <x:c r="K20" s="16" t="n">
+        <x:v>33.53865</x:v>
+      </x:c>
+      <x:c r="L20" s="16" t="n">
+        <x:v>-112.18599</x:v>
+      </x:c>
       <x:c r="M20" s="11"/>
       <x:c r="N20" s="11" t="str">
         <x:v>Verified city - official source</x:v>
@@ -1385,8 +1453,12 @@
       <x:c r="J21" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K21" s="16"/>
-      <x:c r="L21" s="16"/>
+      <x:c r="K21" s="16" t="n">
+        <x:v>34.00071</x:v>
+      </x:c>
+      <x:c r="L21" s="16" t="n">
+        <x:v>-81.03481</x:v>
+      </x:c>
       <x:c r="M21" s="11"/>
       <x:c r="N21" s="11" t="str">
         <x:v>Verified city - official source</x:v>
@@ -1423,8 +1495,12 @@
       <x:c r="J22" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K22" s="16"/>
-      <x:c r="L22" s="16"/>
+      <x:c r="K22" s="16" t="n">
+        <x:v>40.70121</x:v>
+      </x:c>
+      <x:c r="L22" s="16" t="n">
+        <x:v>-74.23015</x:v>
+      </x:c>
       <x:c r="M22" s="11"/>
       <x:c r="N22" s="11" t="str">
         <x:v>Verified city - official source</x:v>
@@ -1461,8 +1537,12 @@
       <x:c r="J23" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K23" s="16"/>
-      <x:c r="L23" s="16"/>
+      <x:c r="K23" s="16" t="n">
+        <x:v>38.43283</x:v>
+      </x:c>
+      <x:c r="L23" s="16" t="n">
+        <x:v>-90.37762</x:v>
+      </x:c>
       <x:c r="M23" s="11"/>
       <x:c r="N23" s="11" t="str">
         <x:v>Current status check required</x:v>
@@ -1501,8 +1581,12 @@
       <x:c r="J24" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K24" s="16"/>
-      <x:c r="L24" s="16"/>
+      <x:c r="K24" s="16" t="n">
+        <x:v>30.33218</x:v>
+      </x:c>
+      <x:c r="L24" s="16" t="n">
+        <x:v>-81.65565</x:v>
+      </x:c>
       <x:c r="M24" s="11"/>
       <x:c r="N24" s="11" t="str">
         <x:v>Current status check required</x:v>
@@ -1541,8 +1625,12 @@
       <x:c r="J25" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K25" s="16"/>
-      <x:c r="L25" s="16"/>
+      <x:c r="K25" s="16" t="n">
+        <x:v>33.99251</x:v>
+      </x:c>
+      <x:c r="L25" s="16" t="n">
+        <x:v>-117.51644</x:v>
+      </x:c>
       <x:c r="M25" s="11"/>
       <x:c r="N25" s="11" t="str">
         <x:v>Current status check required</x:v>
@@ -1581,8 +1669,12 @@
       <x:c r="J26" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K26" s="16"/>
-      <x:c r="L26" s="16"/>
+      <x:c r="K26" s="16" t="n">
+        <x:v>41.50343</x:v>
+      </x:c>
+      <x:c r="L26" s="16" t="n">
+        <x:v>-74.01042</x:v>
+      </x:c>
       <x:c r="M26" s="11"/>
       <x:c r="N26" s="11" t="str">
         <x:v>Current status check required</x:v>
@@ -1621,8 +1713,12 @@
       <x:c r="J27" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K27" s="16"/>
-      <x:c r="L27" s="16"/>
+      <x:c r="K27" s="16" t="n">
+        <x:v>40.47748</x:v>
+      </x:c>
+      <x:c r="L27" s="16" t="n">
+        <x:v>-104.90136</x:v>
+      </x:c>
       <x:c r="M27" s="11"/>
       <x:c r="N27" s="11" t="str">
         <x:v>Current status check required</x:v>
@@ -1661,8 +1757,12 @@
       <x:c r="J28" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K28" s="16"/>
-      <x:c r="L28" s="16"/>
+      <x:c r="K28" s="16" t="n">
+        <x:v>35.46756</x:v>
+      </x:c>
+      <x:c r="L28" s="16" t="n">
+        <x:v>-97.51643</x:v>
+      </x:c>
       <x:c r="M28" s="11"/>
       <x:c r="N28" s="11" t="str">
         <x:v>Current status check required</x:v>
@@ -1701,8 +1801,12 @@
       <x:c r="J29" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K29" s="16"/>
-      <x:c r="L29" s="16"/>
+      <x:c r="K29" s="16" t="n">
+        <x:v>33.95335</x:v>
+      </x:c>
+      <x:c r="L29" s="16" t="n">
+        <x:v>-117.39616</x:v>
+      </x:c>
       <x:c r="M29" s="11"/>
       <x:c r="N29" s="11" t="str">
         <x:v>Current status check required</x:v>
@@ -1741,8 +1845,12 @@
       <x:c r="J30" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K30" s="16"/>
-      <x:c r="L30" s="16"/>
+      <x:c r="K30" s="16" t="n">
+        <x:v>39.75554</x:v>
+      </x:c>
+      <x:c r="L30" s="16" t="n">
+        <x:v>-105.2211</x:v>
+      </x:c>
       <x:c r="M30" s="11"/>
       <x:c r="N30" s="11" t="str">
         <x:v>Verified city - street address pending</x:v>
@@ -1779,8 +1887,12 @@
       <x:c r="J31" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K31" s="16"/>
-      <x:c r="L31" s="16"/>
+      <x:c r="K31" s="16" t="n">
+        <x:v>43.0389</x:v>
+      </x:c>
+      <x:c r="L31" s="16" t="n">
+        <x:v>-87.90647</x:v>
+      </x:c>
       <x:c r="M31" s="11"/>
       <x:c r="N31" s="11" t="str">
         <x:v>Verified city - street address pending</x:v>
@@ -1817,8 +1929,12 @@
       <x:c r="J32" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K32" s="16"/>
-      <x:c r="L32" s="16"/>
+      <x:c r="K32" s="16" t="n">
+        <x:v>31.57851</x:v>
+      </x:c>
+      <x:c r="L32" s="16" t="n">
+        <x:v>-84.15574</x:v>
+      </x:c>
       <x:c r="M32" s="11"/>
       <x:c r="N32" s="11" t="str">
         <x:v>Verified city - street address pending</x:v>
@@ -1855,8 +1971,12 @@
       <x:c r="J33" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K33" s="16"/>
-      <x:c r="L33" s="16"/>
+      <x:c r="K33" s="16" t="n">
+        <x:v>32.72541</x:v>
+      </x:c>
+      <x:c r="L33" s="16" t="n">
+        <x:v>-97.32085</x:v>
+      </x:c>
       <x:c r="M33" s="11"/>
       <x:c r="N33" s="11" t="str">
         <x:v>Verified city - street address pending</x:v>
@@ -1893,8 +2013,12 @@
       <x:c r="J34" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K34" s="16"/>
-      <x:c r="L34" s="16"/>
+      <x:c r="K34" s="16" t="n">
+        <x:v>39.48089</x:v>
+      </x:c>
+      <x:c r="L34" s="16" t="n">
+        <x:v>-84.45772</x:v>
+      </x:c>
       <x:c r="M34" s="11"/>
       <x:c r="N34" s="11" t="str">
         <x:v>Verified city - street address pending</x:v>
@@ -1931,8 +2055,12 @@
       <x:c r="J35" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K35" s="16"/>
-      <x:c r="L35" s="16"/>
+      <x:c r="K35" s="16" t="n">
+        <x:v>38.4079</x:v>
+      </x:c>
+      <x:c r="L35" s="16" t="n">
+        <x:v>-78.62363</x:v>
+      </x:c>
       <x:c r="M35" s="11"/>
       <x:c r="N35" s="11" t="str">
         <x:v>Verified city - street address pending</x:v>
@@ -1969,8 +2097,12 @@
       <x:c r="J36" s="11" t="str">
         <x:v>Canada</x:v>
       </x:c>
-      <x:c r="K36" s="16"/>
-      <x:c r="L36" s="16"/>
+      <x:c r="K36" s="16" t="n">
+        <x:v>49.16638</x:v>
+      </x:c>
+      <x:c r="L36" s="16" t="n">
+        <x:v>-121.95257</x:v>
+      </x:c>
       <x:c r="M36" s="11"/>
       <x:c r="N36" s="11" t="str">
         <x:v>Verified city - street address pending</x:v>
@@ -2007,8 +2139,12 @@
       <x:c r="J37" s="11" t="str">
         <x:v>Canada</x:v>
       </x:c>
-      <x:c r="K37" s="16"/>
-      <x:c r="L37" s="16"/>
+      <x:c r="K37" s="16" t="n">
+        <x:v>45.5152</x:v>
+      </x:c>
+      <x:c r="L37" s="16" t="n">
+        <x:v>-73.46818</x:v>
+      </x:c>
       <x:c r="M37" s="11"/>
       <x:c r="N37" s="11" t="str">
         <x:v>Verified city - street address pending</x:v>
@@ -2045,8 +2181,12 @@
       <x:c r="J38" s="11" t="str">
         <x:v>Canada</x:v>
       </x:c>
-      <x:c r="K38" s="16"/>
-      <x:c r="L38" s="16"/>
+      <x:c r="K38" s="16" t="n">
+        <x:v>47.56494</x:v>
+      </x:c>
+      <x:c r="L38" s="16" t="n">
+        <x:v>-52.70931</x:v>
+      </x:c>
       <x:c r="M38" s="11"/>
       <x:c r="N38" s="11" t="str">
         <x:v>Verified city - street address pending</x:v>
@@ -2087,8 +2227,12 @@
       <x:c r="J39" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K39" s="16"/>
-      <x:c r="L39" s="16"/>
+      <x:c r="K39" s="16" t="n">
+        <x:v>43.80438979543</x:v>
+      </x:c>
+      <x:c r="L39" s="16" t="n">
+        <x:v>-91.253384090303</x:v>
+      </x:c>
       <x:c r="M39" s="11"/>
       <x:c r="N39" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -2221,8 +2365,12 @@
       <x:c r="J42" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K42" s="16"/>
-      <x:c r="L42" s="16"/>
+      <x:c r="K42" s="16" t="n">
+        <x:v>34.121702938715</x:v>
+      </x:c>
+      <x:c r="L42" s="16" t="n">
+        <x:v>-117.938222134275</x:v>
+      </x:c>
       <x:c r="M42" s="11"/>
       <x:c r="N42" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -2259,8 +2407,12 @@
       <x:c r="J43" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K43" s="16"/>
-      <x:c r="L43" s="16"/>
+      <x:c r="K43" s="16" t="n">
+        <x:v>42.00392</x:v>
+      </x:c>
+      <x:c r="L43" s="16" t="n">
+        <x:v>-87.97035</x:v>
+      </x:c>
       <x:c r="M43" s="11"/>
       <x:c r="N43" s="11" t="str">
         <x:v>Verified city - official source</x:v>
@@ -2297,8 +2449,12 @@
       <x:c r="J44" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K44" s="16"/>
-      <x:c r="L44" s="16"/>
+      <x:c r="K44" s="16" t="n">
+        <x:v>34.21821</x:v>
+      </x:c>
+      <x:c r="L44" s="16" t="n">
+        <x:v>-80.24841</x:v>
+      </x:c>
       <x:c r="M44" s="11"/>
       <x:c r="N44" s="11" t="str">
         <x:v>Verified city - official source</x:v>
@@ -2335,8 +2491,12 @@
       <x:c r="J45" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K45" s="16"/>
-      <x:c r="L45" s="16"/>
+      <x:c r="K45" s="16" t="n">
+        <x:v>41.85003</x:v>
+      </x:c>
+      <x:c r="L45" s="16" t="n">
+        <x:v>-87.65005</x:v>
+      </x:c>
       <x:c r="M45" s="11"/>
       <x:c r="N45" s="11" t="str">
         <x:v>Verified city - official source</x:v>
@@ -2373,8 +2533,12 @@
       <x:c r="J46" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K46" s="16"/>
-      <x:c r="L46" s="16"/>
+      <x:c r="K46" s="16" t="n">
+        <x:v>38.24936</x:v>
+      </x:c>
+      <x:c r="L46" s="16" t="n">
+        <x:v>-122.03997</x:v>
+      </x:c>
       <x:c r="M46" s="11"/>
       <x:c r="N46" s="11" t="str">
         <x:v>Verified city - official source</x:v>
@@ -2411,8 +2575,12 @@
       <x:c r="J47" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K47" s="16"/>
-      <x:c r="L47" s="16"/>
+      <x:c r="K47" s="16" t="n">
+        <x:v>41.35033</x:v>
+      </x:c>
+      <x:c r="L47" s="16" t="n">
+        <x:v>-83.12186</x:v>
+      </x:c>
       <x:c r="M47" s="11"/>
       <x:c r="N47" s="11" t="str">
         <x:v>Verified city - official source</x:v>
@@ -2449,8 +2617,12 @@
       <x:c r="J48" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K48" s="16"/>
-      <x:c r="L48" s="16"/>
+      <x:c r="K48" s="16" t="n">
+        <x:v>41.39505</x:v>
+      </x:c>
+      <x:c r="L48" s="16" t="n">
+        <x:v>-82.55517</x:v>
+      </x:c>
       <x:c r="M48" s="11"/>
       <x:c r="N48" s="11" t="str">
         <x:v>Verified city - official source</x:v>
@@ -2487,8 +2659,12 @@
       <x:c r="J49" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K49" s="16"/>
-      <x:c r="L49" s="16"/>
+      <x:c r="K49" s="16" t="n">
+        <x:v>34.96176</x:v>
+      </x:c>
+      <x:c r="L49" s="16" t="n">
+        <x:v>-89.82953</x:v>
+      </x:c>
       <x:c r="M49" s="11"/>
       <x:c r="N49" s="11" t="str">
         <x:v>Verified city - official source</x:v>
@@ -2525,8 +2701,12 @@
       <x:c r="J50" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K50" s="16"/>
-      <x:c r="L50" s="16"/>
+      <x:c r="K50" s="16" t="n">
+        <x:v>41.47309</x:v>
+      </x:c>
+      <x:c r="L50" s="16" t="n">
+        <x:v>-87.06114</x:v>
+      </x:c>
       <x:c r="M50" s="11"/>
       <x:c r="N50" s="11" t="str">
         <x:v>Verified city - official source</x:v>
@@ -2563,8 +2743,12 @@
       <x:c r="J51" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K51" s="16"/>
-      <x:c r="L51" s="16"/>
+      <x:c r="K51" s="16" t="n">
+        <x:v>36.09986</x:v>
+      </x:c>
+      <x:c r="L51" s="16" t="n">
+        <x:v>-80.24422</x:v>
+      </x:c>
       <x:c r="M51" s="11"/>
       <x:c r="N51" s="11" t="str">
         <x:v>Verified city - official source</x:v>
@@ -2603,8 +2787,12 @@
       <x:c r="J52" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K52" s="16"/>
-      <x:c r="L52" s="16"/>
+      <x:c r="K52" s="16" t="n">
+        <x:v>33.61143</x:v>
+      </x:c>
+      <x:c r="L52" s="16" t="n">
+        <x:v>-112.42711</x:v>
+      </x:c>
       <x:c r="M52" s="11"/>
       <x:c r="N52" s="11" t="str">
         <x:v>Verified current manufacturing city - official careers source</x:v>
@@ -2643,8 +2831,12 @@
       <x:c r="J53" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K53" s="16"/>
-      <x:c r="L53" s="16"/>
+      <x:c r="K53" s="16" t="n">
+        <x:v>33.43532</x:v>
+      </x:c>
+      <x:c r="L53" s="16" t="n">
+        <x:v>-112.35821</x:v>
+      </x:c>
       <x:c r="M53" s="11"/>
       <x:c r="N53" s="11" t="str">
         <x:v>Verified current manufacturing city - official careers source</x:v>
@@ -2683,8 +2875,12 @@
       <x:c r="J54" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K54" s="16"/>
-      <x:c r="L54" s="16"/>
+      <x:c r="K54" s="16" t="n">
+        <x:v>39.75554</x:v>
+      </x:c>
+      <x:c r="L54" s="16" t="n">
+        <x:v>-105.2211</x:v>
+      </x:c>
       <x:c r="M54" s="11"/>
       <x:c r="N54" s="11" t="str">
         <x:v>Verified current manufacturing city - official careers source</x:v>
@@ -2723,8 +2919,12 @@
       <x:c r="J55" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K55" s="16"/>
-      <x:c r="L55" s="16"/>
+      <x:c r="K55" s="16" t="n">
+        <x:v>34.25704</x:v>
+      </x:c>
+      <x:c r="L55" s="16" t="n">
+        <x:v>-85.16467</x:v>
+      </x:c>
       <x:c r="M55" s="11"/>
       <x:c r="N55" s="11" t="str">
         <x:v>Verified current manufacturing city - official careers source</x:v>
@@ -2763,8 +2963,12 @@
       <x:c r="J56" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K56" s="16"/>
-      <x:c r="L56" s="16"/>
+      <x:c r="K56" s="16" t="n">
+        <x:v>41.04422</x:v>
+      </x:c>
+      <x:c r="L56" s="16" t="n">
+        <x:v>-83.64993</x:v>
+      </x:c>
       <x:c r="M56" s="11"/>
       <x:c r="N56" s="11" t="str">
         <x:v>Verified current manufacturing city - official careers source</x:v>
@@ -2803,8 +3007,12 @@
       <x:c r="J57" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K57" s="16"/>
-      <x:c r="L57" s="16"/>
+      <x:c r="K57" s="16" t="n">
+        <x:v>41.32591</x:v>
+      </x:c>
+      <x:c r="L57" s="16" t="n">
+        <x:v>-75.78936</x:v>
+      </x:c>
       <x:c r="M57" s="11"/>
       <x:c r="N57" s="11" t="str">
         <x:v>Verified current manufacturing city - official careers source</x:v>
@@ -2843,8 +3051,12 @@
       <x:c r="J58" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K58" s="16"/>
-      <x:c r="L58" s="16"/>
+      <x:c r="K58" s="16" t="n">
+        <x:v>32.72541</x:v>
+      </x:c>
+      <x:c r="L58" s="16" t="n">
+        <x:v>-97.32085</x:v>
+      </x:c>
       <x:c r="M58" s="11"/>
       <x:c r="N58" s="11" t="str">
         <x:v>Verified current manufacturing city - official careers source</x:v>
@@ -2883,8 +3095,12 @@
       <x:c r="J59" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K59" s="16"/>
-      <x:c r="L59" s="16"/>
+      <x:c r="K59" s="16" t="n">
+        <x:v>30.31188</x:v>
+      </x:c>
+      <x:c r="L59" s="16" t="n">
+        <x:v>-95.45605</x:v>
+      </x:c>
       <x:c r="M59" s="11"/>
       <x:c r="N59" s="11" t="str">
         <x:v>Verified current manufacturing city - official careers source</x:v>
@@ -2923,8 +3139,12 @@
       <x:c r="J60" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K60" s="16"/>
-      <x:c r="L60" s="16"/>
+      <x:c r="K60" s="16" t="n">
+        <x:v>44.68095</x:v>
+      </x:c>
+      <x:c r="L60" s="16" t="n">
+        <x:v>-123.06148</x:v>
+      </x:c>
       <x:c r="M60" s="11"/>
       <x:c r="N60" s="11" t="str">
         <x:v>Verified current manufacturing city - official careers source</x:v>
@@ -2963,8 +3183,12 @@
       <x:c r="J61" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K61" s="16"/>
-      <x:c r="L61" s="16"/>
+      <x:c r="K61" s="16" t="n">
+        <x:v>42.92889</x:v>
+      </x:c>
+      <x:c r="L61" s="16" t="n">
+        <x:v>-88.83705</x:v>
+      </x:c>
       <x:c r="M61" s="11"/>
       <x:c r="N61" s="11" t="str">
         <x:v>Verified current manufacturing city - official careers source</x:v>
@@ -3003,8 +3227,12 @@
       <x:c r="J62" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K62" s="16"/>
-      <x:c r="L62" s="16"/>
+      <x:c r="K62" s="16" t="n">
+        <x:v>43.08313</x:v>
+      </x:c>
+      <x:c r="L62" s="16" t="n">
+        <x:v>-73.78457</x:v>
+      </x:c>
       <x:c r="M62" s="11"/>
       <x:c r="N62" s="11" t="str">
         <x:v>Verified current manufacturing city - official careers source</x:v>
@@ -3043,8 +3271,12 @@
       <x:c r="J63" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K63" s="16"/>
-      <x:c r="L63" s="16"/>
+      <x:c r="K63" s="16" t="n">
+        <x:v>28.02224</x:v>
+      </x:c>
+      <x:c r="L63" s="16" t="n">
+        <x:v>-81.73286</x:v>
+      </x:c>
       <x:c r="M63" s="11"/>
       <x:c r="N63" s="11" t="str">
         <x:v>Verified current manufacturing city - official careers source</x:v>
@@ -3753,8 +3985,12 @@
       <x:c r="J80" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K80" s="16"/>
-      <x:c r="L80" s="16"/>
+      <x:c r="K80" s="16" t="n">
+        <x:v>34.05794</x:v>
+      </x:c>
+      <x:c r="L80" s="16" t="n">
+        <x:v>-79.75312</x:v>
+      </x:c>
       <x:c r="M80" s="11"/>
       <x:c r="N80" s="11" t="str">
         <x:v>Verified official location - street address pending</x:v>
@@ -4085,8 +4321,12 @@
       <x:c r="J88" s="11" t="str">
         <x:v>Canada</x:v>
       </x:c>
-      <x:c r="K88" s="16"/>
-      <x:c r="L88" s="16"/>
+      <x:c r="K88" s="16" t="n">
+        <x:v>51.05011</x:v>
+      </x:c>
+      <x:c r="L88" s="16" t="n">
+        <x:v>-114.08529</x:v>
+      </x:c>
       <x:c r="M88" s="11"/>
       <x:c r="N88" s="11" t="str">
         <x:v>Verified official location - street address pending</x:v>
@@ -4123,8 +4363,12 @@
       <x:c r="J89" s="11" t="str">
         <x:v>Canada</x:v>
       </x:c>
-      <x:c r="K89" s="16"/>
-      <x:c r="L89" s="16"/>
+      <x:c r="K89" s="16" t="n">
+        <x:v>43.6403</x:v>
+      </x:c>
+      <x:c r="L89" s="16" t="n">
+        <x:v>-79.93146</x:v>
+      </x:c>
       <x:c r="M89" s="11"/>
       <x:c r="N89" s="11" t="str">
         <x:v>Verified official location - street address pending</x:v>
@@ -4161,8 +4405,12 @@
       <x:c r="J90" s="11" t="str">
         <x:v>Canada</x:v>
       </x:c>
-      <x:c r="K90" s="16"/>
-      <x:c r="L90" s="16"/>
+      <x:c r="K90" s="16" t="n">
+        <x:v>43.70643</x:v>
+      </x:c>
+      <x:c r="L90" s="16" t="n">
+        <x:v>-79.39864</x:v>
+      </x:c>
       <x:c r="M90" s="11"/>
       <x:c r="N90" s="11" t="str">
         <x:v>Verified official location - street address pending</x:v>
@@ -4249,8 +4497,12 @@
       <x:c r="J92" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K92" s="16"/>
-      <x:c r="L92" s="16"/>
+      <x:c r="K92" s="16" t="n">
+        <x:v>36.99032</x:v>
+      </x:c>
+      <x:c r="L92" s="16" t="n">
+        <x:v>-86.4436</x:v>
+      </x:c>
       <x:c r="M92" s="11"/>
       <x:c r="N92" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -4291,8 +4543,12 @@
       <x:c r="J93" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K93" s="16"/>
-      <x:c r="L93" s="16"/>
+      <x:c r="K93" s="16" t="n">
+        <x:v>41.25978</x:v>
+      </x:c>
+      <x:c r="L93" s="16" t="n">
+        <x:v>-78.72669</x:v>
+      </x:c>
       <x:c r="M93" s="11"/>
       <x:c r="N93" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -4335,8 +4591,12 @@
       <x:c r="J94" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K94" s="16"/>
-      <x:c r="L94" s="16"/>
+      <x:c r="K94" s="16" t="n">
+        <x:v>41.25978</x:v>
+      </x:c>
+      <x:c r="L94" s="16" t="n">
+        <x:v>-78.72669</x:v>
+      </x:c>
       <x:c r="M94" s="11"/>
       <x:c r="N94" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -4379,8 +4639,12 @@
       <x:c r="J95" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K95" s="16"/>
-      <x:c r="L95" s="16"/>
+      <x:c r="K95" s="16" t="n">
+        <x:v>36.602204767916</x:v>
+      </x:c>
+      <x:c r="L95" s="16" t="n">
+        <x:v>-79.324605643441</x:v>
+      </x:c>
       <x:c r="M95" s="11"/>
       <x:c r="N95" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -4423,8 +4687,12 @@
       <x:c r="J96" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K96" s="16"/>
-      <x:c r="L96" s="16"/>
+      <x:c r="K96" s="16" t="n">
+        <x:v>46.00767</x:v>
+      </x:c>
+      <x:c r="L96" s="16" t="n">
+        <x:v>-122.84436</x:v>
+      </x:c>
       <x:c r="M96" s="11"/>
       <x:c r="N96" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -4465,8 +4733,12 @@
       <x:c r="J97" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K97" s="16"/>
-      <x:c r="L97" s="16"/>
+      <x:c r="K97" s="16" t="n">
+        <x:v>40.065310780698</x:v>
+      </x:c>
+      <x:c r="L97" s="16" t="n">
+        <x:v>-85.85352230634</x:v>
+      </x:c>
       <x:c r="M97" s="11"/>
       <x:c r="N97" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -4507,8 +4779,12 @@
       <x:c r="J98" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K98" s="16"/>
-      <x:c r="L98" s="16"/>
+      <x:c r="K98" s="16" t="n">
+        <x:v>33.996509871154</x:v>
+      </x:c>
+      <x:c r="L98" s="16" t="n">
+        <x:v>-118.217269023485</x:v>
+      </x:c>
       <x:c r="M98" s="11"/>
       <x:c r="N98" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -4595,8 +4871,12 @@
       <x:c r="J100" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K100" s="16"/>
-      <x:c r="L100" s="16"/>
+      <x:c r="K100" s="16" t="n">
+        <x:v>37.387052809169</x:v>
+      </x:c>
+      <x:c r="L100" s="16" t="n">
+        <x:v>-76.800724664983</x:v>
+      </x:c>
       <x:c r="M100" s="11"/>
       <x:c r="N100" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -4637,8 +4917,12 @@
       <x:c r="J101" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K101" s="16"/>
-      <x:c r="L101" s="16"/>
+      <x:c r="K101" s="16" t="n">
+        <x:v>37.72154699135</x:v>
+      </x:c>
+      <x:c r="L101" s="16" t="n">
+        <x:v>-121.488567279937</x:v>
+      </x:c>
       <x:c r="M101" s="11"/>
       <x:c r="N101" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -4773,8 +5057,12 @@
       <x:c r="J104" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K104" s="16"/>
-      <x:c r="L104" s="16"/>
+      <x:c r="K104" s="16" t="n">
+        <x:v>39.94013491987</x:v>
+      </x:c>
+      <x:c r="L104" s="16" t="n">
+        <x:v>-82.02878750731</x:v>
+      </x:c>
       <x:c r="M104" s="11"/>
       <x:c r="N104" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -4815,8 +5103,12 @@
       <x:c r="J105" s="11" t="str">
         <x:v>Canada</x:v>
       </x:c>
-      <x:c r="K105" s="16"/>
-      <x:c r="L105" s="16"/>
+      <x:c r="K105" s="16" t="n">
+        <x:v>43.68341</x:v>
+      </x:c>
+      <x:c r="L105" s="16" t="n">
+        <x:v>-79.76633</x:v>
+      </x:c>
       <x:c r="M105" s="11"/>
       <x:c r="N105" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -4899,8 +5191,12 @@
       <x:c r="J107" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K107" s="16"/>
-      <x:c r="L107" s="16"/>
+      <x:c r="K107" s="16" t="n">
+        <x:v>41.66892</x:v>
+      </x:c>
+      <x:c r="L107" s="16" t="n">
+        <x:v>-87.73866</x:v>
+      </x:c>
       <x:c r="M107" s="11"/>
       <x:c r="N107" s="11" t="str">
         <x:v>Research starter - exact address pending</x:v>
@@ -4939,8 +5235,12 @@
       <x:c r="J108" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K108" s="16"/>
-      <x:c r="L108" s="16"/>
+      <x:c r="K108" s="16" t="n">
+        <x:v>33.83529</x:v>
+      </x:c>
+      <x:c r="L108" s="16" t="n">
+        <x:v>-117.9145</x:v>
+      </x:c>
       <x:c r="M108" s="11"/>
       <x:c r="N108" s="11" t="str">
         <x:v>Research starter - exact address pending</x:v>
@@ -4979,8 +5279,12 @@
       <x:c r="J109" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K109" s="16"/>
-      <x:c r="L109" s="16"/>
+      <x:c r="K109" s="16" t="n">
+        <x:v>41.69864</x:v>
+      </x:c>
+      <x:c r="L109" s="16" t="n">
+        <x:v>-88.0684</x:v>
+      </x:c>
       <x:c r="M109" s="11"/>
       <x:c r="N109" s="11" t="str">
         <x:v>Research starter - exact address pending</x:v>
@@ -5019,8 +5323,12 @@
       <x:c r="J110" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K110" s="16"/>
-      <x:c r="L110" s="16"/>
+      <x:c r="K110" s="16" t="n">
+        <x:v>41.50615</x:v>
+      </x:c>
+      <x:c r="L110" s="16" t="n">
+        <x:v>-87.6356</x:v>
+      </x:c>
       <x:c r="M110" s="11"/>
       <x:c r="N110" s="11" t="str">
         <x:v>Research starter - exact address pending</x:v>
@@ -5059,8 +5367,12 @@
       <x:c r="J111" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K111" s="16"/>
-      <x:c r="L111" s="16"/>
+      <x:c r="K111" s="16" t="n">
+        <x:v>44.78941</x:v>
+      </x:c>
+      <x:c r="L111" s="16" t="n">
+        <x:v>-93.60218</x:v>
+      </x:c>
       <x:c r="M111" s="11"/>
       <x:c r="N111" s="11" t="str">
         <x:v>Research starter - exact address pending</x:v>
@@ -5099,8 +5411,12 @@
       <x:c r="J112" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K112" s="16"/>
-      <x:c r="L112" s="16"/>
+      <x:c r="K112" s="16" t="n">
+        <x:v>33.96571</x:v>
+      </x:c>
+      <x:c r="L112" s="16" t="n">
+        <x:v>-81.07398</x:v>
+      </x:c>
       <x:c r="M112" s="11"/>
       <x:c r="N112" s="11" t="str">
         <x:v>Research starter - exact address pending</x:v>
@@ -5139,8 +5455,12 @@
       <x:c r="J113" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K113" s="16"/>
-      <x:c r="L113" s="16"/>
+      <x:c r="K113" s="16" t="n">
+        <x:v>34.00057</x:v>
+      </x:c>
+      <x:c r="L113" s="16" t="n">
+        <x:v>-118.15979</x:v>
+      </x:c>
       <x:c r="M113" s="11"/>
       <x:c r="N113" s="11" t="str">
         <x:v>Research starter - exact address pending</x:v>
@@ -5179,8 +5499,12 @@
       <x:c r="J114" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K114" s="16"/>
-      <x:c r="L114" s="16"/>
+      <x:c r="K114" s="16" t="n">
+        <x:v>40.95842</x:v>
+      </x:c>
+      <x:c r="L114" s="16" t="n">
+        <x:v>-75.97465</x:v>
+      </x:c>
       <x:c r="M114" s="11"/>
       <x:c r="N114" s="11" t="str">
         <x:v>Research starter - exact address pending</x:v>
@@ -5219,8 +5543,12 @@
       <x:c r="J115" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K115" s="16"/>
-      <x:c r="L115" s="16"/>
+      <x:c r="K115" s="16" t="n">
+        <x:v>39.74761</x:v>
+      </x:c>
+      <x:c r="L115" s="16" t="n">
+        <x:v>-75.31047</x:v>
+      </x:c>
       <x:c r="M115" s="11"/>
       <x:c r="N115" s="11" t="str">
         <x:v>Research starter - exact address pending</x:v>
@@ -5259,8 +5587,12 @@
       <x:c r="J116" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K116" s="16"/>
-      <x:c r="L116" s="16"/>
+      <x:c r="K116" s="16" t="n">
+        <x:v>34.18667</x:v>
+      </x:c>
+      <x:c r="L116" s="16" t="n">
+        <x:v>-118.44897</x:v>
+      </x:c>
       <x:c r="M116" s="11"/>
       <x:c r="N116" s="11" t="str">
         <x:v>Research starter - exact address pending</x:v>
@@ -5299,8 +5631,12 @@
       <x:c r="J117" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K117" s="16"/>
-      <x:c r="L117" s="16"/>
+      <x:c r="K117" s="16" t="n">
+        <x:v>39.48309</x:v>
+      </x:c>
+      <x:c r="L117" s="16" t="n">
+        <x:v>-88.37283</x:v>
+      </x:c>
       <x:c r="M117" s="11"/>
       <x:c r="N117" s="11" t="str">
         <x:v>Verified operating city - not exhaustive</x:v>
@@ -5339,8 +5675,12 @@
       <x:c r="J118" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K118" s="16"/>
-      <x:c r="L118" s="16"/>
+      <x:c r="K118" s="16" t="n">
+        <x:v>34.1975</x:v>
+      </x:c>
+      <x:c r="L118" s="16" t="n">
+        <x:v>-119.17705</x:v>
+      </x:c>
       <x:c r="M118" s="11"/>
       <x:c r="N118" s="11" t="str">
         <x:v>Verified operating city - not exhaustive</x:v>
@@ -5379,8 +5719,12 @@
       <x:c r="J119" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K119" s="16"/>
-      <x:c r="L119" s="16"/>
+      <x:c r="K119" s="16" t="n">
+        <x:v>32.72541</x:v>
+      </x:c>
+      <x:c r="L119" s="16" t="n">
+        <x:v>-97.32085</x:v>
+      </x:c>
       <x:c r="M119" s="11"/>
       <x:c r="N119" s="11" t="str">
         <x:v>Verified operating city - not exhaustive</x:v>
@@ -5419,8 +5763,12 @@
       <x:c r="J120" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K120" s="16"/>
-      <x:c r="L120" s="16"/>
+      <x:c r="K120" s="16" t="n">
+        <x:v>29.42412</x:v>
+      </x:c>
+      <x:c r="L120" s="16" t="n">
+        <x:v>-98.49363</x:v>
+      </x:c>
       <x:c r="M120" s="11"/>
       <x:c r="N120" s="11" t="str">
         <x:v>Verified operating city - not exhaustive</x:v>
@@ -5459,8 +5807,12 @@
       <x:c r="J121" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K121" s="16"/>
-      <x:c r="L121" s="16"/>
+      <x:c r="K121" s="16" t="n">
+        <x:v>32.93123</x:v>
+      </x:c>
+      <x:c r="L121" s="16" t="n">
+        <x:v>-96.45971</x:v>
+      </x:c>
       <x:c r="M121" s="11"/>
       <x:c r="N121" s="11" t="str">
         <x:v>Verified operating city - not exhaustive</x:v>
@@ -5499,8 +5851,12 @@
       <x:c r="J122" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K122" s="16"/>
-      <x:c r="L122" s="16"/>
+      <x:c r="K122" s="16" t="n">
+        <x:v>39.73915</x:v>
+      </x:c>
+      <x:c r="L122" s="16" t="n">
+        <x:v>-104.9847</x:v>
+      </x:c>
       <x:c r="M122" s="11"/>
       <x:c r="N122" s="11" t="str">
         <x:v>Verified operating city - not exhaustive</x:v>
@@ -5539,8 +5895,12 @@
       <x:c r="J123" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K123" s="16"/>
-      <x:c r="L123" s="16"/>
+      <x:c r="K123" s="16" t="n">
+        <x:v>33.44838</x:v>
+      </x:c>
+      <x:c r="L123" s="16" t="n">
+        <x:v>-112.07404</x:v>
+      </x:c>
       <x:c r="M123" s="11"/>
       <x:c r="N123" s="11" t="str">
         <x:v>Verified operating city - not exhaustive</x:v>
@@ -5579,8 +5939,12 @@
       <x:c r="J124" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K124" s="16"/>
-      <x:c r="L124" s="16"/>
+      <x:c r="K124" s="16" t="n">
+        <x:v>37.65466</x:v>
+      </x:c>
+      <x:c r="L124" s="16" t="n">
+        <x:v>-122.40775</x:v>
+      </x:c>
       <x:c r="M124" s="11"/>
       <x:c r="N124" s="11" t="str">
         <x:v>Verified operating city - not exhaustive</x:v>
@@ -5619,8 +5983,12 @@
       <x:c r="J125" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K125" s="16"/>
-      <x:c r="L125" s="16"/>
+      <x:c r="K125" s="16" t="n">
+        <x:v>33.11921</x:v>
+      </x:c>
+      <x:c r="L125" s="16" t="n">
+        <x:v>-117.08642</x:v>
+      </x:c>
       <x:c r="M125" s="11"/>
       <x:c r="N125" s="11" t="str">
         <x:v>Verified operating city - not exhaustive</x:v>
@@ -5659,8 +6027,12 @@
       <x:c r="J126" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K126" s="16"/>
-      <x:c r="L126" s="16"/>
+      <x:c r="K126" s="16" t="n">
+        <x:v>41.85003</x:v>
+      </x:c>
+      <x:c r="L126" s="16" t="n">
+        <x:v>-87.65005</x:v>
+      </x:c>
       <x:c r="M126" s="11"/>
       <x:c r="N126" s="11" t="str">
         <x:v>Research starter - exact address/current status pending</x:v>
@@ -5699,8 +6071,12 @@
       <x:c r="J127" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K127" s="16"/>
-      <x:c r="L127" s="16"/>
+      <x:c r="K127" s="16" t="n">
+        <x:v>37.55376</x:v>
+      </x:c>
+      <x:c r="L127" s="16" t="n">
+        <x:v>-77.46026</x:v>
+      </x:c>
       <x:c r="M127" s="11"/>
       <x:c r="N127" s="11" t="str">
         <x:v>Research starter - exact address/current status pending</x:v>
@@ -5739,8 +6115,12 @@
       <x:c r="J128" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K128" s="16"/>
-      <x:c r="L128" s="16"/>
+      <x:c r="K128" s="16" t="n">
+        <x:v>40.94038</x:v>
+      </x:c>
+      <x:c r="L128" s="16" t="n">
+        <x:v>-74.13181</x:v>
+      </x:c>
       <x:c r="M128" s="11"/>
       <x:c r="N128" s="11" t="str">
         <x:v>Research starter - exact address/current status pending</x:v>
@@ -5779,8 +6159,12 @@
       <x:c r="J129" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K129" s="16"/>
-      <x:c r="L129" s="16"/>
+      <x:c r="K129" s="16" t="n">
+        <x:v>45.52345</x:v>
+      </x:c>
+      <x:c r="L129" s="16" t="n">
+        <x:v>-122.67621</x:v>
+      </x:c>
       <x:c r="M129" s="11"/>
       <x:c r="N129" s="11" t="str">
         <x:v>Research starter - exact address/current status pending</x:v>
@@ -5819,8 +6203,12 @@
       <x:c r="J130" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K130" s="16"/>
-      <x:c r="L130" s="16"/>
+      <x:c r="K130" s="16" t="n">
+        <x:v>41.78586</x:v>
+      </x:c>
+      <x:c r="L130" s="16" t="n">
+        <x:v>-88.14729</x:v>
+      </x:c>
       <x:c r="M130" s="11"/>
       <x:c r="N130" s="11" t="str">
         <x:v>Research starter - exact address/current status pending</x:v>
@@ -6139,8 +6527,12 @@
       <x:c r="J137" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K137" s="16"/>
-      <x:c r="L137" s="16"/>
+      <x:c r="K137" s="16" t="n">
+        <x:v>38.471699999211</x:v>
+      </x:c>
+      <x:c r="L137" s="16" t="n">
+        <x:v>-121.803858296129</x:v>
+      </x:c>
       <x:c r="M137" s="11"/>
       <x:c r="N137" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -6551,8 +6943,12 @@
       <x:c r="J146" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K146" s="16"/>
-      <x:c r="L146" s="16"/>
+      <x:c r="K146" s="16" t="n">
+        <x:v>34.775499728168</x:v>
+      </x:c>
+      <x:c r="L146" s="16" t="n">
+        <x:v>-79.32553172153</x:v>
+      </x:c>
       <x:c r="M146" s="11"/>
       <x:c r="N146" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -6639,8 +7035,12 @@
       <x:c r="J148" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K148" s="16"/>
-      <x:c r="L148" s="16"/>
+      <x:c r="K148" s="16" t="n">
+        <x:v>41.39227</x:v>
+      </x:c>
+      <x:c r="L148" s="16" t="n">
+        <x:v>-84.12522</x:v>
+      </x:c>
       <x:c r="M148" s="11"/>
       <x:c r="N148" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -6681,8 +7081,12 @@
       <x:c r="J149" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K149" s="16"/>
-      <x:c r="L149" s="16"/>
+      <x:c r="K149" s="16" t="n">
+        <x:v>33.684771937241</x:v>
+      </x:c>
+      <x:c r="L149" s="16" t="n">
+        <x:v>-95.570562156569</x:v>
+      </x:c>
       <x:c r="M149" s="11"/>
       <x:c r="N149" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -6725,8 +7129,12 @@
       <x:c r="J150" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K150" s="16"/>
-      <x:c r="L150" s="16"/>
+      <x:c r="K150" s="16" t="n">
+        <x:v>41.92271</x:v>
+      </x:c>
+      <x:c r="L150" s="16" t="n">
+        <x:v>-111.81356</x:v>
+      </x:c>
       <x:c r="M150" s="11"/>
       <x:c r="N150" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -6907,8 +7315,12 @@
       <x:c r="J154" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K154" s="16"/>
-      <x:c r="L154" s="16"/>
+      <x:c r="K154" s="16" t="n">
+        <x:v>41.05290173703</x:v>
+      </x:c>
+      <x:c r="L154" s="16" t="n">
+        <x:v>-82.703997880593</x:v>
+      </x:c>
       <x:c r="M154" s="11"/>
       <x:c r="N154" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -7137,8 +7549,12 @@
       <x:c r="J159" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K159" s="16"/>
-      <x:c r="L159" s="16"/>
+      <x:c r="K159" s="16" t="n">
+        <x:v>40.10532</x:v>
+      </x:c>
+      <x:c r="L159" s="16" t="n">
+        <x:v>-85.68025</x:v>
+      </x:c>
       <x:c r="M159" s="11"/>
       <x:c r="N159" s="11" t="str">
         <x:v>Research starter - exact address pending</x:v>
@@ -7177,8 +7593,12 @@
       <x:c r="J160" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K160" s="16"/>
-      <x:c r="L160" s="16"/>
+      <x:c r="K160" s="16" t="n">
+        <x:v>42.67807</x:v>
+      </x:c>
+      <x:c r="L160" s="16" t="n">
+        <x:v>-88.2762</x:v>
+      </x:c>
       <x:c r="M160" s="11"/>
       <x:c r="N160" s="11" t="str">
         <x:v>Research starter - exact address pending</x:v>
@@ -7217,8 +7637,12 @@
       <x:c r="J161" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K161" s="16"/>
-      <x:c r="L161" s="16"/>
+      <x:c r="K161" s="16" t="n">
+        <x:v>41.4995</x:v>
+      </x:c>
+      <x:c r="L161" s="16" t="n">
+        <x:v>-81.69541</x:v>
+      </x:c>
       <x:c r="M161" s="11"/>
       <x:c r="N161" s="11" t="str">
         <x:v>Research starter - exact address pending</x:v>
@@ -7257,8 +7681,12 @@
       <x:c r="J162" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K162" s="16"/>
-      <x:c r="L162" s="16"/>
+      <x:c r="K162" s="16" t="n">
+        <x:v>41.52364</x:v>
+      </x:c>
+      <x:c r="L162" s="16" t="n">
+        <x:v>-90.57764</x:v>
+      </x:c>
       <x:c r="M162" s="11"/>
       <x:c r="N162" s="11" t="str">
         <x:v>Research starter - exact address pending</x:v>
@@ -7297,8 +7725,12 @@
       <x:c r="J163" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K163" s="16"/>
-      <x:c r="L163" s="16"/>
+      <x:c r="K163" s="16" t="n">
+        <x:v>36.48847</x:v>
+      </x:c>
+      <x:c r="L163" s="16" t="n">
+        <x:v>-79.7667</x:v>
+      </x:c>
       <x:c r="M163" s="11"/>
       <x:c r="N163" s="11" t="str">
         <x:v>Research starter - exact address pending</x:v>
@@ -7337,8 +7769,12 @@
       <x:c r="J164" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K164" s="16"/>
-      <x:c r="L164" s="16"/>
+      <x:c r="K164" s="16" t="n">
+        <x:v>34.35288</x:v>
+      </x:c>
+      <x:c r="L164" s="16" t="n">
+        <x:v>-82.93209</x:v>
+      </x:c>
       <x:c r="M164" s="11"/>
       <x:c r="N164" s="11" t="str">
         <x:v>Research starter - exact address pending</x:v>
@@ -7377,8 +7813,12 @@
       <x:c r="J165" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K165" s="16"/>
-      <x:c r="L165" s="16"/>
+      <x:c r="K165" s="16" t="n">
+        <x:v>38.62727</x:v>
+      </x:c>
+      <x:c r="L165" s="16" t="n">
+        <x:v>-90.19789</x:v>
+      </x:c>
       <x:c r="M165" s="11"/>
       <x:c r="N165" s="11" t="str">
         <x:v>Research starter - exact address pending</x:v>
@@ -7417,8 +7857,12 @@
       <x:c r="J166" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K166" s="16"/>
-      <x:c r="L166" s="16"/>
+      <x:c r="K166" s="16" t="n">
+        <x:v>41.38978</x:v>
+      </x:c>
+      <x:c r="L166" s="16" t="n">
+        <x:v>-81.44123</x:v>
+      </x:c>
       <x:c r="M166" s="11"/>
       <x:c r="N166" s="11" t="str">
         <x:v>Research starter - exact address pending</x:v>
@@ -8013,8 +8457,12 @@
       <x:c r="J179" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K179" s="16"/>
-      <x:c r="L179" s="16"/>
+      <x:c r="K179" s="16" t="n">
+        <x:v>44.780998207338</x:v>
+      </x:c>
+      <x:c r="L179" s="16" t="n">
+        <x:v>-93.336507201048</x:v>
+      </x:c>
       <x:c r="M179" s="11"/>
       <x:c r="N179" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -8147,8 +8595,12 @@
       <x:c r="J182" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K182" s="16"/>
-      <x:c r="L182" s="16"/>
+      <x:c r="K182" s="16" t="n">
+        <x:v>34.775499728168</x:v>
+      </x:c>
+      <x:c r="L182" s="16" t="n">
+        <x:v>-79.32553172153</x:v>
+      </x:c>
       <x:c r="M182" s="11"/>
       <x:c r="N182" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -8189,8 +8641,12 @@
       <x:c r="J183" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K183" s="16"/>
-      <x:c r="L183" s="16"/>
+      <x:c r="K183" s="16" t="n">
+        <x:v>41.39227</x:v>
+      </x:c>
+      <x:c r="L183" s="16" t="n">
+        <x:v>-84.12522</x:v>
+      </x:c>
       <x:c r="M183" s="11"/>
       <x:c r="N183" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -8369,8 +8825,12 @@
       <x:c r="J187" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K187" s="16"/>
-      <x:c r="L187" s="16"/>
+      <x:c r="K187" s="16" t="n">
+        <x:v>33.684771937241</x:v>
+      </x:c>
+      <x:c r="L187" s="16" t="n">
+        <x:v>-95.570562156569</x:v>
+      </x:c>
       <x:c r="M187" s="11"/>
       <x:c r="N187" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -8457,8 +8917,12 @@
       <x:c r="J189" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K189" s="16"/>
-      <x:c r="L189" s="16"/>
+      <x:c r="K189" s="16" t="n">
+        <x:v>42.492857822128</x:v>
+      </x:c>
+      <x:c r="L189" s="16" t="n">
+        <x:v>-87.822021464507</x:v>
+      </x:c>
       <x:c r="M189" s="11"/>
       <x:c r="N189" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -8545,8 +9009,12 @@
       <x:c r="J191" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K191" s="16"/>
-      <x:c r="L191" s="16"/>
+      <x:c r="K191" s="16" t="n">
+        <x:v>44.898896360646</x:v>
+      </x:c>
+      <x:c r="L191" s="16" t="n">
+        <x:v>-91.87233653056</x:v>
+      </x:c>
       <x:c r="M191" s="11"/>
       <x:c r="N191" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -8679,8 +9147,12 @@
       <x:c r="J194" s="11" t="str">
         <x:v>Puerto Rico</x:v>
       </x:c>
-      <x:c r="K194" s="16"/>
-      <x:c r="L194" s="16"/>
+      <x:c r="K194" s="16" t="n">
+        <x:v>18.18301</x:v>
+      </x:c>
+      <x:c r="L194" s="16" t="n">
+        <x:v>-65.86627</x:v>
+      </x:c>
       <x:c r="M194" s="11"/>
       <x:c r="N194" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -8717,8 +9189,12 @@
       <x:c r="J195" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K195" s="16"/>
-      <x:c r="L195" s="16"/>
+      <x:c r="K195" s="16" t="n">
+        <x:v>40.11642</x:v>
+      </x:c>
+      <x:c r="L195" s="16" t="n">
+        <x:v>-88.24338</x:v>
+      </x:c>
       <x:c r="M195" s="11"/>
       <x:c r="N195" s="11" t="str">
         <x:v>Research starter - exact address pending</x:v>
@@ -8757,8 +9233,12 @@
       <x:c r="J196" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K196" s="16"/>
-      <x:c r="L196" s="16"/>
+      <x:c r="K196" s="16" t="n">
+        <x:v>41.35033</x:v>
+      </x:c>
+      <x:c r="L196" s="16" t="n">
+        <x:v>-83.12186</x:v>
+      </x:c>
       <x:c r="M196" s="11"/>
       <x:c r="N196" s="11" t="str">
         <x:v>Research starter - exact address pending</x:v>
@@ -8797,8 +9277,12 @@
       <x:c r="J197" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K197" s="16"/>
-      <x:c r="L197" s="16"/>
+      <x:c r="K197" s="16" t="n">
+        <x:v>37.21533</x:v>
+      </x:c>
+      <x:c r="L197" s="16" t="n">
+        <x:v>-93.29824</x:v>
+      </x:c>
       <x:c r="M197" s="11"/>
       <x:c r="N197" s="11" t="str">
         <x:v>Research starter - exact address pending</x:v>
@@ -8837,8 +9321,12 @@
       <x:c r="J198" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K198" s="16"/>
-      <x:c r="L198" s="16"/>
+      <x:c r="K198" s="16" t="n">
+        <x:v>32.91262</x:v>
+      </x:c>
+      <x:c r="L198" s="16" t="n">
+        <x:v>-96.63888</x:v>
+      </x:c>
       <x:c r="M198" s="11"/>
       <x:c r="N198" s="11" t="str">
         <x:v>Research starter - exact address pending</x:v>
@@ -8877,8 +9365,12 @@
       <x:c r="J199" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K199" s="16"/>
-      <x:c r="L199" s="16"/>
+      <x:c r="K199" s="16" t="n">
+        <x:v>39.15817</x:v>
+      </x:c>
+      <x:c r="L199" s="16" t="n">
+        <x:v>-75.52437</x:v>
+      </x:c>
       <x:c r="M199" s="11"/>
       <x:c r="N199" s="11" t="str">
         <x:v>Research starter - exact address pending</x:v>
@@ -8917,8 +9409,12 @@
       <x:c r="J200" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K200" s="16"/>
-      <x:c r="L200" s="16"/>
+      <x:c r="K200" s="16" t="n">
+        <x:v>34.27458</x:v>
+      </x:c>
+      <x:c r="L200" s="16" t="n">
+        <x:v>-81.61872</x:v>
+      </x:c>
       <x:c r="M200" s="11"/>
       <x:c r="N200" s="11" t="str">
         <x:v>Research starter - exact address pending</x:v>
@@ -8957,8 +9453,12 @@
       <x:c r="J201" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K201" s="16"/>
-      <x:c r="L201" s="16"/>
+      <x:c r="K201" s="16" t="n">
+        <x:v>40.79672</x:v>
+      </x:c>
+      <x:c r="L201" s="16" t="n">
+        <x:v>-81.52151</x:v>
+      </x:c>
       <x:c r="M201" s="11"/>
       <x:c r="N201" s="11" t="str">
         <x:v>Research starter - exact address pending</x:v>
@@ -8997,8 +9497,12 @@
       <x:c r="J202" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K202" s="16"/>
-      <x:c r="L202" s="16"/>
+      <x:c r="K202" s="16" t="n">
+        <x:v>30.33218</x:v>
+      </x:c>
+      <x:c r="L202" s="16" t="n">
+        <x:v>-81.65565</x:v>
+      </x:c>
       <x:c r="M202" s="11"/>
       <x:c r="N202" s="11" t="str">
         <x:v>Research starter - exact address pending</x:v>
@@ -9473,8 +9977,12 @@
       <x:c r="J212" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K212" s="16"/>
-      <x:c r="L212" s="16"/>
+      <x:c r="K212" s="16" t="n">
+        <x:v>33.349134149831</x:v>
+      </x:c>
+      <x:c r="L212" s="16" t="n">
+        <x:v>-111.967945054298</x:v>
+      </x:c>
       <x:c r="M212" s="11" t="str"/>
       <x:c r="N212" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -9661,8 +10169,12 @@
       <x:c r="J216" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K216" s="16"/>
-      <x:c r="L216" s="16"/>
+      <x:c r="K216" s="16" t="n">
+        <x:v>44.004893987001</x:v>
+      </x:c>
+      <x:c r="L216" s="16" t="n">
+        <x:v>-116.921694796566</x:v>
+      </x:c>
       <x:c r="M216" s="11" t="str"/>
       <x:c r="N216" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -9701,8 +10213,12 @@
       <x:c r="J217" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K217" s="16"/>
-      <x:c r="L217" s="16"/>
+      <x:c r="K217" s="16" t="n">
+        <x:v>38.83388</x:v>
+      </x:c>
+      <x:c r="L217" s="16" t="n">
+        <x:v>-104.82136</x:v>
+      </x:c>
       <x:c r="M217" s="11" t="str"/>
       <x:c r="N217" s="11" t="str">
         <x:v>Planned / under construction - official source</x:v>
@@ -10173,8 +10689,12 @@
       <x:c r="J227" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K227" s="16"/>
-      <x:c r="L227" s="16"/>
+      <x:c r="K227" s="16" t="n">
+        <x:v>39.95238</x:v>
+      </x:c>
+      <x:c r="L227" s="16" t="n">
+        <x:v>-75.16362</x:v>
+      </x:c>
       <x:c r="M227" s="11" t="str"/>
       <x:c r="N227" s="11" t="str">
         <x:v>Verified production city - street address pending</x:v>
@@ -10213,8 +10733,12 @@
       <x:c r="J228" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K228" s="16"/>
-      <x:c r="L228" s="16"/>
+      <x:c r="K228" s="16" t="n">
+        <x:v>39.96706</x:v>
+      </x:c>
+      <x:c r="L228" s="16" t="n">
+        <x:v>-74.94267</x:v>
+      </x:c>
       <x:c r="M228" s="11" t="str"/>
       <x:c r="N228" s="11" t="str">
         <x:v>Verified production city - street address pending</x:v>
@@ -10349,8 +10873,12 @@
       <x:c r="J231" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K231" s="16"/>
-      <x:c r="L231" s="16"/>
+      <x:c r="K231" s="16" t="n">
+        <x:v>35.22709</x:v>
+      </x:c>
+      <x:c r="L231" s="16" t="n">
+        <x:v>-80.84313</x:v>
+      </x:c>
       <x:c r="M231" s="11" t="str"/>
       <x:c r="N231" s="11" t="str">
         <x:v>Verified current manufacturing site - official source</x:v>
@@ -10389,8 +10917,12 @@
       <x:c r="J232" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K232" s="16"/>
-      <x:c r="L232" s="16"/>
+      <x:c r="K232" s="16" t="n">
+        <x:v>37.52348</x:v>
+      </x:c>
+      <x:c r="L232" s="16" t="n">
+        <x:v>-77.31581</x:v>
+      </x:c>
       <x:c r="M232" s="11" t="str"/>
       <x:c r="N232" s="11" t="str">
         <x:v>Verified current manufacturing site - official source</x:v>
@@ -10429,8 +10961,12 @@
       <x:c r="J233" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K233" s="16"/>
-      <x:c r="L233" s="16"/>
+      <x:c r="K233" s="16" t="n">
+        <x:v>38.99067</x:v>
+      </x:c>
+      <x:c r="L233" s="16" t="n">
+        <x:v>-77.02609</x:v>
+      </x:c>
       <x:c r="M233" s="11" t="str"/>
       <x:c r="N233" s="11" t="str">
         <x:v>Verified current manufacturing site - official source</x:v>
@@ -10469,8 +11005,12 @@
       <x:c r="J234" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K234" s="16"/>
-      <x:c r="L234" s="16"/>
+      <x:c r="K234" s="16" t="n">
+        <x:v>39.29038</x:v>
+      </x:c>
+      <x:c r="L234" s="16" t="n">
+        <x:v>-76.61219</x:v>
+      </x:c>
       <x:c r="M234" s="11" t="str"/>
       <x:c r="N234" s="11" t="str">
         <x:v>Verified current manufacturing site - official source</x:v>
@@ -10555,8 +11095,12 @@
       <x:c r="J236" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K236" s="16"/>
-      <x:c r="L236" s="16"/>
+      <x:c r="K236" s="16" t="n">
+        <x:v>40.43449</x:v>
+      </x:c>
+      <x:c r="L236" s="16" t="n">
+        <x:v>-84.97775</x:v>
+      </x:c>
       <x:c r="M236" s="11" t="str"/>
       <x:c r="N236" s="11" t="str">
         <x:v>Manufacturing site identified - current street/status final-check</x:v>
@@ -10595,8 +11139,12 @@
       <x:c r="J237" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K237" s="16"/>
-      <x:c r="L237" s="16"/>
+      <x:c r="K237" s="16" t="n">
+        <x:v>39.12711</x:v>
+      </x:c>
+      <x:c r="L237" s="16" t="n">
+        <x:v>-84.51439</x:v>
+      </x:c>
       <x:c r="M237" s="11" t="str"/>
       <x:c r="N237" s="11" t="str">
         <x:v>Manufacturing site identified - current street/status final-check</x:v>
@@ -10681,8 +11229,12 @@
       <x:c r="J239" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K239" s="16"/>
-      <x:c r="L239" s="16"/>
+      <x:c r="K239" s="16" t="n">
+        <x:v>35.14648</x:v>
+      </x:c>
+      <x:c r="L239" s="16" t="n">
+        <x:v>-90.18454</x:v>
+      </x:c>
       <x:c r="M239" s="11" t="str"/>
       <x:c r="N239" s="11" t="str">
         <x:v>Verified current manufacturing site - official source</x:v>
@@ -10721,8 +11273,12 @@
       <x:c r="J240" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K240" s="16"/>
-      <x:c r="L240" s="16"/>
+      <x:c r="K240" s="16" t="n">
+        <x:v>35.14953</x:v>
+      </x:c>
+      <x:c r="L240" s="16" t="n">
+        <x:v>-90.04898</x:v>
+      </x:c>
       <x:c r="M240" s="11" t="str"/>
       <x:c r="N240" s="11" t="str">
         <x:v>Manufacturing site identified - current street/status final-check</x:v>
@@ -10765,8 +11321,12 @@
       <x:c r="J241" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K241" s="16"/>
-      <x:c r="L241" s="16"/>
+      <x:c r="K241" s="16" t="n">
+        <x:v>35.71126</x:v>
+      </x:c>
+      <x:c r="L241" s="16" t="n">
+        <x:v>-78.61417</x:v>
+      </x:c>
       <x:c r="M241" s="11" t="str"/>
       <x:c r="N241" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -11229,8 +11789,12 @@
       <x:c r="J251" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K251" s="16"/>
-      <x:c r="L251" s="16"/>
+      <x:c r="K251" s="16" t="n">
+        <x:v>35.990446107832</x:v>
+      </x:c>
+      <x:c r="L251" s="16" t="n">
+        <x:v>-89.394241184782</x:v>
+      </x:c>
       <x:c r="M251" s="11" t="str"/>
       <x:c r="N251" s="11" t="str">
         <x:v>Verified - official source</x:v>
@@ -11557,8 +12121,12 @@
       <x:c r="J258" s="11" t="str">
         <x:v>United States</x:v>
       </x:c>
-      <x:c r="K258" s="16"/>
-      <x:c r="L258" s="16"/>
+      <x:c r="K258" s="16" t="n">
+        <x:v>33.80816</x:v>
+      </x:c>
+      <x:c r="L258" s="16" t="n">
+        <x:v>-84.1702</x:v>
+      </x:c>
       <x:c r="M258" s="11" t="str"/>
       <x:c r="N258" s="11" t="str">
         <x:v>Verified production city - street address pending</x:v>
@@ -11581,7 +12149,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re09bc30023e84cda"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6693230adada4a02"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11661,7 +12229,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re56804ff7fce4fa0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc82838e477d44795"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11809,16 +12377,16 @@
         <x:v>DP1-03</x:v>
       </x:c>
       <x:c r="C3" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D3" s="35" t="str">
-        <x:v>U.S. Census + OpenStreetMap fallback</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E3" s="35" t="str">
-        <x:v>No accepted match</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F3" s="36" t="str">
-        <x:v>Street address requires manual verification</x:v>
+        <x:v>Santa Clarita, California; GeoNames ID 5393049</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -11849,16 +12417,16 @@
         <x:v>DP2</x:v>
       </x:c>
       <x:c r="C5" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D5" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E5" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F5" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Fort Worth, Texas; GeoNames ID 4691930</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -11869,16 +12437,16 @@
         <x:v>DP3</x:v>
       </x:c>
       <x:c r="C6" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D6" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E6" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F6" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Philadelphia, Pennsylvania; GeoNames ID 4560349</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -11889,13 +12457,13 @@
         <x:v>RAUCH North America</x:v>
       </x:c>
       <x:c r="C7" s="35" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D7" s="35" t="str">
         <x:v>U.S. Census Geocoder, benchmark 4</x:v>
       </x:c>
       <x:c r="E7" s="35" t="str">
-        <x:v>Non-exact match</x:v>
+        <x:v>Non-exact street match</x:v>
       </x:c>
       <x:c r="F7" s="36" t="str">
         <x:v>10501 REEMS RD, WADDELL, AZ, 85355</x:v>
@@ -11909,16 +12477,16 @@
         <x:v>Anheuser-Busch Brewery - St. Louis</x:v>
       </x:c>
       <x:c r="C8" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D8" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E8" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F8" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>St. Louis, Missouri; GeoNames ID 4407066</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -11929,16 +12497,16 @@
         <x:v>Anheuser-Busch Brewery - Baldwinsville</x:v>
       </x:c>
       <x:c r="C9" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D9" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E9" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F9" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Baldwinsville, New York; GeoNames ID 5107785</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -11949,16 +12517,16 @@
         <x:v>Anheuser-Busch Brewery - Cartersville</x:v>
       </x:c>
       <x:c r="C10" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D10" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E10" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F10" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Cartersville, Georgia; GeoNames ID 4186531</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -11969,16 +12537,16 @@
         <x:v>Anheuser-Busch Brewery - Columbus</x:v>
       </x:c>
       <x:c r="C11" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D11" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E11" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F11" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Columbus, Ohio; GeoNames ID 4509177</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -11989,16 +12557,16 @@
         <x:v>Anheuser-Busch Brewery - Fort Collins</x:v>
       </x:c>
       <x:c r="C12" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D12" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E12" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F12" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Fort Collins, Colorado; GeoNames ID 5577147</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -12009,16 +12577,16 @@
         <x:v>Anheuser-Busch Brewery - Houston</x:v>
       </x:c>
       <x:c r="C13" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D13" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E13" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F13" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Houston, Texas; GeoNames ID 4699066</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -12029,16 +12597,16 @@
         <x:v>Anheuser-Busch Brewery - Jacksonville</x:v>
       </x:c>
       <x:c r="C14" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D14" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E14" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F14" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Jacksonville, Florida; GeoNames ID 4160021</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -12049,16 +12617,16 @@
         <x:v>Anheuser-Busch Brewery - Los Angeles</x:v>
       </x:c>
       <x:c r="C15" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D15" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E15" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F15" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Los Angeles, California; GeoNames ID 5368361</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -12069,16 +12637,16 @@
         <x:v>Anheuser-Busch Brewery - Williamsburg</x:v>
       </x:c>
       <x:c r="C16" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D16" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E16" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F16" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Williamsburg, Virginia; GeoNames ID 4793846</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -12089,16 +12657,16 @@
         <x:v>Anheuser-Busch Brewery - Fairfield</x:v>
       </x:c>
       <x:c r="C17" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D17" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E17" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F17" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Fairfield, California; GeoNames ID 5347335</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -12109,16 +12677,16 @@
         <x:v>Anheuser-Busch Brewery - Merrimack</x:v>
       </x:c>
       <x:c r="C18" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D18" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E18" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F18" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Merrimack, New Hampshire; GeoNames ID 5089478</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -12129,16 +12697,16 @@
         <x:v>Anheuser-Busch Brewery - Newark</x:v>
       </x:c>
       <x:c r="C19" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D19" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E19" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F19" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Newark, New Jersey; GeoNames ID 5101798</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -12149,16 +12717,16 @@
         <x:v>Mark Anthony Brewing - Glendale</x:v>
       </x:c>
       <x:c r="C20" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D20" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E20" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F20" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Glendale, Arizona; GeoNames ID 5295985</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -12169,16 +12737,16 @@
         <x:v>Mark Anthony Brewing - Columbia</x:v>
       </x:c>
       <x:c r="C21" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D21" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E21" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F21" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Columbia, South Carolina; GeoNames ID 4575352</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -12189,16 +12757,16 @@
         <x:v>Mark Anthony Brewing - Hillside</x:v>
       </x:c>
       <x:c r="C22" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D22" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E22" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F22" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Hillside, New Jersey; GeoNames ID 5099093</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -12209,16 +12777,16 @@
         <x:v>MCC - Arnold</x:v>
       </x:c>
       <x:c r="C23" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D23" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E23" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F23" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Arnold, Missouri; GeoNames ID 4375087</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -12229,16 +12797,16 @@
         <x:v>MCC - Jacksonville</x:v>
       </x:c>
       <x:c r="C24" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D24" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E24" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F24" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Jacksonville, Florida; GeoNames ID 4160021</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -12249,16 +12817,16 @@
         <x:v>MCC - Mira Loma</x:v>
       </x:c>
       <x:c r="C25" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D25" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E25" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F25" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Jurupa Valley, California; GeoNames ID 5373492</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -12269,16 +12837,16 @@
         <x:v>MCC - Newburgh</x:v>
       </x:c>
       <x:c r="C26" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D26" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E26" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F26" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Newburgh, New York; GeoNames ID 5128654</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -12289,16 +12857,16 @@
         <x:v>MCC - Windsor</x:v>
       </x:c>
       <x:c r="C27" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D27" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E27" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F27" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Windsor, Colorado; GeoNames ID 5583509</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -12309,16 +12877,16 @@
         <x:v>MCC - Oklahoma City</x:v>
       </x:c>
       <x:c r="C28" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D28" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E28" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F28" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Oklahoma City, Oklahoma; GeoNames ID 4544349</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -12329,16 +12897,16 @@
         <x:v>MCC - Riverside</x:v>
       </x:c>
       <x:c r="C29" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D29" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E29" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F29" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Riverside, California; GeoNames ID 5387877</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -12349,16 +12917,16 @@
         <x:v>Molson Coors - Golden</x:v>
       </x:c>
       <x:c r="C30" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D30" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E30" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F30" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Golden, Colorado; GeoNames ID 5423294</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
@@ -12369,16 +12937,16 @@
         <x:v>Molson Coors - Milwaukee</x:v>
       </x:c>
       <x:c r="C31" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D31" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E31" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F31" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Milwaukee, Wisconsin; GeoNames ID 5263045</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
@@ -12389,16 +12957,16 @@
         <x:v>Molson Coors - Albany</x:v>
       </x:c>
       <x:c r="C32" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D32" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E32" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F32" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Albany, Georgia; GeoNames ID 4179320</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
@@ -12409,16 +12977,16 @@
         <x:v>Molson Coors - Fort Worth</x:v>
       </x:c>
       <x:c r="C33" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D33" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E33" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F33" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Fort Worth, Texas; GeoNames ID 4691930</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
@@ -12429,16 +12997,16 @@
         <x:v>Molson Coors - Trenton</x:v>
       </x:c>
       <x:c r="C34" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D34" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E34" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F34" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Trenton, Ohio; GeoNames ID 4526469</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
@@ -12449,16 +13017,16 @@
         <x:v>Molson Coors - Elkton</x:v>
       </x:c>
       <x:c r="C35" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D35" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E35" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F35" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Elkton, Virginia; GeoNames ID 4757467</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
@@ -12469,16 +13037,16 @@
         <x:v>Molson Coors - Chilliwack</x:v>
       </x:c>
       <x:c r="C36" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D36" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E36" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F36" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Chilliwack, British Columbia; GeoNames ID 5921356</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
@@ -12489,16 +13057,16 @@
         <x:v>Molson Coors - Longueuil</x:v>
       </x:c>
       <x:c r="C37" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D37" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E37" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F37" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Longueuil, Quebec; GeoNames ID 6059891</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
@@ -12509,16 +13077,16 @@
         <x:v>Molson Coors - St. John's</x:v>
       </x:c>
       <x:c r="C38" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D38" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E38" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F38" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>St. John's, Newfoundland and Labrador; GeoNames ID 6324733</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
@@ -12529,13 +13097,13 @@
         <x:v>City Brewing - La Crosse</x:v>
       </x:c>
       <x:c r="C39" s="35" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D39" s="35" t="str">
         <x:v>U.S. Census Geocoder, benchmark 4</x:v>
       </x:c>
       <x:c r="E39" s="35" t="str">
-        <x:v>Non-exact match</x:v>
+        <x:v>Non-exact street match</x:v>
       </x:c>
       <x:c r="F39" s="36" t="str">
         <x:v>925 3RD ST S, LA CROSSE, WI, 54601</x:v>
@@ -12589,13 +13157,13 @@
         <x:v>City Brewing - Irwindale</x:v>
       </x:c>
       <x:c r="C42" s="35" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D42" s="35" t="str">
         <x:v>U.S. Census Geocoder, benchmark 4</x:v>
       </x:c>
       <x:c r="E42" s="35" t="str">
-        <x:v>Non-exact match</x:v>
+        <x:v>Non-exact street match</x:v>
       </x:c>
       <x:c r="F42" s="36" t="str">
         <x:v>15801 E 1ST ST, IRWINDALE, CA, 91706</x:v>
@@ -12609,16 +13177,16 @@
         <x:v>Ardagh - Elk Grove Village</x:v>
       </x:c>
       <x:c r="C43" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D43" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E43" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F43" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Elk Grove Village, Illinois; GeoNames ID 4890925</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
@@ -12629,16 +13197,16 @@
         <x:v>Ardagh - Bishopville</x:v>
       </x:c>
       <x:c r="C44" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D44" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E44" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F44" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Bishopville, South Carolina; GeoNames ID 4571470</x:v>
       </x:c>
     </x:row>
     <x:row r="45">
@@ -12649,16 +13217,16 @@
         <x:v>Ardagh - Chicago</x:v>
       </x:c>
       <x:c r="C45" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D45" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E45" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F45" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Chicago, Illinois; GeoNames ID 4887398</x:v>
       </x:c>
     </x:row>
     <x:row r="46">
@@ -12669,16 +13237,16 @@
         <x:v>Ardagh - Fairfield</x:v>
       </x:c>
       <x:c r="C46" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D46" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E46" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F46" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Fairfield, California; GeoNames ID 5347335</x:v>
       </x:c>
     </x:row>
     <x:row r="47">
@@ -12689,16 +13257,16 @@
         <x:v>Ardagh - Fremont</x:v>
       </x:c>
       <x:c r="C47" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D47" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E47" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F47" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Fremont, Ohio; GeoNames ID 5155207</x:v>
       </x:c>
     </x:row>
     <x:row r="48">
@@ -12709,16 +13277,16 @@
         <x:v>Ardagh - Huron</x:v>
       </x:c>
       <x:c r="C48" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D48" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E48" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F48" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Huron, Ohio; GeoNames ID 5158298</x:v>
       </x:c>
     </x:row>
     <x:row r="49">
@@ -12729,16 +13297,16 @@
         <x:v>Ardagh - Olive Branch</x:v>
       </x:c>
       <x:c r="C49" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D49" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E49" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F49" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Olive Branch, Mississippi; GeoNames ID 4439869</x:v>
       </x:c>
     </x:row>
     <x:row r="50">
@@ -12749,16 +13317,16 @@
         <x:v>Ardagh - Valparaiso</x:v>
       </x:c>
       <x:c r="C50" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D50" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E50" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F50" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Valparaiso, Indiana; GeoNames ID 4927537</x:v>
       </x:c>
     </x:row>
     <x:row r="51">
@@ -12769,16 +13337,16 @@
         <x:v>Ardagh - Winston-Salem</x:v>
       </x:c>
       <x:c r="C51" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D51" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E51" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F51" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Winston-Salem, North Carolina; GeoNames ID 4499612</x:v>
       </x:c>
     </x:row>
     <x:row r="52">
@@ -12789,16 +13357,16 @@
         <x:v>Ball - Waddell</x:v>
       </x:c>
       <x:c r="C52" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D52" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E52" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F52" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Waddell, Arizona; GeoNames ID 5319614</x:v>
       </x:c>
     </x:row>
     <x:row r="53">
@@ -12809,16 +13377,16 @@
         <x:v>Ball - Goodyear</x:v>
       </x:c>
       <x:c r="C53" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D53" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E53" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F53" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Goodyear, Arizona; GeoNames ID 5296266</x:v>
       </x:c>
     </x:row>
     <x:row r="54">
@@ -12829,16 +13397,16 @@
         <x:v>Ball - Golden</x:v>
       </x:c>
       <x:c r="C54" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D54" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E54" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F54" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Golden, Colorado; GeoNames ID 5423294</x:v>
       </x:c>
     </x:row>
     <x:row r="55">
@@ -12849,16 +13417,16 @@
         <x:v>Ball - Rome</x:v>
       </x:c>
       <x:c r="C55" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D55" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E55" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F55" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Rome, Georgia; GeoNames ID 4219762</x:v>
       </x:c>
     </x:row>
     <x:row r="56">
@@ -12869,16 +13437,16 @@
         <x:v>Ball - Findlay</x:v>
       </x:c>
       <x:c r="C56" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D56" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E56" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F56" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Findlay, Ohio; GeoNames ID 5153924</x:v>
       </x:c>
     </x:row>
     <x:row r="57">
@@ -12889,16 +13457,16 @@
         <x:v>Ball - Pittston</x:v>
       </x:c>
       <x:c r="C57" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D57" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E57" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F57" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Pittston, Pennsylvania; GeoNames ID 5206397</x:v>
       </x:c>
     </x:row>
     <x:row r="58">
@@ -12909,16 +13477,16 @@
         <x:v>Ball - Fort Worth</x:v>
       </x:c>
       <x:c r="C58" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D58" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E58" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F58" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Fort Worth, Texas; GeoNames ID 4691930</x:v>
       </x:c>
     </x:row>
     <x:row r="59">
@@ -12929,16 +13497,16 @@
         <x:v>Ball - Conroe</x:v>
       </x:c>
       <x:c r="C59" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D59" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E59" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F59" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Conroe, Texas; GeoNames ID 4682991</x:v>
       </x:c>
     </x:row>
     <x:row r="60">
@@ -12949,16 +13517,16 @@
         <x:v>Ball - Millersburg</x:v>
       </x:c>
       <x:c r="C60" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D60" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E60" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F60" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Millersburg, Oregon; GeoNames ID 5740834</x:v>
       </x:c>
     </x:row>
     <x:row r="61">
@@ -12969,16 +13537,16 @@
         <x:v>Ball - Ft. Atkinson</x:v>
       </x:c>
       <x:c r="C61" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D61" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E61" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F61" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Fort Atkinson, Wisconsin; GeoNames ID 5253498</x:v>
       </x:c>
     </x:row>
     <x:row r="62">
@@ -12989,16 +13557,16 @@
         <x:v>Ball - Saratoga Springs</x:v>
       </x:c>
       <x:c r="C62" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D62" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E62" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F62" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Saratoga Springs, New York; GeoNames ID 5136334</x:v>
       </x:c>
     </x:row>
     <x:row r="63">
@@ -13009,16 +13577,16 @@
         <x:v>Ball - Winter Haven</x:v>
       </x:c>
       <x:c r="C63" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D63" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E63" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F63" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Winter Haven, Florida; GeoNames ID 4178552</x:v>
       </x:c>
     </x:row>
     <x:row r="64">
@@ -13349,16 +13917,16 @@
         <x:v>Crown - Effingham</x:v>
       </x:c>
       <x:c r="C80" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D80" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E80" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F80" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Effingham, South Carolina; GeoNames ID 4577612</x:v>
       </x:c>
     </x:row>
     <x:row r="81">
@@ -13509,16 +14077,16 @@
         <x:v>Crown - Calgary</x:v>
       </x:c>
       <x:c r="C88" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D88" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E88" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F88" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Calgary, Alberta; GeoNames ID 5913490</x:v>
       </x:c>
     </x:row>
     <x:row r="89">
@@ -13529,16 +14097,16 @@
         <x:v>Crown - Halton Hills</x:v>
       </x:c>
       <x:c r="C89" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D89" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E89" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F89" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Halton Hills, Ontario; GeoNames ID 5969721</x:v>
       </x:c>
     </x:row>
     <x:row r="90">
@@ -13549,16 +14117,16 @@
         <x:v>Crown - Toronto</x:v>
       </x:c>
       <x:c r="C90" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D90" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E90" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F90" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Toronto, Ontario; GeoNames ID 6167865</x:v>
       </x:c>
     </x:row>
     <x:row r="91">
@@ -13589,16 +14157,16 @@
         <x:v>O-I - Bowling Green</x:v>
       </x:c>
       <x:c r="C92" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D92" s="35" t="str">
-        <x:v>U.S. Census + OpenStreetMap fallback</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E92" s="35" t="str">
-        <x:v>No accepted match</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F92" s="36" t="str">
-        <x:v>Street address requires manual verification</x:v>
+        <x:v>Bowling Green, Kentucky; GeoNames ID 4285268</x:v>
       </x:c>
     </x:row>
     <x:row r="93">
@@ -13609,16 +14177,16 @@
         <x:v>O-I - Brockway</x:v>
       </x:c>
       <x:c r="C93" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D93" s="35" t="str">
-        <x:v>U.S. Census + OpenStreetMap fallback</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E93" s="35" t="str">
-        <x:v>No accepted match</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F93" s="36" t="str">
-        <x:v>Street address requires manual verification</x:v>
+        <x:v>Brockport, Pennsylvania; GeoNames ID 5181750</x:v>
       </x:c>
     </x:row>
     <x:row r="94">
@@ -13629,16 +14197,16 @@
         <x:v>O-I - Crenshaw</x:v>
       </x:c>
       <x:c r="C94" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D94" s="35" t="str">
-        <x:v>U.S. Census + OpenStreetMap fallback</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E94" s="35" t="str">
-        <x:v>No accepted match</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F94" s="36" t="str">
-        <x:v>Street address requires manual verification</x:v>
+        <x:v>Brockport, Pennsylvania; GeoNames ID 5181750</x:v>
       </x:c>
     </x:row>
     <x:row r="95">
@@ -13649,13 +14217,13 @@
         <x:v>O-I - Danville</x:v>
       </x:c>
       <x:c r="C95" s="35" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D95" s="35" t="str">
         <x:v>U.S. Census Geocoder, benchmark 4</x:v>
       </x:c>
       <x:c r="E95" s="35" t="str">
-        <x:v>Non-exact match</x:v>
+        <x:v>Non-exact street match</x:v>
       </x:c>
       <x:c r="F95" s="36" t="str">
         <x:v>29 GLASSBLOWER LN, RINGGOLD, VA, 24586</x:v>
@@ -13669,16 +14237,16 @@
         <x:v>O-I - Kalama</x:v>
       </x:c>
       <x:c r="C96" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D96" s="35" t="str">
-        <x:v>U.S. Census + OpenStreetMap fallback</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E96" s="35" t="str">
-        <x:v>No accepted match</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F96" s="36" t="str">
-        <x:v>Street address requires manual verification</x:v>
+        <x:v>Kalama, Washington; GeoNames ID 5799410</x:v>
       </x:c>
     </x:row>
     <x:row r="97">
@@ -13689,13 +14257,13 @@
         <x:v>O-I - Lapel</x:v>
       </x:c>
       <x:c r="C97" s="35" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D97" s="35" t="str">
         <x:v>U.S. Census Geocoder, benchmark 4</x:v>
       </x:c>
       <x:c r="E97" s="35" t="str">
-        <x:v>Non-exact match</x:v>
+        <x:v>Non-exact street match</x:v>
       </x:c>
       <x:c r="F97" s="36" t="str">
         <x:v>2481 BROOKSIDE RD, LAPEL, IN, 46051</x:v>
@@ -13709,13 +14277,13 @@
         <x:v>O-I - Los Angeles</x:v>
       </x:c>
       <x:c r="C98" s="35" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D98" s="35" t="str">
         <x:v>U.S. Census Geocoder, benchmark 4</x:v>
       </x:c>
       <x:c r="E98" s="35" t="str">
-        <x:v>Non-exact match</x:v>
+        <x:v>Non-exact street match</x:v>
       </x:c>
       <x:c r="F98" s="36" t="str">
         <x:v>2901 FRUITLAND AVE, LOS ANGELES, CA, 90058</x:v>
@@ -13749,13 +14317,13 @@
         <x:v>O-I - Toano</x:v>
       </x:c>
       <x:c r="C100" s="35" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D100" s="35" t="str">
         <x:v>U.S. Census Geocoder, benchmark 4</x:v>
       </x:c>
       <x:c r="E100" s="35" t="str">
-        <x:v>Non-exact match</x:v>
+        <x:v>Non-exact street match</x:v>
       </x:c>
       <x:c r="F100" s="36" t="str">
         <x:v>150 INDUSTRIAL BLVD, TOANO, VA, 23168</x:v>
@@ -13769,13 +14337,13 @@
         <x:v>O-I - Tracy</x:v>
       </x:c>
       <x:c r="C101" s="35" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D101" s="35" t="str">
         <x:v>U.S. Census Geocoder, benchmark 4</x:v>
       </x:c>
       <x:c r="E101" s="35" t="str">
-        <x:v>Non-exact match</x:v>
+        <x:v>Non-exact street match</x:v>
       </x:c>
       <x:c r="F101" s="36" t="str">
         <x:v>14700 W SCHULTE RD, TRACY, CA, 95377</x:v>
@@ -13829,13 +14397,13 @@
         <x:v>O-I - Zanesville</x:v>
       </x:c>
       <x:c r="C104" s="35" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D104" s="35" t="str">
         <x:v>U.S. Census Geocoder, benchmark 4</x:v>
       </x:c>
       <x:c r="E104" s="35" t="str">
-        <x:v>Non-exact match</x:v>
+        <x:v>Non-exact street match</x:v>
       </x:c>
       <x:c r="F104" s="36" t="str">
         <x:v>1700 S STATE ST, ZANESVILLE, OH, 43701</x:v>
@@ -13849,16 +14417,16 @@
         <x:v>O-I - Brampton</x:v>
       </x:c>
       <x:c r="C105" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D105" s="35" t="str">
-        <x:v>Not automatically matched</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E105" s="35" t="str">
-        <x:v>Street address pending</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F105" s="36" t="str">
-        <x:v>Requires manual verification or non-U.S. geocoder</x:v>
+        <x:v>Brampton, Ontario; GeoNames ID 5907364</x:v>
       </x:c>
     </x:row>
     <x:row r="106">
@@ -13889,16 +14457,16 @@
         <x:v>Aspire Bakeries - Alsip</x:v>
       </x:c>
       <x:c r="C107" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D107" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E107" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F107" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Alsip, Illinois; GeoNames ID 4883207</x:v>
       </x:c>
     </x:row>
     <x:row r="108">
@@ -13909,16 +14477,16 @@
         <x:v>Aspire Bakeries - Anaheim</x:v>
       </x:c>
       <x:c r="C108" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D108" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E108" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F108" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Anaheim, California; GeoNames ID 5323810</x:v>
       </x:c>
     </x:row>
     <x:row r="109">
@@ -13929,16 +14497,16 @@
         <x:v>Aspire Bakeries - Bolingbrook</x:v>
       </x:c>
       <x:c r="C109" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D109" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E109" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F109" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Bolingbrook, Illinois; GeoNames ID 4885265</x:v>
       </x:c>
     </x:row>
     <x:row r="110">
@@ -13949,16 +14517,16 @@
         <x:v>Aspire Bakeries - Chicago Heights</x:v>
       </x:c>
       <x:c r="C110" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D110" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E110" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F110" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Chicago Heights, Illinois; GeoNames ID 4887442</x:v>
       </x:c>
     </x:row>
     <x:row r="111">
@@ -13969,16 +14537,16 @@
         <x:v>Aspire Bakeries - Chaska</x:v>
       </x:c>
       <x:c r="C111" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D111" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E111" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F111" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Chaska, Minnesota; GeoNames ID 5020938</x:v>
       </x:c>
     </x:row>
     <x:row r="112">
@@ -13989,16 +14557,16 @@
         <x:v>Aspire Bakeries - Cayce</x:v>
       </x:c>
       <x:c r="C112" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D112" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E112" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F112" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Cayce, South Carolina; GeoNames ID 4573888</x:v>
       </x:c>
     </x:row>
     <x:row r="113">
@@ -14009,16 +14577,16 @@
         <x:v>Aspire Bakeries - Commerce</x:v>
       </x:c>
       <x:c r="C113" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D113" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E113" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F113" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Commerce, California; GeoNames ID 5338929</x:v>
       </x:c>
     </x:row>
     <x:row r="114">
@@ -14029,16 +14597,16 @@
         <x:v>Aspire Bakeries - Hazleton</x:v>
       </x:c>
       <x:c r="C114" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D114" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E114" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F114" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Hazleton, Pennsylvania; GeoNames ID 5193011</x:v>
       </x:c>
     </x:row>
     <x:row r="115">
@@ -14049,16 +14617,16 @@
         <x:v>Aspire Bakeries - Swedesboro</x:v>
       </x:c>
       <x:c r="C115" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D115" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E115" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F115" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Swedesboro, New Jersey; GeoNames ID 4504391</x:v>
       </x:c>
     </x:row>
     <x:row r="116">
@@ -14069,16 +14637,16 @@
         <x:v>Aspire Bakeries - Van Nuys</x:v>
       </x:c>
       <x:c r="C116" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D116" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E116" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F116" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Van Nuys, California; GeoNames ID 5405693</x:v>
       </x:c>
     </x:row>
     <x:row r="117">
@@ -14089,16 +14657,16 @@
         <x:v>Bimbo Bakeries USA - Mattoon</x:v>
       </x:c>
       <x:c r="C117" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D117" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E117" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F117" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Mattoon, Illinois; GeoNames ID 4244099</x:v>
       </x:c>
     </x:row>
     <x:row r="118">
@@ -14109,16 +14677,16 @@
         <x:v>Bimbo Bakeries USA - Oxnard</x:v>
       </x:c>
       <x:c r="C118" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D118" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E118" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F118" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Oxnard, California; GeoNames ID 5380184</x:v>
       </x:c>
     </x:row>
     <x:row r="119">
@@ -14129,16 +14697,16 @@
         <x:v>Bimbo Bakeries USA - Fort Worth</x:v>
       </x:c>
       <x:c r="C119" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D119" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E119" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F119" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Fort Worth, Texas; GeoNames ID 4691930</x:v>
       </x:c>
     </x:row>
     <x:row r="120">
@@ -14149,16 +14717,16 @@
         <x:v>Bimbo Bakeries USA - San Antonio</x:v>
       </x:c>
       <x:c r="C120" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D120" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E120" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F120" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>San Antonio, Texas; GeoNames ID 4726206</x:v>
       </x:c>
     </x:row>
     <x:row r="121">
@@ -14169,16 +14737,16 @@
         <x:v>Bimbo Bakeries USA - Rockwall</x:v>
       </x:c>
       <x:c r="C121" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D121" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E121" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F121" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Rockwall, Texas; GeoNames ID 4723406</x:v>
       </x:c>
     </x:row>
     <x:row r="122">
@@ -14189,16 +14757,16 @@
         <x:v>Bimbo Bakeries USA - Denver</x:v>
       </x:c>
       <x:c r="C122" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D122" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E122" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F122" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Denver, Colorado; GeoNames ID 5419384</x:v>
       </x:c>
     </x:row>
     <x:row r="123">
@@ -14209,16 +14777,16 @@
         <x:v>Bimbo Bakeries USA - Phoenix</x:v>
       </x:c>
       <x:c r="C123" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D123" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E123" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F123" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Phoenix, Arizona; GeoNames ID 5308655</x:v>
       </x:c>
     </x:row>
     <x:row r="124">
@@ -14229,16 +14797,16 @@
         <x:v>Bimbo Bakeries USA - South San Francisco</x:v>
       </x:c>
       <x:c r="C124" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D124" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E124" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F124" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>South San Francisco, California; GeoNames ID 5397765</x:v>
       </x:c>
     </x:row>
     <x:row r="125">
@@ -14249,16 +14817,16 @@
         <x:v>Bimbo Bakeries USA - Escondido</x:v>
       </x:c>
       <x:c r="C125" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D125" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E125" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F125" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Escondido, California; GeoNames ID 5346827</x:v>
       </x:c>
     </x:row>
     <x:row r="126">
@@ -14269,16 +14837,16 @@
         <x:v>Mondelez - Chicago</x:v>
       </x:c>
       <x:c r="C126" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D126" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E126" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F126" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Chicago, Illinois; GeoNames ID 4887398</x:v>
       </x:c>
     </x:row>
     <x:row r="127">
@@ -14289,16 +14857,16 @@
         <x:v>Mondelez - Richmond</x:v>
       </x:c>
       <x:c r="C127" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D127" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E127" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F127" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Richmond, Virginia; GeoNames ID 4781708</x:v>
       </x:c>
     </x:row>
     <x:row r="128">
@@ -14309,16 +14877,16 @@
         <x:v>Mondelez - Fair Lawn</x:v>
       </x:c>
       <x:c r="C128" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D128" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E128" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F128" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Fair Lawn, New Jersey; GeoNames ID 5097773</x:v>
       </x:c>
     </x:row>
     <x:row r="129">
@@ -14329,16 +14897,16 @@
         <x:v>Mondelez - Portland</x:v>
       </x:c>
       <x:c r="C129" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D129" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E129" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F129" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Portland, Oregon; GeoNames ID 5746545</x:v>
       </x:c>
     </x:row>
     <x:row r="130">
@@ -14349,16 +14917,16 @@
         <x:v>Mondelez - Naperville</x:v>
       </x:c>
       <x:c r="C130" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D130" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E130" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F130" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Naperville, Illinois; GeoNames ID 4903279</x:v>
       </x:c>
     </x:row>
     <x:row r="131">
@@ -14489,13 +15057,13 @@
         <x:v>Campbell's - Dixon</x:v>
       </x:c>
       <x:c r="C137" s="35" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D137" s="35" t="str">
         <x:v>U.S. Census Geocoder, benchmark 4</x:v>
       </x:c>
       <x:c r="E137" s="35" t="str">
-        <x:v>Non-exact match</x:v>
+        <x:v>Non-exact street match</x:v>
       </x:c>
       <x:c r="F137" s="36" t="str">
         <x:v>8380 PEDRICK RD, DIXON, CA, 95620</x:v>
@@ -14669,13 +15237,13 @@
         <x:v>Campbell's - Maxton</x:v>
       </x:c>
       <x:c r="C146" s="35" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D146" s="35" t="str">
         <x:v>U.S. Census Geocoder, benchmark 4</x:v>
       </x:c>
       <x:c r="E146" s="35" t="str">
-        <x:v>Non-exact match</x:v>
+        <x:v>Non-exact street match</x:v>
       </x:c>
       <x:c r="F146" s="36" t="str">
         <x:v>2120 STATE HWY 71 N, MAXTON, NC, 28364</x:v>
@@ -14709,16 +15277,16 @@
         <x:v>Campbell's - Napoleon</x:v>
       </x:c>
       <x:c r="C148" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D148" s="35" t="str">
-        <x:v>U.S. Census + OpenStreetMap fallback</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E148" s="35" t="str">
-        <x:v>No accepted match</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F148" s="36" t="str">
-        <x:v>Street address requires manual verification</x:v>
+        <x:v>Napoleon, Ohio; GeoNames ID 5164057</x:v>
       </x:c>
     </x:row>
     <x:row r="149">
@@ -14729,13 +15297,13 @@
         <x:v>Campbell's - Paris</x:v>
       </x:c>
       <x:c r="C149" s="35" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D149" s="35" t="str">
         <x:v>U.S. Census Geocoder, benchmark 4</x:v>
       </x:c>
       <x:c r="E149" s="35" t="str">
-        <x:v>Non-exact match</x:v>
+        <x:v>Non-exact street match</x:v>
       </x:c>
       <x:c r="F149" s="36" t="str">
         <x:v>500 NW LOOP 286, PARIS, TX, 75460</x:v>
@@ -14749,16 +15317,16 @@
         <x:v>Campbell's - Richmond</x:v>
       </x:c>
       <x:c r="C150" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D150" s="35" t="str">
-        <x:v>U.S. Census + OpenStreetMap fallback</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E150" s="35" t="str">
-        <x:v>No accepted match</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F150" s="36" t="str">
-        <x:v>Street address requires manual verification</x:v>
+        <x:v>Richmond, Utah; GeoNames ID 5780388</x:v>
       </x:c>
     </x:row>
     <x:row r="151">
@@ -14829,13 +15397,13 @@
         <x:v>Campbell's - Willard</x:v>
       </x:c>
       <x:c r="C154" s="35" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D154" s="35" t="str">
         <x:v>U.S. Census Geocoder, benchmark 4</x:v>
       </x:c>
       <x:c r="E154" s="35" t="str">
-        <x:v>Non-exact match</x:v>
+        <x:v>Non-exact street match</x:v>
       </x:c>
       <x:c r="F154" s="36" t="str">
         <x:v>3320 STATE RTE 103, WILLARD, OH, 44890</x:v>
@@ -14929,16 +15497,16 @@
         <x:v>Nestlé - Anderson</x:v>
       </x:c>
       <x:c r="C159" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D159" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E159" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F159" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Anderson, Indiana; GeoNames ID 4917592</x:v>
       </x:c>
     </x:row>
     <x:row r="160">
@@ -14949,16 +15517,16 @@
         <x:v>Nestlé - Burlington</x:v>
       </x:c>
       <x:c r="C160" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D160" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E160" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F160" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Burlington, Wisconsin; GeoNames ID 5247214</x:v>
       </x:c>
     </x:row>
     <x:row r="161">
@@ -14969,16 +15537,16 @@
         <x:v>Nestlé - Cleveland</x:v>
       </x:c>
       <x:c r="C161" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D161" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E161" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F161" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Cleveland, Ohio; GeoNames ID 5150529</x:v>
       </x:c>
     </x:row>
     <x:row r="162">
@@ -14989,16 +15557,16 @@
         <x:v>Nestlé - Davenport</x:v>
       </x:c>
       <x:c r="C162" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D162" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E162" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F162" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Davenport, Iowa; GeoNames ID 4853423</x:v>
       </x:c>
     </x:row>
     <x:row r="163">
@@ -15009,16 +15577,16 @@
         <x:v>Nestlé - Eden</x:v>
       </x:c>
       <x:c r="C163" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D163" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E163" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F163" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Eden, North Carolina; GeoNames ID 4464873</x:v>
       </x:c>
     </x:row>
     <x:row r="164">
@@ -15029,16 +15597,16 @@
         <x:v>Nestlé - Hartwell</x:v>
       </x:c>
       <x:c r="C164" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D164" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E164" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F164" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Hartwell, Georgia; GeoNames ID 4199572</x:v>
       </x:c>
     </x:row>
     <x:row r="165">
@@ -15049,16 +15617,16 @@
         <x:v>Nestlé - St. Louis</x:v>
       </x:c>
       <x:c r="C165" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D165" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E165" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F165" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>St. Louis, Missouri; GeoNames ID 4407066</x:v>
       </x:c>
     </x:row>
     <x:row r="166">
@@ -15069,16 +15637,16 @@
         <x:v>Nestlé - Solon</x:v>
       </x:c>
       <x:c r="C166" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D166" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E166" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F166" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Solon, Ohio; GeoNames ID 5172387</x:v>
       </x:c>
     </x:row>
     <x:row r="167">
@@ -15329,13 +15897,13 @@
         <x:v>Silgan - Savage</x:v>
       </x:c>
       <x:c r="C179" s="35" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D179" s="35" t="str">
         <x:v>U.S. Census Geocoder, benchmark 4</x:v>
       </x:c>
       <x:c r="E179" s="35" t="str">
-        <x:v>Non-exact match</x:v>
+        <x:v>Non-exact street match</x:v>
       </x:c>
       <x:c r="F179" s="36" t="str">
         <x:v>12130 LYNN AVE, SAVAGE, MN, 55378</x:v>
@@ -15389,13 +15957,13 @@
         <x:v>Silgan - Maxton</x:v>
       </x:c>
       <x:c r="C182" s="35" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D182" s="35" t="str">
         <x:v>U.S. Census Geocoder, benchmark 4</x:v>
       </x:c>
       <x:c r="E182" s="35" t="str">
-        <x:v>Non-exact match</x:v>
+        <x:v>Non-exact street match</x:v>
       </x:c>
       <x:c r="F182" s="36" t="str">
         <x:v>2120 STATE HWY 71 N, MAXTON, NC, 28364</x:v>
@@ -15409,16 +15977,16 @@
         <x:v>Silgan - Napoleon</x:v>
       </x:c>
       <x:c r="C183" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D183" s="35" t="str">
-        <x:v>U.S. Census + OpenStreetMap fallback</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E183" s="35" t="str">
-        <x:v>No accepted match</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F183" s="36" t="str">
-        <x:v>Street address requires manual verification</x:v>
+        <x:v>Napoleon, Ohio; GeoNames ID 5164057</x:v>
       </x:c>
     </x:row>
     <x:row r="184">
@@ -15489,13 +16057,13 @@
         <x:v>Silgan - Paris</x:v>
       </x:c>
       <x:c r="C187" s="35" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D187" s="35" t="str">
         <x:v>U.S. Census Geocoder, benchmark 4</x:v>
       </x:c>
       <x:c r="E187" s="35" t="str">
-        <x:v>Non-exact match</x:v>
+        <x:v>Non-exact street match</x:v>
       </x:c>
       <x:c r="F187" s="36" t="str">
         <x:v>500 NW LOOP 286, PARIS, TX, 75460</x:v>
@@ -15529,13 +16097,13 @@
         <x:v>Silgan - Kenosha</x:v>
       </x:c>
       <x:c r="C189" s="35" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D189" s="35" t="str">
         <x:v>U.S. Census Geocoder, benchmark 4</x:v>
       </x:c>
       <x:c r="E189" s="35" t="str">
-        <x:v>Non-exact match</x:v>
+        <x:v>Non-exact street match</x:v>
       </x:c>
       <x:c r="F189" s="36" t="str">
         <x:v>2602 128TH ST, KENOSHA, WI, 53158</x:v>
@@ -15569,13 +16137,13 @@
         <x:v>Silgan - Menomonie</x:v>
       </x:c>
       <x:c r="C191" s="35" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D191" s="35" t="str">
         <x:v>U.S. Census Geocoder, benchmark 4</x:v>
       </x:c>
       <x:c r="E191" s="35" t="str">
-        <x:v>Non-exact match</x:v>
+        <x:v>Non-exact street match</x:v>
       </x:c>
       <x:c r="F191" s="36" t="str">
         <x:v>1416 INDIANHEAD DR E, MENOMONIE, WI, 54751</x:v>
@@ -15629,16 +16197,16 @@
         <x:v>Silgan - Las Piedras</x:v>
       </x:c>
       <x:c r="C194" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D194" s="35" t="str">
-        <x:v>U.S. Census + OpenStreetMap fallback</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E194" s="35" t="str">
-        <x:v>No accepted match</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F194" s="36" t="str">
-        <x:v>Street address requires manual verification</x:v>
+        <x:v>Las Piedras, Las Piedras; GeoNames ID 4565980</x:v>
       </x:c>
     </x:row>
     <x:row r="195">
@@ -15649,16 +16217,16 @@
         <x:v>Kraft Heinz - Champaign</x:v>
       </x:c>
       <x:c r="C195" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D195" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E195" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F195" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Champaign, Illinois; GeoNames ID 4887158</x:v>
       </x:c>
     </x:row>
     <x:row r="196">
@@ -15669,16 +16237,16 @@
         <x:v>Kraft Heinz - Fremont</x:v>
       </x:c>
       <x:c r="C196" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D196" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E196" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F196" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Fremont, Ohio; GeoNames ID 5155207</x:v>
       </x:c>
     </x:row>
     <x:row r="197">
@@ -15689,16 +16257,16 @@
         <x:v>Kraft Heinz - Springfield</x:v>
       </x:c>
       <x:c r="C197" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D197" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E197" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F197" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Springfield, Missouri; GeoNames ID 4409896</x:v>
       </x:c>
     </x:row>
     <x:row r="198">
@@ -15709,16 +16277,16 @@
         <x:v>Kraft Heinz - Garland</x:v>
       </x:c>
       <x:c r="C198" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D198" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E198" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F198" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Garland, Texas; GeoNames ID 4693003</x:v>
       </x:c>
     </x:row>
     <x:row r="199">
@@ -15729,16 +16297,16 @@
         <x:v>Kraft Heinz - Dover</x:v>
       </x:c>
       <x:c r="C199" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D199" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E199" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F199" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Dover, Delaware; GeoNames ID 4142290</x:v>
       </x:c>
     </x:row>
     <x:row r="200">
@@ -15749,16 +16317,16 @@
         <x:v>Kraft Heinz - Newberry</x:v>
       </x:c>
       <x:c r="C200" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D200" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E200" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F200" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Newberry, South Carolina; GeoNames ID 4589207</x:v>
       </x:c>
     </x:row>
     <x:row r="201">
@@ -15769,16 +16337,16 @@
         <x:v>Kraft Heinz - Massillon</x:v>
       </x:c>
       <x:c r="C201" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D201" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E201" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F201" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Massillon, Ohio; GeoNames ID 5162097</x:v>
       </x:c>
     </x:row>
     <x:row r="202">
@@ -15789,16 +16357,16 @@
         <x:v>Kraft Heinz - Jacksonville</x:v>
       </x:c>
       <x:c r="C202" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D202" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E202" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F202" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Jacksonville, Florida; GeoNames ID 4160021</x:v>
       </x:c>
     </x:row>
     <x:row r="203">
@@ -15989,13 +16557,13 @@
         <x:v>Tempe Plant</x:v>
       </x:c>
       <x:c r="C212" s="35" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D212" s="35" t="str">
         <x:v>U.S. Census Geocoder, benchmark 4</x:v>
       </x:c>
       <x:c r="E212" s="35" t="str">
-        <x:v>Non-exact match</x:v>
+        <x:v>Non-exact street match</x:v>
       </x:c>
       <x:c r="F212" s="36" t="str">
         <x:v>1850 W ELLIOT RD, TEMPE, AZ, 85284</x:v>
@@ -16069,13 +16637,13 @@
         <x:v>Fruitland Plant</x:v>
       </x:c>
       <x:c r="C216" s="35" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D216" s="35" t="str">
         <x:v>U.S. Census Geocoder, benchmark 4</x:v>
       </x:c>
       <x:c r="E216" s="35" t="str">
-        <x:v>Non-exact match</x:v>
+        <x:v>Non-exact street match</x:v>
       </x:c>
       <x:c r="F216" s="36" t="str">
         <x:v>500 SW 7TH ST, FRUITLAND, ID, 83619</x:v>
@@ -16089,16 +16657,16 @@
         <x:v>Colorado Springs Manufacturing Facility</x:v>
       </x:c>
       <x:c r="C217" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D217" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E217" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F217" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Colorado Springs, Colorado; GeoNames ID 5417598</x:v>
       </x:c>
     </x:row>
     <x:row r="218">
@@ -16289,16 +16857,16 @@
         <x:v>Philadelphia Production, Sales &amp; Distribution</x:v>
       </x:c>
       <x:c r="C227" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D227" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E227" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F227" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Philadelphia, Pennsylvania; GeoNames ID 4560349</x:v>
       </x:c>
     </x:row>
     <x:row r="228">
@@ -16309,16 +16877,16 @@
         <x:v>Moorestown Production Plant</x:v>
       </x:c>
       <x:c r="C228" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D228" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E228" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F228" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Moorestown, New Jersey; GeoNames ID 4503106</x:v>
       </x:c>
     </x:row>
     <x:row r="229">
@@ -16369,16 +16937,16 @@
         <x:v>Snyder Production Center</x:v>
       </x:c>
       <x:c r="C231" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D231" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E231" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F231" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Charlotte, North Carolina; GeoNames ID 4460243</x:v>
       </x:c>
     </x:row>
     <x:row r="232">
@@ -16389,16 +16957,16 @@
         <x:v>Sandston Manufacturing Facility</x:v>
       </x:c>
       <x:c r="C232" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D232" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E232" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F232" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Sandston, Virginia; GeoNames ID 4784352</x:v>
       </x:c>
     </x:row>
     <x:row r="233">
@@ -16409,16 +16977,16 @@
         <x:v>Silver Spring Production Facility</x:v>
       </x:c>
       <x:c r="C233" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D233" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E233" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F233" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Silver Spring, Maryland; GeoNames ID 4369596</x:v>
       </x:c>
     </x:row>
     <x:row r="234">
@@ -16429,16 +16997,16 @@
         <x:v>Baltimore Production Center</x:v>
       </x:c>
       <x:c r="C234" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D234" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E234" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F234" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Baltimore, Maryland; GeoNames ID 4347778</x:v>
       </x:c>
     </x:row>
     <x:row r="235">
@@ -16469,16 +17037,16 @@
         <x:v>Portland Manufacturing Facility</x:v>
       </x:c>
       <x:c r="C236" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D236" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E236" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F236" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Portland, Indiana; GeoNames ID 4925037</x:v>
       </x:c>
     </x:row>
     <x:row r="237">
@@ -16489,16 +17057,16 @@
         <x:v>Cincinnati Manufacturing Facility</x:v>
       </x:c>
       <x:c r="C237" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D237" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E237" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F237" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Cincinnati, Ohio; GeoNames ID 4508722</x:v>
       </x:c>
     </x:row>
     <x:row r="238">
@@ -16529,16 +17097,16 @@
         <x:v>West Memphis Manufacturing Facility</x:v>
       </x:c>
       <x:c r="C239" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D239" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E239" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F239" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>West Memphis, Arkansas; GeoNames ID 4135865</x:v>
       </x:c>
     </x:row>
     <x:row r="240">
@@ -16549,16 +17117,16 @@
         <x:v>Memphis Manufacturing Facility</x:v>
       </x:c>
       <x:c r="C240" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D240" s="35" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E240" s="35" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F240" s="36" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Memphis, Tennessee; GeoNames ID 4641239</x:v>
       </x:c>
     </x:row>
     <x:row r="241">
@@ -16569,16 +17137,16 @@
         <x:v>Garner Production Facility</x:v>
       </x:c>
       <x:c r="C241" s="35" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D241" s="35" t="str">
-        <x:v>U.S. Census + OpenStreetMap fallback</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E241" s="35" t="str">
-        <x:v>No accepted match</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F241" s="36" t="str">
-        <x:v>Street address requires manual verification</x:v>
+        <x:v>Garner, North Carolina; GeoNames ID 4467657</x:v>
       </x:c>
     </x:row>
     <x:row r="242">
@@ -16769,13 +17337,13 @@
         <x:v>Dyersburg Filling Plant</x:v>
       </x:c>
       <x:c r="C251" s="35" t="str">
-        <x:v>Pending review</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D251" s="35" t="str">
         <x:v>U.S. Census Geocoder, benchmark 4</x:v>
       </x:c>
       <x:c r="E251" s="35" t="str">
-        <x:v>Non-exact match</x:v>
+        <x:v>Non-exact street match</x:v>
       </x:c>
       <x:c r="F251" s="36" t="str">
         <x:v>2918 US HWY 51, DYERSBURG, TN, 38024</x:v>
@@ -16909,22 +17477,22 @@
         <x:v>Stone Mountain / Atlanta Beverage Plant</x:v>
       </x:c>
       <x:c r="C258" s="38" t="str">
-        <x:v>Unresolved</x:v>
+        <x:v>Added — approximate</x:v>
       </x:c>
       <x:c r="D258" s="38" t="str">
-        <x:v>No street address supplied</x:v>
+        <x:v>GeoNames city/place centroid (CC BY 4.0)</x:v>
       </x:c>
       <x:c r="E258" s="38" t="str">
-        <x:v>City-level research required</x:v>
+        <x:v>City-center fallback</x:v>
       </x:c>
       <x:c r="F258" s="39" t="str">
-        <x:v>Latitude/longitude intentionally left blank</x:v>
+        <x:v>Stone Mountain, Georgia; GeoNames ID 4224745</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra6d17ae4bcfd4818"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R19d3de9bd3be4928"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/source-data/Strategic_End_User_Facilities_Bottler_Expansion_v2.xlsx
+++ b/source-data/Strategic_End_User_Facilities_Bottler_Expansion_v2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/josephnovotny/Documents/Codex/2026-08-10/continue-my-strategic-facility-locations-map-2/outputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23E71029-25E2-E545-A52A-062A2E9E6C43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A341C086-26E4-DD4B-AC93-3F78D5800768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="600" windowWidth="51200" windowHeight="26400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="26400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Master Facilities v2" sheetId="1" r:id="rId1"/>
@@ -3912,7 +3912,7 @@
   <autoFilter ref="A1:P258" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}">
     <filterColumn colId="7">
       <filters>
-        <filter val="ID"/>
+        <filter val="AZ"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -4467,7 +4467,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="7" spans="1:16" ht="30" hidden="1">
+    <row r="7" spans="1:16" ht="30">
       <c r="A7" s="2" t="s">
         <v>16</v>
       </c>
@@ -5049,7 +5049,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="20" spans="1:16" ht="30" hidden="1">
+    <row r="20" spans="1:16" ht="30">
       <c r="A20" s="2" t="s">
         <v>52</v>
       </c>
@@ -6487,7 +6487,7 @@
       </c>
       <c r="P51" s="2"/>
     </row>
-    <row r="52" spans="1:16" ht="30" hidden="1">
+    <row r="52" spans="1:16" ht="30">
       <c r="A52" s="2" t="s">
         <v>165</v>
       </c>
@@ -6533,7 +6533,7 @@
       </c>
       <c r="P52" s="2"/>
     </row>
-    <row r="53" spans="1:16" ht="30" hidden="1">
+    <row r="53" spans="1:16" ht="30">
       <c r="A53" s="2" t="s">
         <v>165</v>
       </c>
@@ -9739,7 +9739,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="123" spans="1:16" ht="30" hidden="1">
+    <row r="123" spans="1:16" ht="30">
       <c r="A123" s="2" t="s">
         <v>364</v>
       </c>
@@ -10587,7 +10587,7 @@
       </c>
       <c r="P140" s="2"/>
     </row>
-    <row r="141" spans="1:16" ht="15" hidden="1">
+    <row r="141" spans="1:16" ht="15">
       <c r="A141" s="2" t="s">
         <v>425</v>
       </c>
@@ -10625,7 +10625,7 @@
         <v>-112.37537741849501</v>
       </c>
       <c r="M141" s="2" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="N141" s="2" t="s">
         <v>25</v>
@@ -13995,7 +13995,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="212" spans="1:16" ht="30" hidden="1">
+    <row r="212" spans="1:16" ht="30">
       <c r="A212" s="2" t="s">
         <v>16</v>
       </c>
@@ -14195,7 +14195,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="216" spans="1:16" ht="30">
+    <row r="216" spans="1:16" ht="30" hidden="1">
       <c r="A216" s="2" t="s">
         <v>16</v>
       </c>
